--- a/palpites/palpiteRenato.xlsx
+++ b/palpites/palpiteRenato.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30128"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D48B6998-F1F5-47FC-9CB0-BA5A74C1573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9945A814-C848-4CA7-B870-F367A730DD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1222,6 +1222,57 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1270,9 +1321,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1283,54 +1331,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1720,27 +1720,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="J1" s="134" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="J1" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="S1" s="134" t="s">
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="S1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
       <c r="AB1" s="42"/>
       <c r="AC1" s="17" t="s">
         <v>3</v>
@@ -1767,14 +1767,14 @@
       <c r="AL1" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="100"/>
-      <c r="AS1" s="100"/>
-      <c r="AV1" s="100"/>
-      <c r="AW1" s="100"/>
-      <c r="AX1" s="100"/>
+      <c r="AM1" s="112"/>
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="112"/>
+      <c r="AX1" s="112"/>
       <c r="BI1" s="11" t="str">
         <f>COUNTIF($AG$38:$AG$45,"A") &amp; COUNTIF($AG$38:$AG$45,"B") &amp; COUNTIF($AG$38:$AG$45,"C") &amp; COUNTIF($AG$38:$AG$45,"D") &amp; COUNTIF($AG$38:$AG$45,"E") &amp; COUNTIF($AG$38:$AG$45,"F") &amp; COUNTIF($AG$38:$AG$45,"G") &amp; COUNTIF($AG$38:$AG$45,"H") &amp; COUNTIF($AG$38:$AG$45,"I") &amp; COUNTIF($AG$38:$AG$45,"J") &amp; COUNTIF($AG$38:$AG$45,"K") &amp; COUNTIF($AG$38:$AG$45,"L")</f>
         <v>011111011001</v>
@@ -1803,13 +1803,13 @@
         <v>46191</v>
       </c>
       <c r="P2" s="3"/>
-      <c r="S2" s="123" t="s">
+      <c r="S2" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
       <c r="X2" s="10">
         <v>46197</v>
       </c>
@@ -1820,15 +1820,15 @@
         <f>INDEX($AC$80:$AC$83, MATCH(LARGE($AG$80:$AG$83, AB2), $AG$80:$AG$83, 0))</f>
         <v>México</v>
       </c>
-      <c r="AD2" s="105">
+      <c r="AD2" s="102">
         <f>VLOOKUP(AC2, $AC$80:$AF$83, 2, 0)</f>
         <v>9</v>
       </c>
-      <c r="AE2" s="105">
+      <c r="AE2" s="102">
         <f>VLOOKUP(AC2, $AC$80:$AF$83, 3, 0)</f>
         <v>8</v>
       </c>
-      <c r="AF2" s="105">
+      <c r="AF2" s="102">
         <f>VLOOKUP(AC2, $AC$80:$AF$83, 4, 0)</f>
         <v>9</v>
       </c>
@@ -1839,38 +1839,38 @@
         <f>INDEX($AI$80:$AI$83, MATCH(LARGE($AM$80:$AM$83, AH2), $AM$80:$AM$83, 0))</f>
         <v>Suíça</v>
       </c>
-      <c r="AJ2" s="108">
+      <c r="AJ2" s="103">
         <f>VLOOKUP(AI2, $AI$80:$AL$83, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AK2" s="108">
+      <c r="AK2" s="103">
         <f>VLOOKUP(AI2, $AI$80:$AL$83, 3, 0)</f>
         <v>5</v>
       </c>
-      <c r="AL2" s="108">
+      <c r="AL2" s="103">
         <f>VLOOKUP(AI2, $AI$80:$AL$83, 4, 0)</f>
         <v>7</v>
       </c>
-      <c r="AM2" s="100"/>
-      <c r="AP2" s="100"/>
-      <c r="AQ2" s="100"/>
-      <c r="AR2" s="100"/>
-      <c r="AS2" s="100"/>
-      <c r="AV2" s="100"/>
-      <c r="AW2" s="100"/>
-      <c r="AX2" s="100"/>
+      <c r="AM2" s="112"/>
+      <c r="AP2" s="112"/>
+      <c r="AQ2" s="112"/>
+      <c r="AR2" s="112"/>
+      <c r="AS2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="112"/>
+      <c r="AX2" s="112"/>
     </row>
     <row r="3" spans="1:61">
       <c r="A3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="100">
+      <c r="B3" s="112">
         <v>2</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="100">
+      <c r="D3" s="112">
         <v>1</v>
       </c>
       <c r="E3" s="76" t="s">
@@ -1890,13 +1890,13 @@
       <c r="J3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="100">
+      <c r="K3" s="112">
         <v>1</v>
       </c>
-      <c r="L3" s="105" t="s">
+      <c r="L3" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="100">
+      <c r="M3" s="112">
         <v>2</v>
       </c>
       <c r="N3" s="76" t="s">
@@ -1916,13 +1916,13 @@
       <c r="S3" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="100">
+      <c r="T3" s="112">
         <v>2</v>
       </c>
-      <c r="U3" s="108" t="s">
+      <c r="U3" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="100">
+      <c r="V3" s="112">
         <v>2</v>
       </c>
       <c r="W3" s="29" t="s">
@@ -1946,15 +1946,15 @@
         <f t="shared" ref="AC3:AC5" si="0">INDEX($AC$80:$AC$83, MATCH(LARGE($AG$80:$AG$83, AB3), $AG$80:$AG$83, 0))</f>
         <v>África do Sul</v>
       </c>
-      <c r="AD3" s="105">
+      <c r="AD3" s="102">
         <f t="shared" ref="AD3:AD5" si="1">VLOOKUP(AC3, $AC$80:$AF$83, 2, 0)</f>
         <v>4</v>
       </c>
-      <c r="AE3" s="105">
+      <c r="AE3" s="102">
         <f t="shared" ref="AE3:AE5" si="2">VLOOKUP(AC3, $AC$80:$AF$83, 3, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="105">
+      <c r="AF3" s="102">
         <f t="shared" ref="AF3:AF5" si="3">VLOOKUP(AC3, $AC$80:$AF$83, 4, 0)</f>
         <v>4</v>
       </c>
@@ -1965,26 +1965,26 @@
         <f>INDEX($AI$80:$AI$83, MATCH(LARGE($AM$80:$AM$83, AH3), $AM$80:$AM$83, 0))</f>
         <v>Catar</v>
       </c>
-      <c r="AJ3" s="108">
+      <c r="AJ3" s="103">
         <f t="shared" ref="AJ3:AJ5" si="4">VLOOKUP(AI3, $AI$80:$AL$83, 2, 0)</f>
         <v>4</v>
       </c>
-      <c r="AK3" s="108">
+      <c r="AK3" s="103">
         <f t="shared" ref="AK3:AK5" si="5">VLOOKUP(AI3, $AI$80:$AL$83, 3, 0)</f>
         <v>-1</v>
       </c>
-      <c r="AL3" s="108">
+      <c r="AL3" s="103">
         <f t="shared" ref="AL3:AL5" si="6">VLOOKUP(AI3, $AI$80:$AL$83, 4, 0)</f>
         <v>5</v>
       </c>
-      <c r="AM3" s="100"/>
-      <c r="AP3" s="100"/>
-      <c r="AQ3" s="100"/>
-      <c r="AR3" s="100"/>
-      <c r="AS3" s="100"/>
-      <c r="AV3" s="100"/>
-      <c r="AW3" s="100"/>
-      <c r="AX3" s="100"/>
+      <c r="AM3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
     </row>
     <row r="4" spans="1:61">
       <c r="A4" s="122" t="s">
@@ -1998,24 +1998,24 @@
         <v>46184</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="J4" s="123" t="s">
+      <c r="J4" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="123"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
       <c r="O4" s="10">
         <v>46191</v>
       </c>
       <c r="P4" s="3"/>
-      <c r="S4" s="123" t="s">
+      <c r="S4" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="123"/>
-      <c r="U4" s="123"/>
-      <c r="V4" s="123"/>
-      <c r="W4" s="123"/>
+      <c r="T4" s="125"/>
+      <c r="U4" s="125"/>
+      <c r="V4" s="125"/>
+      <c r="W4" s="125"/>
       <c r="X4" s="10">
         <v>46197</v>
       </c>
@@ -2026,15 +2026,15 @@
         <f>INDEX($AC$80:$AC$83, MATCH(LARGE($AG$80:$AG$83, AB4), $AG$80:$AG$83, 0))</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="AD4" s="105">
+      <c r="AD4" s="102">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AE4" s="105">
+      <c r="AE4" s="102">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="AF4" s="105">
+      <c r="AF4" s="102">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -2045,38 +2045,38 @@
         <f t="shared" ref="AI3:AI5" si="7">INDEX($AI$80:$AI$83, MATCH(LARGE($AM$80:$AM$83, AH4), $AM$80:$AM$83, 0))</f>
         <v>Canadá</v>
       </c>
-      <c r="AJ4" s="108">
+      <c r="AJ4" s="103">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AK4" s="108">
+      <c r="AK4" s="103">
         <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="AL4" s="108">
+      <c r="AL4" s="103">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="AM4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="100"/>
-      <c r="AR4" s="100"/>
-      <c r="AS4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="100"/>
+      <c r="AM4" s="112"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="112"/>
+      <c r="AS4" s="112"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
     </row>
     <row r="5" spans="1:61">
       <c r="A5" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="100">
+      <c r="B5" s="112">
         <v>0</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="100">
+      <c r="D5" s="112">
         <v>0</v>
       </c>
       <c r="E5" s="76" t="s">
@@ -2096,13 +2096,13 @@
       <c r="J5" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="100">
+      <c r="K5" s="112">
         <v>2</v>
       </c>
-      <c r="L5" s="108" t="s">
+      <c r="L5" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="100">
+      <c r="M5" s="112">
         <v>0</v>
       </c>
       <c r="N5" s="29" t="s">
@@ -2122,13 +2122,13 @@
       <c r="S5" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="T5" s="100">
+      <c r="T5" s="112">
         <v>3</v>
       </c>
-      <c r="U5" s="108" t="s">
+      <c r="U5" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="100">
+      <c r="V5" s="112">
         <v>3</v>
       </c>
       <c r="W5" s="29" t="s">
@@ -2152,15 +2152,15 @@
         <f t="shared" si="0"/>
         <v>Tchéquia</v>
       </c>
-      <c r="AD5" s="105">
+      <c r="AD5" s="102">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AE5" s="105">
+      <c r="AE5" s="102">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="AF5" s="105">
+      <c r="AF5" s="102">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -2171,86 +2171,86 @@
         <f t="shared" si="7"/>
         <v>Bósnia e H.</v>
       </c>
-      <c r="AJ5" s="108">
+      <c r="AJ5" s="103">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AK5" s="108">
+      <c r="AK5" s="103">
         <f t="shared" si="5"/>
         <v>-3</v>
       </c>
-      <c r="AL5" s="108">
+      <c r="AL5" s="103">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="AM5" s="100"/>
-      <c r="AP5" s="100"/>
-      <c r="AQ5" s="100"/>
-      <c r="AR5" s="100"/>
-      <c r="AS5" s="100"/>
-      <c r="AV5" s="100"/>
-      <c r="AW5" s="100"/>
-      <c r="AX5" s="100"/>
+      <c r="AM5" s="112"/>
+      <c r="AP5" s="112"/>
+      <c r="AQ5" s="112"/>
+      <c r="AR5" s="112"/>
+      <c r="AS5" s="112"/>
+      <c r="AV5" s="112"/>
+      <c r="AW5" s="112"/>
+      <c r="AX5" s="112"/>
     </row>
     <row r="6" spans="1:61">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
       <c r="F6" s="10">
         <v>46185</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="J6" s="123" t="s">
+      <c r="J6" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="123"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="123"/>
-      <c r="N6" s="123"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
       <c r="O6" s="10">
         <v>46191</v>
       </c>
       <c r="P6" s="3"/>
-      <c r="S6" s="125" t="s">
+      <c r="S6" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="T6" s="125"/>
-      <c r="U6" s="125"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="125"/>
+      <c r="T6" s="126"/>
+      <c r="U6" s="126"/>
+      <c r="V6" s="126"/>
+      <c r="W6" s="126"/>
       <c r="X6" s="10">
         <v>46197</v>
       </c>
-      <c r="AD6" s="100"/>
-      <c r="AE6" s="100"/>
-      <c r="AF6" s="100"/>
-      <c r="AJ6" s="100"/>
-      <c r="AK6" s="100"/>
-      <c r="AL6" s="100"/>
-      <c r="AM6" s="100"/>
-      <c r="AP6" s="100"/>
-      <c r="AQ6" s="100"/>
-      <c r="AR6" s="100"/>
-      <c r="AS6" s="100"/>
-      <c r="AV6" s="100"/>
-      <c r="AW6" s="100"/>
-      <c r="AX6" s="100"/>
+      <c r="AD6" s="112"/>
+      <c r="AE6" s="112"/>
+      <c r="AF6" s="112"/>
+      <c r="AJ6" s="112"/>
+      <c r="AK6" s="112"/>
+      <c r="AL6" s="112"/>
+      <c r="AM6" s="112"/>
+      <c r="AP6" s="112"/>
+      <c r="AQ6" s="112"/>
+      <c r="AR6" s="112"/>
+      <c r="AS6" s="112"/>
+      <c r="AV6" s="112"/>
+      <c r="AW6" s="112"/>
+      <c r="AX6" s="112"/>
     </row>
     <row r="7" spans="1:61">
       <c r="A7" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="100">
+      <c r="B7" s="112">
         <v>1</v>
       </c>
-      <c r="C7" s="108" t="s">
+      <c r="C7" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="100">
+      <c r="D7" s="112">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="s">
@@ -2270,13 +2270,13 @@
       <c r="J7" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="100">
+      <c r="K7" s="112">
         <v>0</v>
       </c>
-      <c r="L7" s="108" t="s">
+      <c r="L7" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="100">
+      <c r="M7" s="112">
         <v>2</v>
       </c>
       <c r="N7" s="29" t="s">
@@ -2296,13 +2296,13 @@
       <c r="S7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="T7" s="100">
+      <c r="T7" s="112">
         <v>2</v>
       </c>
-      <c r="U7" s="109" t="s">
+      <c r="U7" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="V7" s="100">
+      <c r="V7" s="112">
         <v>1</v>
       </c>
       <c r="W7" s="30" t="s">
@@ -2332,7 +2332,7 @@
       <c r="AF7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="100"/>
+      <c r="AG7" s="112"/>
       <c r="AH7" s="71"/>
       <c r="AI7" s="18" t="s">
         <v>33</v>
@@ -2346,23 +2346,23 @@
       <c r="AL7" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="AM7" s="100"/>
-      <c r="AP7" s="100"/>
-      <c r="AQ7" s="100"/>
-      <c r="AR7" s="100"/>
-      <c r="AS7" s="100"/>
-      <c r="AV7" s="100"/>
-      <c r="AW7" s="100"/>
-      <c r="AX7" s="100"/>
+      <c r="AM7" s="112"/>
+      <c r="AP7" s="112"/>
+      <c r="AQ7" s="112"/>
+      <c r="AR7" s="112"/>
+      <c r="AS7" s="112"/>
+      <c r="AV7" s="112"/>
+      <c r="AW7" s="112"/>
+      <c r="AX7" s="112"/>
     </row>
     <row r="8" spans="1:61">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
       <c r="F8" s="10">
         <v>46185</v>
       </c>
@@ -2378,13 +2378,13 @@
         <v>46191</v>
       </c>
       <c r="P8" s="3"/>
-      <c r="S8" s="125" t="s">
+      <c r="S8" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="T8" s="125"/>
-      <c r="U8" s="125"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
+      <c r="T8" s="126"/>
+      <c r="U8" s="126"/>
+      <c r="V8" s="126"/>
+      <c r="W8" s="126"/>
       <c r="X8" s="10">
         <v>46197</v>
       </c>
@@ -2395,19 +2395,19 @@
         <f>INDEX($AO$80:$AO$83, MATCH(LARGE($AS$80:$AS$83, AB8), $AS$80:$AS$83, 0))</f>
         <v>Brasil</v>
       </c>
-      <c r="AD8" s="109">
+      <c r="AD8" s="105">
         <f>VLOOKUP(AC8, $AO$80:$AR$83, 2, 0)</f>
         <v>9</v>
       </c>
-      <c r="AE8" s="109">
+      <c r="AE8" s="105">
         <f>VLOOKUP(AC8, $AO$80:$AR$83, 3, 0)</f>
         <v>8</v>
       </c>
-      <c r="AF8" s="109">
+      <c r="AF8" s="105">
         <f>VLOOKUP(AC8, $AO$80:$AR$83, 4, 0)</f>
         <v>10</v>
       </c>
-      <c r="AG8" s="100"/>
+      <c r="AG8" s="112"/>
       <c r="AH8" s="72">
         <v>1</v>
       </c>
@@ -2415,38 +2415,38 @@
         <f>INDEX($AU$80:$AU$83, MATCH(LARGE($AY$80:$AY$83, AH8), $AY$80:$AY$83, 0))</f>
         <v>Paraguai</v>
       </c>
-      <c r="AJ8" s="110">
+      <c r="AJ8" s="104">
         <f>VLOOKUP(AI8, $AU$80:$AX$83, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AK8" s="110">
+      <c r="AK8" s="104">
         <f>VLOOKUP(AI8, $AU$80:$AX$83, 3, 0)</f>
         <v>5</v>
       </c>
-      <c r="AL8" s="110">
+      <c r="AL8" s="104">
         <f>VLOOKUP(AI8, $AU$80:$AX$83, 4, 0)</f>
         <v>8</v>
       </c>
-      <c r="AM8" s="100"/>
-      <c r="AP8" s="100"/>
-      <c r="AQ8" s="100"/>
-      <c r="AR8" s="100"/>
-      <c r="AS8" s="100"/>
-      <c r="AV8" s="100"/>
-      <c r="AW8" s="100"/>
-      <c r="AX8" s="100"/>
+      <c r="AM8" s="112"/>
+      <c r="AP8" s="112"/>
+      <c r="AQ8" s="112"/>
+      <c r="AR8" s="112"/>
+      <c r="AS8" s="112"/>
+      <c r="AV8" s="112"/>
+      <c r="AW8" s="112"/>
+      <c r="AX8" s="112"/>
     </row>
     <row r="9" spans="1:61">
       <c r="A9" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="100">
+      <c r="B9" s="112">
         <v>1</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="100">
+      <c r="D9" s="112">
         <v>1</v>
       </c>
       <c r="E9" s="31" t="s">
@@ -2466,13 +2466,13 @@
       <c r="J9" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="112">
         <v>4</v>
       </c>
-      <c r="L9" s="105" t="s">
+      <c r="L9" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="112">
         <v>0</v>
       </c>
       <c r="N9" s="76" t="s">
@@ -2492,13 +2492,13 @@
       <c r="S9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="T9" s="100">
+      <c r="T9" s="112">
         <v>2</v>
       </c>
-      <c r="U9" s="109" t="s">
+      <c r="U9" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="V9" s="100">
+      <c r="V9" s="112">
         <v>3</v>
       </c>
       <c r="W9" s="30" t="s">
@@ -2522,19 +2522,19 @@
         <f>INDEX($AO$80:$AO$83, MATCH(LARGE($AS$80:$AS$83, AB9), $AS$80:$AS$83, 0))</f>
         <v>Marrocos</v>
       </c>
-      <c r="AD9" s="109">
+      <c r="AD9" s="105">
         <f t="shared" ref="AD9:AD11" si="26">VLOOKUP(AC9, $AO$80:$AR$83, 2, 0)</f>
         <v>6</v>
       </c>
-      <c r="AE9" s="109">
+      <c r="AE9" s="105">
         <f t="shared" ref="AE9:AE11" si="27">VLOOKUP(AC9, $AO$80:$AR$83, 3, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="109">
+      <c r="AF9" s="105">
         <f t="shared" ref="AF9:AF11" si="28">VLOOKUP(AC9, $AO$80:$AR$83, 4, 0)</f>
         <v>4</v>
       </c>
-      <c r="AG9" s="100"/>
+      <c r="AG9" s="112"/>
       <c r="AH9" s="72">
         <v>2</v>
       </c>
@@ -2542,46 +2542,46 @@
         <f t="shared" ref="AI9:AI11" si="29">INDEX($AU$80:$AU$83, MATCH(LARGE($AY$80:$AY$83, AH9), $AY$80:$AY$83, 0))</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="AJ9" s="110">
+      <c r="AJ9" s="104">
         <f t="shared" ref="AJ9:AJ11" si="30">VLOOKUP(AI9, $AU$80:$AX$83, 2, 0)</f>
         <v>5</v>
       </c>
-      <c r="AK9" s="110">
+      <c r="AK9" s="104">
         <f t="shared" ref="AK9:AK11" si="31">VLOOKUP(AI9, $AU$80:$AX$83, 3, 0)</f>
         <v>1</v>
       </c>
-      <c r="AL9" s="110">
+      <c r="AL9" s="104">
         <f t="shared" ref="AL9:AL11" si="32">VLOOKUP(AI9, $AU$80:$AX$83, 4, 0)</f>
         <v>5</v>
       </c>
-      <c r="AM9" s="100"/>
-      <c r="AP9" s="100"/>
-      <c r="AQ9" s="100"/>
-      <c r="AR9" s="100"/>
-      <c r="AS9" s="100"/>
-      <c r="AV9" s="100"/>
-      <c r="AW9" s="100"/>
-      <c r="AX9" s="100"/>
+      <c r="AM9" s="112"/>
+      <c r="AP9" s="112"/>
+      <c r="AQ9" s="112"/>
+      <c r="AR9" s="112"/>
+      <c r="AS9" s="112"/>
+      <c r="AV9" s="112"/>
+      <c r="AW9" s="112"/>
+      <c r="AX9" s="112"/>
     </row>
     <row r="10" spans="1:61">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="123"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
       <c r="F10" s="10">
         <v>46186</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="J10" s="124" t="s">
+      <c r="J10" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="127"/>
       <c r="O10" s="10">
         <v>46192</v>
       </c>
@@ -2603,19 +2603,19 @@
         <f t="shared" ref="AC9:AC11" si="33">INDEX($AO$80:$AO$83, MATCH(LARGE($AS$80:$AS$83, AB10), $AS$80:$AS$83, 0))</f>
         <v>Escócia</v>
       </c>
-      <c r="AD10" s="109">
+      <c r="AD10" s="105">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="AE10" s="109">
+      <c r="AE10" s="105">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="109">
+        <v>2</v>
+      </c>
+      <c r="AF10" s="105">
         <f t="shared" si="28"/>
-        <v>5</v>
-      </c>
-      <c r="AG10" s="100"/>
+        <v>7</v>
+      </c>
+      <c r="AG10" s="112"/>
       <c r="AH10" s="72">
         <v>3</v>
       </c>
@@ -2623,38 +2623,38 @@
         <f t="shared" si="29"/>
         <v>Austrália</v>
       </c>
-      <c r="AJ10" s="110">
+      <c r="AJ10" s="104">
         <f t="shared" si="30"/>
         <v>2</v>
       </c>
-      <c r="AK10" s="110">
+      <c r="AK10" s="104">
         <f t="shared" si="31"/>
         <v>-3</v>
       </c>
-      <c r="AL10" s="110">
+      <c r="AL10" s="104">
         <f t="shared" si="32"/>
         <v>5</v>
       </c>
-      <c r="AM10" s="100"/>
-      <c r="AP10" s="100"/>
-      <c r="AQ10" s="100"/>
-      <c r="AR10" s="100"/>
-      <c r="AS10" s="100"/>
-      <c r="AV10" s="100"/>
-      <c r="AW10" s="100"/>
-      <c r="AX10" s="100"/>
+      <c r="AM10" s="112"/>
+      <c r="AP10" s="112"/>
+      <c r="AQ10" s="112"/>
+      <c r="AR10" s="112"/>
+      <c r="AS10" s="112"/>
+      <c r="AV10" s="112"/>
+      <c r="AW10" s="112"/>
+      <c r="AX10" s="112"/>
     </row>
     <row r="11" spans="1:61">
       <c r="A11" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="100">
+      <c r="B11" s="112">
         <v>0</v>
       </c>
-      <c r="C11" s="108" t="s">
+      <c r="C11" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="100">
+      <c r="D11" s="112">
         <v>3</v>
       </c>
       <c r="E11" s="29" t="s">
@@ -2674,13 +2674,13 @@
       <c r="J11" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="100">
+      <c r="K11" s="112">
         <v>2</v>
       </c>
-      <c r="L11" s="110" t="s">
+      <c r="L11" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="100">
+      <c r="M11" s="112">
         <v>2</v>
       </c>
       <c r="N11" s="31" t="s">
@@ -2700,13 +2700,13 @@
       <c r="S11" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="T11" s="100">
+      <c r="T11" s="112">
         <v>1</v>
       </c>
-      <c r="U11" s="105" t="s">
+      <c r="U11" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="V11" s="100">
+      <c r="V11" s="112">
         <v>1</v>
       </c>
       <c r="W11" s="76" t="s">
@@ -2730,19 +2730,19 @@
         <f t="shared" si="33"/>
         <v>Haiti</v>
       </c>
-      <c r="AD11" s="109">
+      <c r="AD11" s="105">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AE11" s="109">
+      <c r="AE11" s="105">
         <f t="shared" si="27"/>
         <v>-10</v>
       </c>
-      <c r="AF11" s="109">
+      <c r="AF11" s="105">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="AG11" s="100"/>
+      <c r="AG11" s="112"/>
       <c r="AH11" s="72">
         <v>4</v>
       </c>
@@ -2750,46 +2750,46 @@
         <f t="shared" si="29"/>
         <v>Turquia</v>
       </c>
-      <c r="AJ11" s="110">
+      <c r="AJ11" s="104">
         <f t="shared" si="30"/>
         <v>1</v>
       </c>
-      <c r="AK11" s="110">
+      <c r="AK11" s="104">
         <f t="shared" si="31"/>
         <v>-3</v>
       </c>
-      <c r="AL11" s="110">
+      <c r="AL11" s="104">
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="AM11" s="100"/>
-      <c r="AP11" s="100"/>
-      <c r="AQ11" s="100"/>
-      <c r="AR11" s="100"/>
-      <c r="AS11" s="100"/>
-      <c r="AV11" s="100"/>
-      <c r="AW11" s="100"/>
-      <c r="AX11" s="100"/>
+      <c r="AM11" s="112"/>
+      <c r="AP11" s="112"/>
+      <c r="AQ11" s="112"/>
+      <c r="AR11" s="112"/>
+      <c r="AS11" s="112"/>
+      <c r="AV11" s="112"/>
+      <c r="AW11" s="112"/>
+      <c r="AX11" s="112"/>
     </row>
     <row r="12" spans="1:61">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
       <c r="F12" s="10">
         <v>46186</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="J12" s="125" t="s">
+      <c r="J12" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="125"/>
-      <c r="L12" s="125"/>
-      <c r="M12" s="125"/>
-      <c r="N12" s="125"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="126"/>
       <c r="O12" s="10">
         <v>46192</v>
       </c>
@@ -2804,32 +2804,32 @@
       <c r="X12" s="10">
         <v>46197</v>
       </c>
-      <c r="AD12" s="100"/>
-      <c r="AE12" s="100"/>
-      <c r="AF12" s="100"/>
-      <c r="AJ12" s="100"/>
-      <c r="AK12" s="100"/>
-      <c r="AL12" s="100"/>
-      <c r="AM12" s="100"/>
-      <c r="AP12" s="100"/>
-      <c r="AQ12" s="100"/>
-      <c r="AR12" s="100"/>
-      <c r="AS12" s="100"/>
-      <c r="AV12" s="100"/>
-      <c r="AW12" s="100"/>
-      <c r="AX12" s="100"/>
+      <c r="AD12" s="112"/>
+      <c r="AE12" s="112"/>
+      <c r="AF12" s="112"/>
+      <c r="AJ12" s="112"/>
+      <c r="AK12" s="112"/>
+      <c r="AL12" s="112"/>
+      <c r="AM12" s="112"/>
+      <c r="AP12" s="112"/>
+      <c r="AQ12" s="112"/>
+      <c r="AR12" s="112"/>
+      <c r="AS12" s="112"/>
+      <c r="AV12" s="112"/>
+      <c r="AW12" s="112"/>
+      <c r="AX12" s="112"/>
     </row>
     <row r="13" spans="1:61">
       <c r="A13" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="100">
+      <c r="B13" s="112">
         <v>2</v>
       </c>
-      <c r="C13" s="109" t="s">
+      <c r="C13" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="100">
+      <c r="D13" s="112">
         <v>0</v>
       </c>
       <c r="E13" s="30" t="s">
@@ -2849,13 +2849,13 @@
       <c r="J13" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="100">
+      <c r="K13" s="112">
         <v>1</v>
       </c>
-      <c r="L13" s="109" t="s">
+      <c r="L13" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="100">
+      <c r="M13" s="112">
         <v>2</v>
       </c>
       <c r="N13" s="30" t="s">
@@ -2875,13 +2875,13 @@
       <c r="S13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="T13" s="100">
+      <c r="T13" s="112">
         <v>0</v>
       </c>
-      <c r="U13" s="105" t="s">
+      <c r="U13" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="V13" s="100">
+      <c r="V13" s="112">
         <v>3</v>
       </c>
       <c r="W13" s="76" t="s">
@@ -2924,45 +2924,45 @@
       <c r="AL13" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="AM13" s="100"/>
-      <c r="AP13" s="100"/>
-      <c r="AQ13" s="100"/>
-      <c r="AR13" s="100"/>
-      <c r="AS13" s="100"/>
-      <c r="AV13" s="100"/>
-      <c r="AW13" s="100"/>
-      <c r="AX13" s="100"/>
+      <c r="AM13" s="112"/>
+      <c r="AP13" s="112"/>
+      <c r="AQ13" s="112"/>
+      <c r="AR13" s="112"/>
+      <c r="AS13" s="112"/>
+      <c r="AV13" s="112"/>
+      <c r="AW13" s="112"/>
+      <c r="AX13" s="112"/>
     </row>
     <row r="14" spans="1:61">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
       <c r="F14" s="10">
         <v>46186</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="J14" s="125" t="s">
+      <c r="J14" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="126"/>
       <c r="O14" s="10">
         <v>46192</v>
       </c>
       <c r="P14" s="3"/>
-      <c r="S14" s="126" t="s">
+      <c r="S14" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="T14" s="126"/>
-      <c r="U14" s="126"/>
-      <c r="V14" s="126"/>
-      <c r="W14" s="126"/>
+      <c r="T14" s="123"/>
+      <c r="U14" s="123"/>
+      <c r="V14" s="123"/>
+      <c r="W14" s="123"/>
       <c r="X14" s="10">
         <v>46198</v>
       </c>
@@ -3004,26 +3004,26 @@
         <f>VLOOKUP(AI14, $AI$86:$AL$89, 4, 0)</f>
         <v>6</v>
       </c>
-      <c r="AM14" s="100"/>
-      <c r="AP14" s="100"/>
-      <c r="AQ14" s="100"/>
-      <c r="AR14" s="100"/>
-      <c r="AS14" s="100"/>
-      <c r="AV14" s="100"/>
-      <c r="AW14" s="100"/>
-      <c r="AX14" s="100"/>
+      <c r="AM14" s="112"/>
+      <c r="AP14" s="112"/>
+      <c r="AQ14" s="112"/>
+      <c r="AR14" s="112"/>
+      <c r="AS14" s="112"/>
+      <c r="AV14" s="112"/>
+      <c r="AW14" s="112"/>
+      <c r="AX14" s="112"/>
     </row>
     <row r="15" spans="1:61">
       <c r="A15" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="100">
+      <c r="B15" s="112">
         <v>0</v>
       </c>
-      <c r="C15" s="109" t="s">
+      <c r="C15" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="100">
+      <c r="D15" s="112">
         <v>4</v>
       </c>
       <c r="E15" s="30" t="s">
@@ -3043,13 +3043,13 @@
       <c r="J15" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="100">
+      <c r="K15" s="112">
         <v>5</v>
       </c>
-      <c r="L15" s="109" t="s">
+      <c r="L15" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="100">
+      <c r="M15" s="112">
         <v>0</v>
       </c>
       <c r="N15" s="30" t="s">
@@ -3069,13 +3069,13 @@
       <c r="S15" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="T15" s="100">
+      <c r="T15" s="112">
         <v>0</v>
       </c>
       <c r="U15" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="V15" s="100">
+      <c r="V15" s="112">
         <v>3</v>
       </c>
       <c r="W15" s="32" t="s">
@@ -3130,45 +3130,45 @@
         <f t="shared" ref="AL15:AL17" si="59">VLOOKUP(AI15, $AI$86:$AL$89, 4, 0)</f>
         <v>4</v>
       </c>
-      <c r="AM15" s="100"/>
-      <c r="AP15" s="100"/>
-      <c r="AQ15" s="100"/>
-      <c r="AR15" s="100"/>
-      <c r="AS15" s="100"/>
-      <c r="AV15" s="100"/>
-      <c r="AW15" s="100"/>
-      <c r="AX15" s="100"/>
+      <c r="AM15" s="112"/>
+      <c r="AP15" s="112"/>
+      <c r="AQ15" s="112"/>
+      <c r="AR15" s="112"/>
+      <c r="AS15" s="112"/>
+      <c r="AV15" s="112"/>
+      <c r="AW15" s="112"/>
+      <c r="AX15" s="112"/>
     </row>
     <row r="16" spans="1:61">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
       <c r="F16" s="10">
         <v>46187</v>
       </c>
       <c r="G16" s="3"/>
-      <c r="J16" s="124" t="s">
+      <c r="J16" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="127"/>
       <c r="O16" s="10">
         <v>46193</v>
       </c>
       <c r="P16" s="3"/>
-      <c r="S16" s="126" t="s">
+      <c r="S16" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="T16" s="126"/>
-      <c r="U16" s="126"/>
-      <c r="V16" s="126"/>
-      <c r="W16" s="126"/>
+      <c r="T16" s="123"/>
+      <c r="U16" s="123"/>
+      <c r="V16" s="123"/>
+      <c r="W16" s="123"/>
       <c r="X16" s="10">
         <v>46198</v>
       </c>
@@ -3210,26 +3210,26 @@
         <f t="shared" si="59"/>
         <v>4</v>
       </c>
-      <c r="AM16" s="100"/>
-      <c r="AP16" s="100"/>
-      <c r="AQ16" s="100"/>
-      <c r="AR16" s="100"/>
-      <c r="AS16" s="100"/>
-      <c r="AV16" s="100"/>
-      <c r="AW16" s="100"/>
-      <c r="AX16" s="100"/>
+      <c r="AM16" s="112"/>
+      <c r="AP16" s="112"/>
+      <c r="AQ16" s="112"/>
+      <c r="AR16" s="112"/>
+      <c r="AS16" s="112"/>
+      <c r="AV16" s="112"/>
+      <c r="AW16" s="112"/>
+      <c r="AX16" s="112"/>
     </row>
     <row r="17" spans="1:50">
       <c r="A17" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="100">
+      <c r="B17" s="112">
         <v>2</v>
       </c>
-      <c r="C17" s="110" t="s">
+      <c r="C17" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="100">
+      <c r="D17" s="112">
         <v>2</v>
       </c>
       <c r="E17" s="31" t="s">
@@ -3249,13 +3249,13 @@
       <c r="J17" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="100">
+      <c r="K17" s="112">
         <v>1</v>
       </c>
-      <c r="L17" s="110" t="s">
+      <c r="L17" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="100">
+      <c r="M17" s="112">
         <v>3</v>
       </c>
       <c r="N17" s="31" t="s">
@@ -3275,13 +3275,13 @@
       <c r="S17" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="T17" s="100">
+      <c r="T17" s="112">
         <v>2</v>
       </c>
       <c r="U17" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="V17" s="100">
+      <c r="V17" s="112">
         <v>2</v>
       </c>
       <c r="W17" s="32" t="s">
@@ -3336,74 +3336,74 @@
         <f t="shared" si="59"/>
         <v>1</v>
       </c>
-      <c r="AM17" s="100"/>
-      <c r="AP17" s="100"/>
-      <c r="AQ17" s="100"/>
-      <c r="AR17" s="100"/>
-      <c r="AS17" s="100"/>
-      <c r="AV17" s="100"/>
-      <c r="AW17" s="100"/>
-      <c r="AX17" s="100"/>
+      <c r="AM17" s="112"/>
+      <c r="AP17" s="112"/>
+      <c r="AQ17" s="112"/>
+      <c r="AR17" s="112"/>
+      <c r="AS17" s="112"/>
+      <c r="AV17" s="112"/>
+      <c r="AW17" s="112"/>
+      <c r="AX17" s="112"/>
     </row>
     <row r="18" spans="1:50">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="126"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
       <c r="F18" s="10">
         <v>46187</v>
       </c>
       <c r="G18" s="3"/>
-      <c r="J18" s="127" t="s">
+      <c r="J18" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="124"/>
       <c r="O18" s="10">
         <v>46193</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="S18" s="127" t="s">
+      <c r="S18" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="T18" s="127"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="127"/>
-      <c r="W18" s="127"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="124"/>
+      <c r="W18" s="124"/>
       <c r="X18" s="10">
         <v>46198</v>
       </c>
-      <c r="AD18" s="100"/>
-      <c r="AE18" s="100"/>
-      <c r="AF18" s="100"/>
-      <c r="AJ18" s="100"/>
-      <c r="AK18" s="100"/>
-      <c r="AL18" s="100"/>
-      <c r="AM18" s="100"/>
-      <c r="AP18" s="100"/>
-      <c r="AQ18" s="100"/>
-      <c r="AR18" s="100"/>
-      <c r="AS18" s="100"/>
-      <c r="AV18" s="100"/>
-      <c r="AW18" s="100"/>
-      <c r="AX18" s="100"/>
+      <c r="AD18" s="112"/>
+      <c r="AE18" s="112"/>
+      <c r="AF18" s="112"/>
+      <c r="AJ18" s="112"/>
+      <c r="AK18" s="112"/>
+      <c r="AL18" s="112"/>
+      <c r="AM18" s="112"/>
+      <c r="AP18" s="112"/>
+      <c r="AQ18" s="112"/>
+      <c r="AR18" s="112"/>
+      <c r="AS18" s="112"/>
+      <c r="AV18" s="112"/>
+      <c r="AW18" s="112"/>
+      <c r="AX18" s="112"/>
     </row>
     <row r="19" spans="1:50">
       <c r="A19" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="100">
+      <c r="B19" s="112">
         <v>6</v>
       </c>
       <c r="C19" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="100">
+      <c r="D19" s="112">
         <v>0</v>
       </c>
       <c r="E19" s="32" t="s">
@@ -3423,13 +3423,13 @@
       <c r="J19" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="100">
+      <c r="K19" s="112">
         <v>2</v>
       </c>
       <c r="L19" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="100">
+      <c r="M19" s="112">
         <v>2</v>
       </c>
       <c r="N19" s="33" t="s">
@@ -3449,13 +3449,13 @@
       <c r="S19" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="T19" s="100">
+      <c r="T19" s="112">
         <v>0</v>
       </c>
       <c r="U19" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="V19" s="100">
+      <c r="V19" s="112">
         <v>1</v>
       </c>
       <c r="W19" s="33" t="s">
@@ -3485,7 +3485,7 @@
       <c r="AF19" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AG19" s="100"/>
+      <c r="AG19" s="112"/>
       <c r="AH19" s="65"/>
       <c r="AI19" s="25" t="s">
         <v>75</v>
@@ -3499,45 +3499,45 @@
       <c r="AL19" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="AM19" s="100"/>
-      <c r="AP19" s="100"/>
-      <c r="AQ19" s="100"/>
-      <c r="AR19" s="100"/>
-      <c r="AS19" s="100"/>
-      <c r="AV19" s="100"/>
-      <c r="AW19" s="100"/>
-      <c r="AX19" s="100"/>
+      <c r="AM19" s="112"/>
+      <c r="AP19" s="112"/>
+      <c r="AQ19" s="112"/>
+      <c r="AR19" s="112"/>
+      <c r="AS19" s="112"/>
+      <c r="AV19" s="112"/>
+      <c r="AW19" s="112"/>
+      <c r="AX19" s="112"/>
     </row>
     <row r="20" spans="1:50">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
       <c r="F20" s="10">
         <v>46187</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="J20" s="126" t="s">
+      <c r="J20" s="123" t="s">
         <v>77</v>
       </c>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
       <c r="O20" s="10">
         <v>46193</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="S20" s="127" t="s">
+      <c r="S20" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="T20" s="127"/>
-      <c r="U20" s="127"/>
-      <c r="V20" s="127"/>
-      <c r="W20" s="127"/>
+      <c r="T20" s="124"/>
+      <c r="U20" s="124"/>
+      <c r="V20" s="124"/>
+      <c r="W20" s="124"/>
       <c r="X20" s="10">
         <v>46198</v>
       </c>
@@ -3548,19 +3548,19 @@
         <f>INDEX($AO$86:$AO$89, MATCH(LARGE($AS$86:$AS$89, AB20), $AS$86:$AS$89, 0))</f>
         <v>Bélgica</v>
       </c>
-      <c r="AD20" s="103">
+      <c r="AD20" s="108">
         <f>VLOOKUP(AC20, $AO$86:$AR$89, 2, 0)</f>
         <v>9</v>
       </c>
-      <c r="AE20" s="103">
+      <c r="AE20" s="108">
         <f>VLOOKUP(AC20, $AO$86:$AR$89, 3, 0)</f>
         <v>7</v>
       </c>
-      <c r="AF20" s="103">
+      <c r="AF20" s="108">
         <f>VLOOKUP(AC20, $AO$86:$AR$89, 4, 0)</f>
         <v>8</v>
       </c>
-      <c r="AG20" s="100"/>
+      <c r="AG20" s="112"/>
       <c r="AH20" s="64">
         <v>1</v>
       </c>
@@ -3568,38 +3568,38 @@
         <f>INDEX($AU$86:$AU$89, MATCH(LARGE($AY$86:$AY$89, AH20), $AY$86:$AY$89, 0))</f>
         <v>Espanha</v>
       </c>
-      <c r="AJ20" s="102">
+      <c r="AJ20" s="115">
         <f>VLOOKUP(AI20, $AU$86:$AX$89, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AK20" s="102">
+      <c r="AK20" s="115">
         <f>VLOOKUP(AI20, $AU$86:$AX$89, 3, 0)</f>
         <v>4</v>
       </c>
-      <c r="AL20" s="102">
+      <c r="AL20" s="115">
         <f>VLOOKUP(AI20, $AU$86:$AX$89, 4, 0)</f>
         <v>6</v>
       </c>
-      <c r="AM20" s="100"/>
-      <c r="AP20" s="100"/>
-      <c r="AQ20" s="100"/>
-      <c r="AR20" s="100"/>
-      <c r="AS20" s="100"/>
-      <c r="AV20" s="100"/>
-      <c r="AW20" s="100"/>
-      <c r="AX20" s="100"/>
+      <c r="AM20" s="112"/>
+      <c r="AP20" s="112"/>
+      <c r="AQ20" s="112"/>
+      <c r="AR20" s="112"/>
+      <c r="AS20" s="112"/>
+      <c r="AV20" s="112"/>
+      <c r="AW20" s="112"/>
+      <c r="AX20" s="112"/>
     </row>
     <row r="21" spans="1:50">
       <c r="A21" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="100">
+      <c r="B21" s="112">
         <v>1</v>
       </c>
       <c r="C21" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="100">
+      <c r="D21" s="112">
         <v>1</v>
       </c>
       <c r="E21" s="33" t="s">
@@ -3619,13 +3619,13 @@
       <c r="J21" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="K21" s="100">
+      <c r="K21" s="112">
         <v>3</v>
       </c>
       <c r="L21" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="100">
+      <c r="M21" s="112">
         <v>1</v>
       </c>
       <c r="N21" s="32" t="s">
@@ -3645,13 +3645,13 @@
       <c r="S21" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T21" s="100">
+      <c r="T21" s="112">
         <v>3</v>
       </c>
       <c r="U21" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="V21" s="100">
+      <c r="V21" s="112">
         <v>1</v>
       </c>
       <c r="W21" s="33" t="s">
@@ -3675,19 +3675,19 @@
         <f t="shared" ref="AC21:AC23" si="78">INDEX($AO$86:$AO$89, MATCH(LARGE($AS$86:$AS$89, AB21), $AS$86:$AS$89, 0))</f>
         <v>Egito</v>
       </c>
-      <c r="AD21" s="103">
+      <c r="AD21" s="108">
         <f t="shared" ref="AD21:AD23" si="79">VLOOKUP(AC21, $AO$86:$AR$89, 2, 0)</f>
         <v>6</v>
       </c>
-      <c r="AE21" s="103">
+      <c r="AE21" s="108">
         <f t="shared" ref="AE21:AE23" si="80">VLOOKUP(AC21, $AO$86:$AR$89, 3, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="103">
+      <c r="AF21" s="108">
         <f t="shared" ref="AF21:AF23" si="81">VLOOKUP(AC21, $AO$86:$AR$89, 4, 0)</f>
         <v>2</v>
       </c>
-      <c r="AG21" s="100"/>
+      <c r="AG21" s="112"/>
       <c r="AH21" s="64">
         <v>2</v>
       </c>
@@ -3695,57 +3695,57 @@
         <f t="shared" ref="AI21:AI23" si="82">INDEX($AU$86:$AU$89, MATCH(LARGE($AY$86:$AY$89, AH21), $AY$86:$AY$89, 0))</f>
         <v>Uruguai</v>
       </c>
-      <c r="AJ21" s="102">
+      <c r="AJ21" s="115">
         <f t="shared" ref="AJ21:AJ23" si="83">VLOOKUP(AI21, $AU$86:$AX$89, 2, 0)</f>
         <v>5</v>
       </c>
-      <c r="AK21" s="102">
+      <c r="AK21" s="115">
         <f t="shared" ref="AK21:AK23" si="84">VLOOKUP(AI21, $AU$86:$AX$89, 3, 0)</f>
         <v>3</v>
       </c>
-      <c r="AL21" s="102">
+      <c r="AL21" s="115">
         <f t="shared" ref="AL21:AL23" si="85">VLOOKUP(AI21, $AU$86:$AX$89, 4, 0)</f>
         <v>5</v>
       </c>
-      <c r="AM21" s="100"/>
-      <c r="AP21" s="100"/>
-      <c r="AQ21" s="100"/>
-      <c r="AR21" s="100"/>
-      <c r="AS21" s="100"/>
-      <c r="AV21" s="100"/>
-      <c r="AW21" s="100"/>
-      <c r="AX21" s="100"/>
+      <c r="AM21" s="112"/>
+      <c r="AP21" s="112"/>
+      <c r="AQ21" s="112"/>
+      <c r="AR21" s="112"/>
+      <c r="AS21" s="112"/>
+      <c r="AV21" s="112"/>
+      <c r="AW21" s="112"/>
+      <c r="AX21" s="112"/>
     </row>
     <row r="22" spans="1:50">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
       <c r="F22" s="10">
         <v>46187</v>
       </c>
       <c r="G22" s="3"/>
-      <c r="J22" s="126" t="s">
+      <c r="J22" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="123"/>
       <c r="O22" s="10">
         <v>46193</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="S22" s="124" t="s">
+      <c r="S22" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="T22" s="124"/>
-      <c r="U22" s="124"/>
-      <c r="V22" s="124"/>
-      <c r="W22" s="124"/>
+      <c r="T22" s="127"/>
+      <c r="U22" s="127"/>
+      <c r="V22" s="127"/>
+      <c r="W22" s="127"/>
       <c r="X22" s="10">
         <v>46198</v>
       </c>
@@ -3756,19 +3756,19 @@
         <f t="shared" si="78"/>
         <v>Irã</v>
       </c>
-      <c r="AD22" s="103">
+      <c r="AD22" s="108">
         <f t="shared" si="79"/>
         <v>1</v>
       </c>
-      <c r="AE22" s="103">
+      <c r="AE22" s="108">
         <f t="shared" si="80"/>
         <v>-3</v>
       </c>
-      <c r="AF22" s="103">
+      <c r="AF22" s="108">
         <f t="shared" si="81"/>
         <v>1</v>
       </c>
-      <c r="AG22" s="100"/>
+      <c r="AG22" s="112"/>
       <c r="AH22" s="64">
         <v>3</v>
       </c>
@@ -3776,38 +3776,38 @@
         <f t="shared" si="82"/>
         <v>Arábia Saudita</v>
       </c>
-      <c r="AJ22" s="102">
+      <c r="AJ22" s="115">
         <f t="shared" si="83"/>
         <v>4</v>
       </c>
-      <c r="AK22" s="102">
+      <c r="AK22" s="115">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
-      <c r="AL22" s="102">
+      <c r="AL22" s="115">
         <f t="shared" si="85"/>
         <v>5</v>
       </c>
-      <c r="AM22" s="100"/>
-      <c r="AP22" s="100"/>
-      <c r="AQ22" s="100"/>
-      <c r="AR22" s="100"/>
-      <c r="AS22" s="100"/>
-      <c r="AV22" s="100"/>
-      <c r="AW22" s="100"/>
-      <c r="AX22" s="100"/>
+      <c r="AM22" s="112"/>
+      <c r="AP22" s="112"/>
+      <c r="AQ22" s="112"/>
+      <c r="AR22" s="112"/>
+      <c r="AS22" s="112"/>
+      <c r="AV22" s="112"/>
+      <c r="AW22" s="112"/>
+      <c r="AX22" s="112"/>
     </row>
     <row r="23" spans="1:50">
       <c r="A23" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="100">
+      <c r="B23" s="112">
         <v>0</v>
       </c>
       <c r="C23" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="100">
+      <c r="D23" s="112">
         <v>2</v>
       </c>
       <c r="E23" s="32" t="s">
@@ -3827,13 +3827,13 @@
       <c r="J23" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="K23" s="100">
+      <c r="K23" s="112">
         <v>4</v>
       </c>
       <c r="L23" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="100">
+      <c r="M23" s="112">
         <v>0</v>
       </c>
       <c r="N23" s="32" t="s">
@@ -3853,13 +3853,13 @@
       <c r="S23" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="T23" s="100">
+      <c r="T23" s="112">
         <v>1</v>
       </c>
-      <c r="U23" s="110" t="s">
+      <c r="U23" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="V23" s="100">
+      <c r="V23" s="112">
         <v>2</v>
       </c>
       <c r="W23" s="31" t="s">
@@ -3883,19 +3883,19 @@
         <f t="shared" si="78"/>
         <v>Nova Zelândia</v>
       </c>
-      <c r="AD23" s="103">
+      <c r="AD23" s="108">
         <f t="shared" si="79"/>
         <v>1</v>
       </c>
-      <c r="AE23" s="103">
+      <c r="AE23" s="108">
         <f t="shared" si="80"/>
         <v>-4</v>
       </c>
-      <c r="AF23" s="103">
+      <c r="AF23" s="108">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="100"/>
+      <c r="AG23" s="112"/>
       <c r="AH23" s="64">
         <v>4</v>
       </c>
@@ -3903,86 +3903,86 @@
         <f t="shared" si="82"/>
         <v>Cabo Verde</v>
       </c>
-      <c r="AJ23" s="102">
+      <c r="AJ23" s="115">
         <f t="shared" si="83"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="102">
+      <c r="AK23" s="115">
         <f t="shared" si="84"/>
         <v>-9</v>
       </c>
-      <c r="AL23" s="102">
+      <c r="AL23" s="115">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="100"/>
-      <c r="AP23" s="100"/>
-      <c r="AQ23" s="100"/>
-      <c r="AR23" s="100"/>
-      <c r="AS23" s="100"/>
-      <c r="AV23" s="100"/>
-      <c r="AW23" s="100"/>
-      <c r="AX23" s="100"/>
+      <c r="AM23" s="112"/>
+      <c r="AP23" s="112"/>
+      <c r="AQ23" s="112"/>
+      <c r="AR23" s="112"/>
+      <c r="AS23" s="112"/>
+      <c r="AV23" s="112"/>
+      <c r="AW23" s="112"/>
+      <c r="AX23" s="112"/>
     </row>
     <row r="24" spans="1:50">
-      <c r="A24" s="127" t="s">
+      <c r="A24" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
       <c r="F24" s="10">
         <v>46187</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="J24" s="127" t="s">
+      <c r="J24" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="K24" s="127"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="127"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
       <c r="O24" s="10">
         <v>46194</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="S24" s="124" t="s">
+      <c r="S24" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
+      <c r="T24" s="127"/>
+      <c r="U24" s="127"/>
+      <c r="V24" s="127"/>
+      <c r="W24" s="127"/>
       <c r="X24" s="10">
         <v>46198</v>
       </c>
-      <c r="AD24" s="100"/>
-      <c r="AE24" s="100"/>
-      <c r="AF24" s="100"/>
-      <c r="AJ24" s="100"/>
-      <c r="AK24" s="100"/>
-      <c r="AL24" s="100"/>
-      <c r="AM24" s="100"/>
-      <c r="AP24" s="100"/>
-      <c r="AQ24" s="100"/>
-      <c r="AR24" s="100"/>
-      <c r="AS24" s="100"/>
-      <c r="AV24" s="100"/>
-      <c r="AW24" s="100"/>
-      <c r="AX24" s="100"/>
+      <c r="AD24" s="112"/>
+      <c r="AE24" s="112"/>
+      <c r="AF24" s="112"/>
+      <c r="AJ24" s="112"/>
+      <c r="AK24" s="112"/>
+      <c r="AL24" s="112"/>
+      <c r="AM24" s="112"/>
+      <c r="AP24" s="112"/>
+      <c r="AQ24" s="112"/>
+      <c r="AR24" s="112"/>
+      <c r="AS24" s="112"/>
+      <c r="AV24" s="112"/>
+      <c r="AW24" s="112"/>
+      <c r="AX24" s="112"/>
     </row>
     <row r="25" spans="1:50">
       <c r="A25" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="100">
+      <c r="B25" s="112">
         <v>1</v>
       </c>
       <c r="C25" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="100">
+      <c r="D25" s="112">
         <v>0</v>
       </c>
       <c r="E25" s="33" t="s">
@@ -4002,13 +4002,13 @@
       <c r="J25" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="K25" s="100">
+      <c r="K25" s="112">
         <v>1</v>
       </c>
       <c r="L25" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="100">
+      <c r="M25" s="112">
         <v>2</v>
       </c>
       <c r="N25" s="33" t="s">
@@ -4028,13 +4028,13 @@
       <c r="S25" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="T25" s="100">
+      <c r="T25" s="112">
         <v>4</v>
       </c>
-      <c r="U25" s="110" t="s">
+      <c r="U25" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="V25" s="100">
+      <c r="V25" s="112">
         <v>1</v>
       </c>
       <c r="W25" s="31" t="s">
@@ -4077,45 +4077,45 @@
       <c r="AL25" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="AM25" s="100"/>
-      <c r="AP25" s="100"/>
-      <c r="AQ25" s="100"/>
-      <c r="AR25" s="100"/>
-      <c r="AS25" s="100"/>
-      <c r="AV25" s="100"/>
-      <c r="AW25" s="100"/>
-      <c r="AX25" s="100"/>
+      <c r="AM25" s="112"/>
+      <c r="AP25" s="112"/>
+      <c r="AQ25" s="112"/>
+      <c r="AR25" s="112"/>
+      <c r="AS25" s="112"/>
+      <c r="AV25" s="112"/>
+      <c r="AW25" s="112"/>
+      <c r="AX25" s="112"/>
     </row>
     <row r="26" spans="1:50">
-      <c r="A26" s="135" t="s">
+      <c r="A26" s="119" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="135"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
       <c r="F26" s="10">
         <v>46188</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="J26" s="135" t="s">
+      <c r="J26" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="135"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
       <c r="O26" s="10">
         <v>46194</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="S26" s="120" t="s">
+      <c r="S26" s="130" t="s">
         <v>91</v>
       </c>
-      <c r="T26" s="120"/>
-      <c r="U26" s="120"/>
-      <c r="V26" s="120"/>
-      <c r="W26" s="120"/>
+      <c r="T26" s="130"/>
+      <c r="U26" s="130"/>
+      <c r="V26" s="130"/>
+      <c r="W26" s="130"/>
       <c r="X26" s="10">
         <v>46199</v>
       </c>
@@ -4126,15 +4126,15 @@
         <f>INDEX($AC$92:$AC$95, MATCH(LARGE($AG$92:$AG$95, AB26), $AG$92:$AG$95, 0))</f>
         <v>França</v>
       </c>
-      <c r="AD26" s="113">
+      <c r="AD26" s="100">
         <f>VLOOKUP(AC26, $AC$92:$AF$95, 2, 0)</f>
         <v>9</v>
       </c>
-      <c r="AE26" s="113">
+      <c r="AE26" s="100">
         <f>VLOOKUP(AC26, $AC$92:$AF$95, 3, 0)</f>
         <v>8</v>
       </c>
-      <c r="AF26" s="113">
+      <c r="AF26" s="100">
         <f>VLOOKUP(AC26, $AC$92:$AF$95, 4, 0)</f>
         <v>10</v>
       </c>
@@ -4145,38 +4145,38 @@
         <f>INDEX($AI$92:$AI$95, MATCH(LARGE($AM$92:$AM$95, AH26), $AM$92:$AM$95, 0))</f>
         <v>Argentina</v>
       </c>
-      <c r="AJ26" s="111">
+      <c r="AJ26" s="110">
         <f>VLOOKUP(AI26, $AI$92:$AL$95, 2, 0)</f>
         <v>9</v>
       </c>
-      <c r="AK26" s="111">
+      <c r="AK26" s="110">
         <f>VLOOKUP(AI26, $AI$92:$AL$95, 3, 0)</f>
         <v>8</v>
       </c>
-      <c r="AL26" s="111">
+      <c r="AL26" s="110">
         <f>VLOOKUP(AI26, $AI$92:$AL$95, 4, 0)</f>
         <v>9</v>
       </c>
-      <c r="AM26" s="100"/>
-      <c r="AP26" s="100"/>
-      <c r="AQ26" s="100"/>
-      <c r="AR26" s="100"/>
-      <c r="AS26" s="100"/>
-      <c r="AV26" s="100"/>
-      <c r="AW26" s="100"/>
-      <c r="AX26" s="100"/>
+      <c r="AM26" s="112"/>
+      <c r="AP26" s="112"/>
+      <c r="AQ26" s="112"/>
+      <c r="AR26" s="112"/>
+      <c r="AS26" s="112"/>
+      <c r="AV26" s="112"/>
+      <c r="AW26" s="112"/>
+      <c r="AX26" s="112"/>
     </row>
     <row r="27" spans="1:50">
       <c r="A27" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="100">
+      <c r="B27" s="112">
         <v>3</v>
       </c>
-      <c r="C27" s="102" t="s">
+      <c r="C27" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="100">
+      <c r="D27" s="112">
         <v>0</v>
       </c>
       <c r="E27" s="35" t="s">
@@ -4196,13 +4196,13 @@
       <c r="J27" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="100">
+      <c r="K27" s="112">
         <v>2</v>
       </c>
-      <c r="L27" s="102" t="s">
+      <c r="L27" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="100">
+      <c r="M27" s="112">
         <v>1</v>
       </c>
       <c r="N27" s="35" t="s">
@@ -4222,13 +4222,13 @@
       <c r="S27" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="T27" s="100">
+      <c r="T27" s="112">
         <v>1</v>
       </c>
-      <c r="U27" s="113" t="s">
+      <c r="U27" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="V27" s="100">
+      <c r="V27" s="112">
         <v>3</v>
       </c>
       <c r="W27" s="37" t="s">
@@ -4252,15 +4252,15 @@
         <f t="shared" ref="AC27:AC29" si="104">INDEX($AC$92:$AC$95, MATCH(LARGE($AG$92:$AG$95, AB27), $AG$92:$AG$95, 0))</f>
         <v>Noruega</v>
       </c>
-      <c r="AD27" s="113">
+      <c r="AD27" s="100">
         <f t="shared" ref="AD27:AD29" si="105">VLOOKUP(AC27, $AC$92:$AF$95, 2, 0)</f>
         <v>4</v>
       </c>
-      <c r="AE27" s="113">
+      <c r="AE27" s="100">
         <f t="shared" ref="AE27:AE29" si="106">VLOOKUP(AC27, $AC$92:$AF$95, 3, 0)</f>
         <v>1</v>
       </c>
-      <c r="AF27" s="113">
+      <c r="AF27" s="100">
         <f t="shared" ref="AF27:AF29" si="107">VLOOKUP(AC27, $AC$92:$AF$95, 4, 0)</f>
         <v>6</v>
       </c>
@@ -4271,57 +4271,57 @@
         <f t="shared" ref="AI27:AI29" si="108">INDEX($AI$92:$AI$95, MATCH(LARGE($AM$92:$AM$95, AH27), $AM$92:$AM$95, 0))</f>
         <v>Argélia</v>
       </c>
-      <c r="AJ27" s="111">
+      <c r="AJ27" s="110">
         <f t="shared" ref="AJ27:AJ29" si="109">VLOOKUP(AI27, $AI$92:$AL$95, 2, 0)</f>
         <v>6</v>
       </c>
-      <c r="AK27" s="111">
+      <c r="AK27" s="110">
         <f t="shared" ref="AK27:AK29" si="110">VLOOKUP(AI27, $AI$92:$AL$95, 3, 0)</f>
         <v>1</v>
       </c>
-      <c r="AL27" s="111">
+      <c r="AL27" s="110">
         <f t="shared" ref="AL27:AL29" si="111">VLOOKUP(AI27, $AI$92:$AL$95, 4, 0)</f>
         <v>4</v>
       </c>
-      <c r="AM27" s="100"/>
-      <c r="AP27" s="100"/>
-      <c r="AQ27" s="100"/>
-      <c r="AR27" s="100"/>
-      <c r="AS27" s="100"/>
-      <c r="AV27" s="100"/>
-      <c r="AW27" s="100"/>
-      <c r="AX27" s="100"/>
+      <c r="AM27" s="112"/>
+      <c r="AP27" s="112"/>
+      <c r="AQ27" s="112"/>
+      <c r="AR27" s="112"/>
+      <c r="AS27" s="112"/>
+      <c r="AV27" s="112"/>
+      <c r="AW27" s="112"/>
+      <c r="AX27" s="112"/>
     </row>
     <row r="28" spans="1:50">
-      <c r="A28" s="128" t="s">
+      <c r="A28" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="128"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
       <c r="F28" s="10">
         <v>46188</v>
       </c>
       <c r="G28" s="3"/>
-      <c r="J28" s="128" t="s">
+      <c r="J28" s="120" t="s">
         <v>98</v>
       </c>
-      <c r="K28" s="128"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="128"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
       <c r="O28" s="10">
         <v>46194</v>
       </c>
       <c r="P28" s="3"/>
-      <c r="S28" s="120" t="s">
+      <c r="S28" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="T28" s="120"/>
-      <c r="U28" s="120"/>
-      <c r="V28" s="120"/>
-      <c r="W28" s="120"/>
+      <c r="T28" s="130"/>
+      <c r="U28" s="130"/>
+      <c r="V28" s="130"/>
+      <c r="W28" s="130"/>
       <c r="X28" s="10">
         <v>46199</v>
       </c>
@@ -4332,15 +4332,15 @@
         <f t="shared" si="104"/>
         <v>Senegal</v>
       </c>
-      <c r="AD28" s="113">
+      <c r="AD28" s="100">
         <f t="shared" si="105"/>
         <v>4</v>
       </c>
-      <c r="AE28" s="113">
+      <c r="AE28" s="100">
         <f t="shared" si="106"/>
         <v>-1</v>
       </c>
-      <c r="AF28" s="113">
+      <c r="AF28" s="100">
         <f t="shared" si="107"/>
         <v>4</v>
       </c>
@@ -4351,38 +4351,38 @@
         <f t="shared" si="108"/>
         <v>Áustria</v>
       </c>
-      <c r="AJ28" s="111">
+      <c r="AJ28" s="110">
         <f t="shared" si="109"/>
         <v>1</v>
       </c>
-      <c r="AK28" s="111">
+      <c r="AK28" s="110">
         <f t="shared" si="110"/>
         <v>-4</v>
       </c>
-      <c r="AL28" s="111">
+      <c r="AL28" s="110">
         <f t="shared" si="111"/>
         <v>3</v>
       </c>
-      <c r="AM28" s="100"/>
-      <c r="AP28" s="100"/>
-      <c r="AQ28" s="100"/>
-      <c r="AR28" s="100"/>
-      <c r="AS28" s="100"/>
-      <c r="AV28" s="100"/>
-      <c r="AW28" s="100"/>
-      <c r="AX28" s="100"/>
+      <c r="AM28" s="112"/>
+      <c r="AP28" s="112"/>
+      <c r="AQ28" s="112"/>
+      <c r="AR28" s="112"/>
+      <c r="AS28" s="112"/>
+      <c r="AV28" s="112"/>
+      <c r="AW28" s="112"/>
+      <c r="AX28" s="112"/>
     </row>
     <row r="29" spans="1:50">
       <c r="A29" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="100">
+      <c r="B29" s="112">
         <v>2</v>
       </c>
-      <c r="C29" s="103" t="s">
+      <c r="C29" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="100">
+      <c r="D29" s="112">
         <v>0</v>
       </c>
       <c r="E29" s="39" t="s">
@@ -4402,13 +4402,13 @@
       <c r="J29" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="K29" s="100">
+      <c r="K29" s="112">
         <v>3</v>
       </c>
-      <c r="L29" s="103" t="s">
+      <c r="L29" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="100">
+      <c r="M29" s="112">
         <v>1</v>
       </c>
       <c r="N29" s="39" t="s">
@@ -4428,13 +4428,13 @@
       <c r="S29" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="T29" s="100">
+      <c r="T29" s="112">
         <v>1</v>
       </c>
-      <c r="U29" s="113" t="s">
+      <c r="U29" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="V29" s="100">
+      <c r="V29" s="112">
         <v>0</v>
       </c>
       <c r="W29" s="37" t="s">
@@ -4458,15 +4458,15 @@
         <f t="shared" si="104"/>
         <v>Iraque</v>
       </c>
-      <c r="AD29" s="113">
+      <c r="AD29" s="100">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="113">
+      <c r="AE29" s="100">
         <f t="shared" si="106"/>
         <v>-8</v>
       </c>
-      <c r="AF29" s="113">
+      <c r="AF29" s="100">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
@@ -4477,86 +4477,86 @@
         <f t="shared" si="108"/>
         <v>Jordânia</v>
       </c>
-      <c r="AJ29" s="111">
+      <c r="AJ29" s="110">
         <f t="shared" si="109"/>
         <v>1</v>
       </c>
-      <c r="AK29" s="111">
+      <c r="AK29" s="110">
         <f t="shared" si="110"/>
         <v>-5</v>
       </c>
-      <c r="AL29" s="111">
+      <c r="AL29" s="110">
         <f t="shared" si="111"/>
         <v>3</v>
       </c>
-      <c r="AM29" s="100"/>
-      <c r="AP29" s="100"/>
-      <c r="AQ29" s="100"/>
-      <c r="AR29" s="100"/>
-      <c r="AS29" s="100"/>
-      <c r="AV29" s="100"/>
-      <c r="AW29" s="100"/>
-      <c r="AX29" s="100"/>
+      <c r="AM29" s="112"/>
+      <c r="AP29" s="112"/>
+      <c r="AQ29" s="112"/>
+      <c r="AR29" s="112"/>
+      <c r="AS29" s="112"/>
+      <c r="AV29" s="112"/>
+      <c r="AW29" s="112"/>
+      <c r="AX29" s="112"/>
     </row>
     <row r="30" spans="1:50">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="119" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="135"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
       <c r="F30" s="10">
         <v>46188</v>
       </c>
       <c r="G30" s="3"/>
-      <c r="J30" s="135" t="s">
+      <c r="J30" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="119"/>
       <c r="O30" s="10">
         <v>46194</v>
       </c>
       <c r="P30" s="3"/>
-      <c r="S30" s="135" t="s">
+      <c r="S30" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="T30" s="135"/>
-      <c r="U30" s="135"/>
-      <c r="V30" s="135"/>
-      <c r="W30" s="135"/>
+      <c r="T30" s="119"/>
+      <c r="U30" s="119"/>
+      <c r="V30" s="119"/>
+      <c r="W30" s="119"/>
       <c r="X30" s="10">
         <v>46199</v>
       </c>
-      <c r="AD30" s="100"/>
-      <c r="AE30" s="100"/>
-      <c r="AF30" s="100"/>
-      <c r="AJ30" s="100"/>
-      <c r="AK30" s="100"/>
-      <c r="AL30" s="100"/>
-      <c r="AM30" s="100"/>
-      <c r="AP30" s="100"/>
-      <c r="AQ30" s="100"/>
-      <c r="AR30" s="100"/>
-      <c r="AS30" s="100"/>
-      <c r="AV30" s="100"/>
-      <c r="AW30" s="100"/>
-      <c r="AX30" s="100"/>
+      <c r="AD30" s="112"/>
+      <c r="AE30" s="112"/>
+      <c r="AF30" s="112"/>
+      <c r="AJ30" s="112"/>
+      <c r="AK30" s="112"/>
+      <c r="AL30" s="112"/>
+      <c r="AM30" s="112"/>
+      <c r="AP30" s="112"/>
+      <c r="AQ30" s="112"/>
+      <c r="AR30" s="112"/>
+      <c r="AS30" s="112"/>
+      <c r="AV30" s="112"/>
+      <c r="AW30" s="112"/>
+      <c r="AX30" s="112"/>
     </row>
     <row r="31" spans="1:50">
       <c r="A31" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="100">
+      <c r="B31" s="112">
         <v>1</v>
       </c>
-      <c r="C31" s="102" t="s">
+      <c r="C31" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="100">
+      <c r="D31" s="112">
         <v>1</v>
       </c>
       <c r="E31" s="35" t="s">
@@ -4576,13 +4576,13 @@
       <c r="J31" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="K31" s="100">
+      <c r="K31" s="112">
         <v>3</v>
       </c>
-      <c r="L31" s="102" t="s">
+      <c r="L31" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="M31" s="100">
+      <c r="M31" s="112">
         <v>0</v>
       </c>
       <c r="N31" s="35" t="s">
@@ -4602,13 +4602,13 @@
       <c r="S31" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="T31" s="100">
+      <c r="T31" s="112">
         <v>0</v>
       </c>
-      <c r="U31" s="102" t="s">
+      <c r="U31" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="V31" s="100">
+      <c r="V31" s="112">
         <v>3</v>
       </c>
       <c r="W31" s="35" t="s">
@@ -4638,7 +4638,7 @@
       <c r="AF31" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AG31" s="100"/>
+      <c r="AG31" s="112"/>
       <c r="AH31" s="58"/>
       <c r="AI31" s="23" t="s">
         <v>110</v>
@@ -4652,45 +4652,45 @@
       <c r="AL31" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="AM31" s="100"/>
-      <c r="AP31" s="100"/>
-      <c r="AQ31" s="100"/>
-      <c r="AR31" s="100"/>
-      <c r="AS31" s="100"/>
-      <c r="AV31" s="100"/>
-      <c r="AW31" s="100"/>
-      <c r="AX31" s="100"/>
+      <c r="AM31" s="112"/>
+      <c r="AP31" s="112"/>
+      <c r="AQ31" s="112"/>
+      <c r="AR31" s="112"/>
+      <c r="AS31" s="112"/>
+      <c r="AV31" s="112"/>
+      <c r="AW31" s="112"/>
+      <c r="AX31" s="112"/>
     </row>
     <row r="32" spans="1:50">
-      <c r="A32" s="128" t="s">
+      <c r="A32" s="120" t="s">
         <v>111</v>
       </c>
-      <c r="B32" s="128"/>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
+      <c r="B32" s="120"/>
+      <c r="C32" s="120"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="120"/>
       <c r="F32" s="10">
         <v>46188</v>
       </c>
       <c r="G32" s="3"/>
-      <c r="J32" s="128" t="s">
+      <c r="J32" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="120"/>
       <c r="O32" s="10">
         <v>46194</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="S32" s="135" t="s">
+      <c r="S32" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="T32" s="135"/>
-      <c r="U32" s="135"/>
-      <c r="V32" s="135"/>
-      <c r="W32" s="135"/>
+      <c r="T32" s="119"/>
+      <c r="U32" s="119"/>
+      <c r="V32" s="119"/>
+      <c r="W32" s="119"/>
       <c r="X32" s="10">
         <v>46199</v>
       </c>
@@ -4701,19 +4701,19 @@
         <f>INDEX($AO$92:$AO$95, MATCH(LARGE($AS$92:$AS$95, AB32), $AS$92:$AS$95, 0))</f>
         <v>Colômbia</v>
       </c>
-      <c r="AD32" s="112">
+      <c r="AD32" s="109">
         <f>VLOOKUP(AC32, $AO$92:$AR$95, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AE32" s="112">
+      <c r="AE32" s="109">
         <f>VLOOKUP(AC32, $AO$92:$AR$95, 3, 0)</f>
         <v>10</v>
       </c>
-      <c r="AF32" s="112">
+      <c r="AF32" s="109">
         <f>VLOOKUP(AC32, $AO$92:$AR$95, 4, 0)</f>
         <v>10</v>
       </c>
-      <c r="AG32" s="100"/>
+      <c r="AG32" s="112"/>
       <c r="AH32" s="60">
         <v>1</v>
       </c>
@@ -4721,38 +4721,38 @@
         <f>INDEX($AU$92:$AU$95, MATCH(LARGE($AY$92:$AY$95, AH32), $AY$92:$AY$95, 0))</f>
         <v>Inglaterra</v>
       </c>
-      <c r="AJ32" s="104">
+      <c r="AJ32" s="113">
         <f>VLOOKUP(AI32, $AU$92:$AX$95, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AK32" s="104">
+      <c r="AK32" s="113">
         <f>VLOOKUP(AI32, $AU$92:$AX$95, 3, 0)</f>
         <v>9</v>
       </c>
-      <c r="AL32" s="104">
+      <c r="AL32" s="113">
         <f>VLOOKUP(AI32, $AU$92:$AX$95, 4, 0)</f>
         <v>9</v>
       </c>
-      <c r="AM32" s="100"/>
-      <c r="AP32" s="100"/>
-      <c r="AQ32" s="100"/>
-      <c r="AR32" s="100"/>
-      <c r="AS32" s="100"/>
-      <c r="AV32" s="100"/>
-      <c r="AW32" s="100"/>
-      <c r="AX32" s="100"/>
+      <c r="AM32" s="112"/>
+      <c r="AP32" s="112"/>
+      <c r="AQ32" s="112"/>
+      <c r="AR32" s="112"/>
+      <c r="AS32" s="112"/>
+      <c r="AV32" s="112"/>
+      <c r="AW32" s="112"/>
+      <c r="AX32" s="112"/>
     </row>
     <row r="33" spans="1:50">
       <c r="A33" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="100">
+      <c r="B33" s="112">
         <v>0</v>
       </c>
-      <c r="C33" s="103" t="s">
+      <c r="C33" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="100">
+      <c r="D33" s="112">
         <v>0</v>
       </c>
       <c r="E33" s="39" t="s">
@@ -4772,13 +4772,13 @@
       <c r="J33" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="K33" s="100">
+      <c r="K33" s="112">
         <v>0</v>
       </c>
-      <c r="L33" s="103" t="s">
+      <c r="L33" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="M33" s="100">
+      <c r="M33" s="112">
         <v>1</v>
       </c>
       <c r="N33" s="39" t="s">
@@ -4798,13 +4798,13 @@
       <c r="S33" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="T33" s="100">
+      <c r="T33" s="112">
         <v>1</v>
       </c>
-      <c r="U33" s="102" t="s">
+      <c r="U33" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="V33" s="100">
+      <c r="V33" s="112">
         <v>1</v>
       </c>
       <c r="W33" s="35" t="s">
@@ -4828,19 +4828,19 @@
         <f t="shared" ref="AC33:AC35" si="130">INDEX($AO$92:$AO$95, MATCH(LARGE($AS$92:$AS$95, AB33), $AS$92:$AS$95, 0))</f>
         <v>Portugal</v>
       </c>
-      <c r="AD33" s="112">
+      <c r="AD33" s="109">
         <f t="shared" ref="AD33:AD35" si="131">VLOOKUP(AC33, $AO$92:$AR$95, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AE33" s="112">
+      <c r="AE33" s="109">
         <f t="shared" ref="AE33:AE35" si="132">VLOOKUP(AC33, $AO$92:$AR$95, 3, 0)</f>
         <v>7</v>
       </c>
-      <c r="AF33" s="112">
+      <c r="AF33" s="109">
         <f t="shared" ref="AF33:AF35" si="133">VLOOKUP(AC33, $AO$92:$AR$95, 4, 0)</f>
         <v>7</v>
       </c>
-      <c r="AG33" s="100"/>
+      <c r="AG33" s="112"/>
       <c r="AH33" s="60">
         <v>2</v>
       </c>
@@ -4848,57 +4848,57 @@
         <f t="shared" ref="AI33:AI35" si="134">INDEX($AU$92:$AU$95, MATCH(LARGE($AY$92:$AY$95, AH33), $AY$92:$AY$95, 0))</f>
         <v>Croácia</v>
       </c>
-      <c r="AJ33" s="104">
+      <c r="AJ33" s="113">
         <f t="shared" ref="AJ33:AJ35" si="135">VLOOKUP(AI33, $AU$92:$AX$95, 2, 0)</f>
         <v>7</v>
       </c>
-      <c r="AK33" s="104">
+      <c r="AK33" s="113">
         <f t="shared" ref="AK33:AK35" si="136">VLOOKUP(AI33, $AU$92:$AX$95, 3, 0)</f>
         <v>8</v>
       </c>
-      <c r="AL33" s="104">
+      <c r="AL33" s="113">
         <f t="shared" ref="AL33:AL35" si="137">VLOOKUP(AI33, $AU$92:$AX$95, 4, 0)</f>
         <v>8</v>
       </c>
-      <c r="AM33" s="100"/>
-      <c r="AP33" s="100"/>
-      <c r="AQ33" s="100"/>
-      <c r="AR33" s="100"/>
-      <c r="AS33" s="100"/>
-      <c r="AV33" s="100"/>
-      <c r="AW33" s="100"/>
-      <c r="AX33" s="100"/>
+      <c r="AM33" s="112"/>
+      <c r="AP33" s="112"/>
+      <c r="AQ33" s="112"/>
+      <c r="AR33" s="112"/>
+      <c r="AS33" s="112"/>
+      <c r="AV33" s="112"/>
+      <c r="AW33" s="112"/>
+      <c r="AX33" s="112"/>
     </row>
     <row r="34" spans="1:50">
-      <c r="A34" s="120" t="s">
+      <c r="A34" s="130" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="120"/>
-      <c r="C34" s="120"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="120"/>
+      <c r="B34" s="130"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
       <c r="F34" s="10">
         <v>46189</v>
       </c>
       <c r="G34" s="3"/>
-      <c r="J34" s="130" t="s">
+      <c r="J34" s="128" t="s">
         <v>116</v>
       </c>
-      <c r="K34" s="130"/>
-      <c r="L34" s="130"/>
-      <c r="M34" s="130"/>
-      <c r="N34" s="130"/>
+      <c r="K34" s="128"/>
+      <c r="L34" s="128"/>
+      <c r="M34" s="128"/>
+      <c r="N34" s="128"/>
       <c r="O34" s="10">
         <v>46195</v>
       </c>
       <c r="P34" s="3"/>
-      <c r="S34" s="128" t="s">
+      <c r="S34" s="120" t="s">
         <v>117</v>
       </c>
-      <c r="T34" s="128"/>
-      <c r="U34" s="128"/>
-      <c r="V34" s="128"/>
-      <c r="W34" s="128"/>
+      <c r="T34" s="120"/>
+      <c r="U34" s="120"/>
+      <c r="V34" s="120"/>
+      <c r="W34" s="120"/>
       <c r="X34" s="10">
         <v>46200</v>
       </c>
@@ -4909,19 +4909,19 @@
         <f t="shared" si="130"/>
         <v>Uzbequistão</v>
       </c>
-      <c r="AD34" s="112">
+      <c r="AD34" s="109">
         <f t="shared" si="131"/>
         <v>1</v>
       </c>
-      <c r="AE34" s="112">
+      <c r="AE34" s="109">
         <f t="shared" si="132"/>
         <v>-8</v>
       </c>
-      <c r="AF34" s="112">
+      <c r="AF34" s="109">
         <f t="shared" si="133"/>
         <v>2</v>
       </c>
-      <c r="AG34" s="100"/>
+      <c r="AG34" s="112"/>
       <c r="AH34" s="60">
         <v>3</v>
       </c>
@@ -4929,38 +4929,38 @@
         <f t="shared" si="134"/>
         <v>Gana</v>
       </c>
-      <c r="AJ34" s="104">
+      <c r="AJ34" s="113">
         <f t="shared" si="135"/>
         <v>3</v>
       </c>
-      <c r="AK34" s="104">
+      <c r="AK34" s="113">
         <f t="shared" si="136"/>
         <v>-8</v>
       </c>
-      <c r="AL34" s="104">
+      <c r="AL34" s="113">
         <f t="shared" si="137"/>
         <v>3</v>
       </c>
-      <c r="AM34" s="100"/>
-      <c r="AP34" s="100"/>
-      <c r="AQ34" s="100"/>
-      <c r="AR34" s="100"/>
-      <c r="AS34" s="100"/>
-      <c r="AV34" s="100"/>
-      <c r="AW34" s="100"/>
-      <c r="AX34" s="100"/>
+      <c r="AM34" s="112"/>
+      <c r="AP34" s="112"/>
+      <c r="AQ34" s="112"/>
+      <c r="AR34" s="112"/>
+      <c r="AS34" s="112"/>
+      <c r="AV34" s="112"/>
+      <c r="AW34" s="112"/>
+      <c r="AX34" s="112"/>
     </row>
     <row r="35" spans="1:50">
       <c r="A35" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="100">
+      <c r="B35" s="112">
         <v>3</v>
       </c>
-      <c r="C35" s="113" t="s">
+      <c r="C35" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="100">
+      <c r="D35" s="112">
         <v>1</v>
       </c>
       <c r="E35" s="37" t="s">
@@ -4980,13 +4980,13 @@
       <c r="J35" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="K35" s="100">
+      <c r="K35" s="112">
         <v>3</v>
       </c>
-      <c r="L35" s="111" t="s">
+      <c r="L35" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="M35" s="100">
+      <c r="M35" s="112">
         <v>1</v>
       </c>
       <c r="N35" s="36" t="s">
@@ -5006,13 +5006,13 @@
       <c r="S35" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="T35" s="100">
+      <c r="T35" s="112">
         <v>0</v>
       </c>
-      <c r="U35" s="103" t="s">
+      <c r="U35" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="V35" s="100">
+      <c r="V35" s="112">
         <v>3</v>
       </c>
       <c r="W35" s="39" t="s">
@@ -5036,19 +5036,19 @@
         <f t="shared" si="130"/>
         <v>RD Congo</v>
       </c>
-      <c r="AD35" s="112">
+      <c r="AD35" s="109">
         <f t="shared" si="131"/>
         <v>1</v>
       </c>
-      <c r="AE35" s="112">
+      <c r="AE35" s="109">
         <f t="shared" si="132"/>
         <v>-9</v>
       </c>
-      <c r="AF35" s="112">
+      <c r="AF35" s="109">
         <f t="shared" si="133"/>
         <v>2</v>
       </c>
-      <c r="AG35" s="100"/>
+      <c r="AG35" s="112"/>
       <c r="AH35" s="60">
         <v>4</v>
       </c>
@@ -5056,86 +5056,86 @@
         <f t="shared" si="134"/>
         <v>Panamá</v>
       </c>
-      <c r="AJ35" s="104">
+      <c r="AJ35" s="113">
         <f t="shared" si="135"/>
         <v>0</v>
       </c>
-      <c r="AK35" s="104">
+      <c r="AK35" s="113">
         <f t="shared" si="136"/>
         <v>-9</v>
       </c>
-      <c r="AL35" s="104">
+      <c r="AL35" s="113">
         <f t="shared" si="137"/>
         <v>2</v>
       </c>
-      <c r="AM35" s="100"/>
-      <c r="AP35" s="100"/>
-      <c r="AQ35" s="100"/>
-      <c r="AR35" s="100"/>
-      <c r="AS35" s="100"/>
-      <c r="AV35" s="100"/>
-      <c r="AW35" s="100"/>
-      <c r="AX35" s="100"/>
+      <c r="AM35" s="112"/>
+      <c r="AP35" s="112"/>
+      <c r="AQ35" s="112"/>
+      <c r="AR35" s="112"/>
+      <c r="AS35" s="112"/>
+      <c r="AV35" s="112"/>
+      <c r="AW35" s="112"/>
+      <c r="AX35" s="112"/>
     </row>
     <row r="36" spans="1:50">
-      <c r="A36" s="120" t="s">
+      <c r="A36" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="120"/>
-      <c r="C36" s="120"/>
-      <c r="D36" s="120"/>
-      <c r="E36" s="120"/>
+      <c r="B36" s="130"/>
+      <c r="C36" s="130"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
       <c r="F36" s="10">
         <v>46189</v>
       </c>
       <c r="G36" s="3"/>
-      <c r="J36" s="120" t="s">
+      <c r="J36" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="K36" s="120"/>
-      <c r="L36" s="120"/>
-      <c r="M36" s="120"/>
-      <c r="N36" s="120"/>
+      <c r="K36" s="130"/>
+      <c r="L36" s="130"/>
+      <c r="M36" s="130"/>
+      <c r="N36" s="130"/>
       <c r="O36" s="10">
         <v>46195</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="S36" s="128" t="s">
+      <c r="S36" s="120" t="s">
         <v>122</v>
       </c>
-      <c r="T36" s="128"/>
-      <c r="U36" s="128"/>
-      <c r="V36" s="128"/>
-      <c r="W36" s="128"/>
+      <c r="T36" s="120"/>
+      <c r="U36" s="120"/>
+      <c r="V36" s="120"/>
+      <c r="W36" s="120"/>
       <c r="X36" s="10">
         <v>46200</v>
       </c>
-      <c r="AD36" s="100"/>
-      <c r="AE36" s="100"/>
-      <c r="AF36" s="100"/>
-      <c r="AJ36" s="100"/>
-      <c r="AK36" s="100"/>
-      <c r="AL36" s="100"/>
-      <c r="AM36" s="100"/>
-      <c r="AP36" s="100"/>
-      <c r="AQ36" s="100"/>
-      <c r="AR36" s="100"/>
-      <c r="AS36" s="100"/>
-      <c r="AV36" s="100"/>
-      <c r="AW36" s="100"/>
-      <c r="AX36" s="100"/>
+      <c r="AD36" s="112"/>
+      <c r="AE36" s="112"/>
+      <c r="AF36" s="112"/>
+      <c r="AJ36" s="112"/>
+      <c r="AK36" s="112"/>
+      <c r="AL36" s="112"/>
+      <c r="AM36" s="112"/>
+      <c r="AP36" s="112"/>
+      <c r="AQ36" s="112"/>
+      <c r="AR36" s="112"/>
+      <c r="AS36" s="112"/>
+      <c r="AV36" s="112"/>
+      <c r="AW36" s="112"/>
+      <c r="AX36" s="112"/>
     </row>
     <row r="37" spans="1:50">
       <c r="A37" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="100">
+      <c r="B37" s="112">
         <v>0</v>
       </c>
-      <c r="C37" s="113" t="s">
+      <c r="C37" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="100">
+      <c r="D37" s="112">
         <v>3</v>
       </c>
       <c r="E37" s="37" t="s">
@@ -5155,13 +5155,13 @@
       <c r="J37" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="K37" s="100">
+      <c r="K37" s="112">
         <v>4</v>
       </c>
-      <c r="L37" s="113" t="s">
+      <c r="L37" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="100">
+      <c r="M37" s="112">
         <v>0</v>
       </c>
       <c r="N37" s="37" t="s">
@@ -5181,13 +5181,13 @@
       <c r="S37" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="T37" s="100">
+      <c r="T37" s="112">
         <v>1</v>
       </c>
-      <c r="U37" s="103" t="s">
+      <c r="U37" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="V37" s="100">
+      <c r="V37" s="112">
         <v>0</v>
       </c>
       <c r="W37" s="39" t="s">
@@ -5205,61 +5205,61 @@
         <v>0</v>
       </c>
       <c r="AB37" s="77"/>
-      <c r="AC37" s="101" t="s">
+      <c r="AC37" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="AD37" s="101" t="s">
+      <c r="AD37" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="AE37" s="101" t="s">
+      <c r="AE37" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="AF37" s="101" t="s">
+      <c r="AF37" s="114" t="s">
         <v>6</v>
       </c>
       <c r="AG37" s="1"/>
-      <c r="AJ37" s="100"/>
-      <c r="AK37" s="100"/>
-      <c r="AL37" s="100"/>
-      <c r="AM37" s="100"/>
-      <c r="AP37" s="100"/>
-      <c r="AQ37" s="100"/>
-      <c r="AR37" s="100"/>
-      <c r="AS37" s="100"/>
-      <c r="AV37" s="100"/>
-      <c r="AW37" s="100"/>
-      <c r="AX37" s="100"/>
+      <c r="AJ37" s="112"/>
+      <c r="AK37" s="112"/>
+      <c r="AL37" s="112"/>
+      <c r="AM37" s="112"/>
+      <c r="AP37" s="112"/>
+      <c r="AQ37" s="112"/>
+      <c r="AR37" s="112"/>
+      <c r="AS37" s="112"/>
+      <c r="AV37" s="112"/>
+      <c r="AW37" s="112"/>
+      <c r="AX37" s="112"/>
     </row>
     <row r="38" spans="1:50">
-      <c r="A38" s="130" t="s">
+      <c r="A38" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="130"/>
-      <c r="C38" s="130"/>
-      <c r="D38" s="130"/>
-      <c r="E38" s="130"/>
+      <c r="B38" s="128"/>
+      <c r="C38" s="128"/>
+      <c r="D38" s="128"/>
+      <c r="E38" s="128"/>
       <c r="F38" s="10">
         <v>46189</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="J38" s="120" t="s">
+      <c r="J38" s="130" t="s">
         <v>126</v>
       </c>
-      <c r="K38" s="120"/>
-      <c r="L38" s="120"/>
-      <c r="M38" s="120"/>
-      <c r="N38" s="120"/>
+      <c r="K38" s="130"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
       <c r="O38" s="10">
         <v>46195</v>
       </c>
       <c r="P38" s="3"/>
-      <c r="S38" s="133" t="s">
+      <c r="S38" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="T38" s="133"/>
-      <c r="U38" s="133"/>
-      <c r="V38" s="133"/>
-      <c r="W38" s="133"/>
+      <c r="T38" s="121"/>
+      <c r="U38" s="121"/>
+      <c r="V38" s="121"/>
+      <c r="W38" s="121"/>
       <c r="X38" s="10">
         <v>46200</v>
       </c>
@@ -5270,15 +5270,15 @@
         <f>INDEX($BC$80:$BC$91, MATCH(LARGE($BG$80:$BG$91, AB38), $BG$80:$BG$91, 0))</f>
         <v>Arábia Saudita</v>
       </c>
-      <c r="AD38" s="105">
+      <c r="AD38" s="102">
         <f>VLOOKUP(AC38, $BC$80:$BH$91, 2, 0)</f>
         <v>4</v>
       </c>
-      <c r="AE38" s="105">
+      <c r="AE38" s="102">
         <f>VLOOKUP(AC38, $BC$80:$BH$91, 3, 0)</f>
         <v>2</v>
       </c>
-      <c r="AF38" s="105">
+      <c r="AF38" s="102">
         <f>VLOOKUP(AC38, $BC$80:$BH$91, 4, 0)</f>
         <v>5</v>
       </c>
@@ -5286,29 +5286,29 @@
         <f>VLOOKUP(AC38, $BC$80:$BH$91, 6, 0)</f>
         <v>H</v>
       </c>
-      <c r="AJ38" s="100"/>
-      <c r="AK38" s="100"/>
-      <c r="AL38" s="100"/>
-      <c r="AM38" s="100"/>
-      <c r="AP38" s="100"/>
-      <c r="AQ38" s="100"/>
-      <c r="AR38" s="100"/>
-      <c r="AS38" s="100"/>
-      <c r="AV38" s="100"/>
-      <c r="AW38" s="100"/>
-      <c r="AX38" s="100"/>
+      <c r="AJ38" s="112"/>
+      <c r="AK38" s="112"/>
+      <c r="AL38" s="112"/>
+      <c r="AM38" s="112"/>
+      <c r="AP38" s="112"/>
+      <c r="AQ38" s="112"/>
+      <c r="AR38" s="112"/>
+      <c r="AS38" s="112"/>
+      <c r="AV38" s="112"/>
+      <c r="AW38" s="112"/>
+      <c r="AX38" s="112"/>
     </row>
     <row r="39" spans="1:50">
       <c r="A39" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="100">
+      <c r="B39" s="112">
         <v>2</v>
       </c>
-      <c r="C39" s="111" t="s">
+      <c r="C39" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="100">
+      <c r="D39" s="112">
         <v>0</v>
       </c>
       <c r="E39" s="36" t="s">
@@ -5328,13 +5328,13 @@
       <c r="J39" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="K39" s="100">
+      <c r="K39" s="112">
         <v>2</v>
       </c>
-      <c r="L39" s="113" t="s">
+      <c r="L39" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="M39" s="100">
+      <c r="M39" s="112">
         <v>2</v>
       </c>
       <c r="N39" s="37" t="s">
@@ -5354,13 +5354,13 @@
       <c r="S39" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="T39" s="100">
+      <c r="T39" s="112">
         <v>0</v>
       </c>
-      <c r="U39" s="104" t="s">
+      <c r="U39" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="V39" s="100">
+      <c r="V39" s="112">
         <v>4</v>
       </c>
       <c r="W39" s="34" t="s">
@@ -5384,15 +5384,15 @@
         <f t="shared" ref="AC39:AC49" si="156">INDEX($BC$80:$BC$91, MATCH(LARGE($BG$80:$BG$91, AB39), $BG$80:$BG$91, 0))</f>
         <v>Suécia</v>
       </c>
-      <c r="AD39" s="105">
+      <c r="AD39" s="102">
         <f t="shared" ref="AD39:AD49" si="157">VLOOKUP(AC39, $BC$80:$BH$91, 2, 0)</f>
         <v>4</v>
       </c>
-      <c r="AE39" s="105">
+      <c r="AE39" s="102">
         <f t="shared" ref="AE39:AE49" si="158">VLOOKUP(AC39, $BC$80:$BH$91, 3, 0)</f>
         <v>-1</v>
       </c>
-      <c r="AF39" s="105">
+      <c r="AF39" s="102">
         <f t="shared" ref="AF39:AF49" si="159">VLOOKUP(AC39, $BC$80:$BH$91, 4, 0)</f>
         <v>4</v>
       </c>
@@ -5400,48 +5400,48 @@
         <f t="shared" ref="AG39:AG49" si="160">VLOOKUP(AC39, $BC$80:$BH$91, 6, 0)</f>
         <v>F</v>
       </c>
-      <c r="AJ39" s="100"/>
-      <c r="AK39" s="100"/>
-      <c r="AL39" s="100"/>
-      <c r="AM39" s="100"/>
-      <c r="AP39" s="100"/>
-      <c r="AQ39" s="100"/>
-      <c r="AR39" s="100"/>
-      <c r="AS39" s="100"/>
-      <c r="AV39" s="100"/>
-      <c r="AW39" s="100"/>
-      <c r="AX39" s="100"/>
+      <c r="AJ39" s="112"/>
+      <c r="AK39" s="112"/>
+      <c r="AL39" s="112"/>
+      <c r="AM39" s="112"/>
+      <c r="AP39" s="112"/>
+      <c r="AQ39" s="112"/>
+      <c r="AR39" s="112"/>
+      <c r="AS39" s="112"/>
+      <c r="AV39" s="112"/>
+      <c r="AW39" s="112"/>
+      <c r="AX39" s="112"/>
     </row>
     <row r="40" spans="1:50">
-      <c r="A40" s="130" t="s">
+      <c r="A40" s="128" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="130"/>
-      <c r="C40" s="130"/>
-      <c r="D40" s="130"/>
-      <c r="E40" s="130"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
       <c r="F40" s="10">
         <v>46190</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="J40" s="130" t="s">
+      <c r="J40" s="128" t="s">
         <v>132</v>
       </c>
-      <c r="K40" s="130"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="130"/>
-      <c r="N40" s="130"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
       <c r="O40" s="10">
         <v>46196</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="S40" s="133" t="s">
+      <c r="S40" s="121" t="s">
         <v>133</v>
       </c>
-      <c r="T40" s="133"/>
-      <c r="U40" s="133"/>
-      <c r="V40" s="133"/>
-      <c r="W40" s="133"/>
+      <c r="T40" s="121"/>
+      <c r="U40" s="121"/>
+      <c r="V40" s="121"/>
+      <c r="W40" s="121"/>
       <c r="X40" s="10">
         <v>46200</v>
       </c>
@@ -5452,15 +5452,15 @@
         <f t="shared" si="156"/>
         <v>Senegal</v>
       </c>
-      <c r="AD40" s="105">
+      <c r="AD40" s="102">
         <f t="shared" si="157"/>
         <v>4</v>
       </c>
-      <c r="AE40" s="105">
+      <c r="AE40" s="102">
         <f t="shared" si="158"/>
         <v>-1</v>
       </c>
-      <c r="AF40" s="105">
+      <c r="AF40" s="102">
         <f t="shared" si="159"/>
         <v>4</v>
       </c>
@@ -5468,29 +5468,29 @@
         <f t="shared" si="160"/>
         <v>I</v>
       </c>
-      <c r="AJ40" s="100"/>
-      <c r="AK40" s="100"/>
-      <c r="AL40" s="100"/>
-      <c r="AM40" s="100"/>
-      <c r="AP40" s="100"/>
-      <c r="AQ40" s="100"/>
-      <c r="AR40" s="100"/>
-      <c r="AS40" s="100"/>
-      <c r="AV40" s="100"/>
-      <c r="AW40" s="100"/>
-      <c r="AX40" s="100"/>
+      <c r="AJ40" s="112"/>
+      <c r="AK40" s="112"/>
+      <c r="AL40" s="112"/>
+      <c r="AM40" s="112"/>
+      <c r="AP40" s="112"/>
+      <c r="AQ40" s="112"/>
+      <c r="AR40" s="112"/>
+      <c r="AS40" s="112"/>
+      <c r="AV40" s="112"/>
+      <c r="AW40" s="112"/>
+      <c r="AX40" s="112"/>
     </row>
     <row r="41" spans="1:50">
       <c r="A41" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="100">
+      <c r="B41" s="112">
         <v>2</v>
       </c>
-      <c r="C41" s="111" t="s">
+      <c r="C41" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="100">
+      <c r="D41" s="112">
         <v>2</v>
       </c>
       <c r="E41" s="36" t="s">
@@ -5510,13 +5510,13 @@
       <c r="J41" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="K41" s="100">
+      <c r="K41" s="112">
         <v>1</v>
       </c>
-      <c r="L41" s="111" t="s">
+      <c r="L41" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="M41" s="100">
+      <c r="M41" s="112">
         <v>2</v>
       </c>
       <c r="N41" s="36" t="s">
@@ -5536,13 +5536,13 @@
       <c r="S41" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="T41" s="100">
+      <c r="T41" s="112">
         <v>4</v>
       </c>
-      <c r="U41" s="104" t="s">
+      <c r="U41" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="V41" s="100">
+      <c r="V41" s="112">
         <v>0</v>
       </c>
       <c r="W41" s="34" t="s">
@@ -5566,15 +5566,15 @@
         <f t="shared" si="156"/>
         <v>Canadá</v>
       </c>
-      <c r="AD41" s="105">
+      <c r="AD41" s="102">
         <f t="shared" si="157"/>
         <v>4</v>
       </c>
-      <c r="AE41" s="105">
+      <c r="AE41" s="102">
         <f t="shared" si="158"/>
         <v>-1</v>
       </c>
-      <c r="AF41" s="105">
+      <c r="AF41" s="102">
         <f t="shared" si="159"/>
         <v>3</v>
       </c>
@@ -5582,17 +5582,17 @@
         <f t="shared" si="160"/>
         <v>B</v>
       </c>
-      <c r="AJ41" s="100"/>
-      <c r="AK41" s="100"/>
-      <c r="AL41" s="100"/>
-      <c r="AM41" s="100"/>
-      <c r="AP41" s="100"/>
-      <c r="AQ41" s="100"/>
-      <c r="AR41" s="100"/>
-      <c r="AS41" s="100"/>
-      <c r="AV41" s="100"/>
-      <c r="AW41" s="100"/>
-      <c r="AX41" s="100"/>
+      <c r="AJ41" s="112"/>
+      <c r="AK41" s="112"/>
+      <c r="AL41" s="112"/>
+      <c r="AM41" s="112"/>
+      <c r="AP41" s="112"/>
+      <c r="AQ41" s="112"/>
+      <c r="AR41" s="112"/>
+      <c r="AS41" s="112"/>
+      <c r="AV41" s="112"/>
+      <c r="AW41" s="112"/>
+      <c r="AX41" s="112"/>
     </row>
     <row r="42" spans="1:50">
       <c r="A42" s="129" t="s">
@@ -5634,45 +5634,45 @@
         <f t="shared" si="156"/>
         <v>Escócia</v>
       </c>
-      <c r="AD42" s="105">
+      <c r="AD42" s="102">
         <f t="shared" si="157"/>
         <v>3</v>
       </c>
-      <c r="AE42" s="105">
+      <c r="AE42" s="102">
         <f t="shared" si="158"/>
-        <v>0</v>
-      </c>
-      <c r="AF42" s="105">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="102">
         <f t="shared" si="159"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG42" s="12" t="str">
         <f t="shared" si="160"/>
         <v>C</v>
       </c>
-      <c r="AJ42" s="100"/>
-      <c r="AK42" s="100"/>
-      <c r="AL42" s="100"/>
-      <c r="AM42" s="100"/>
-      <c r="AP42" s="100"/>
-      <c r="AQ42" s="100"/>
-      <c r="AR42" s="100"/>
-      <c r="AS42" s="100"/>
-      <c r="AV42" s="100"/>
-      <c r="AW42" s="100"/>
-      <c r="AX42" s="100"/>
+      <c r="AJ42" s="112"/>
+      <c r="AK42" s="112"/>
+      <c r="AL42" s="112"/>
+      <c r="AM42" s="112"/>
+      <c r="AP42" s="112"/>
+      <c r="AQ42" s="112"/>
+      <c r="AR42" s="112"/>
+      <c r="AS42" s="112"/>
+      <c r="AV42" s="112"/>
+      <c r="AW42" s="112"/>
+      <c r="AX42" s="112"/>
     </row>
     <row r="43" spans="1:50">
       <c r="A43" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="100">
+      <c r="B43" s="112">
         <v>4</v>
       </c>
-      <c r="C43" s="112" t="s">
+      <c r="C43" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="D43" s="100">
+      <c r="D43" s="112">
         <v>0</v>
       </c>
       <c r="E43" s="38" t="s">
@@ -5692,13 +5692,13 @@
       <c r="J43" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="K43" s="100">
+      <c r="K43" s="112">
         <v>3</v>
       </c>
-      <c r="L43" s="112" t="s">
+      <c r="L43" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="M43" s="100">
+      <c r="M43" s="112">
         <v>0</v>
       </c>
       <c r="N43" s="38" t="s">
@@ -5718,13 +5718,13 @@
       <c r="S43" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="T43" s="100">
+      <c r="T43" s="112">
         <v>0</v>
       </c>
-      <c r="U43" s="112" t="s">
+      <c r="U43" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="V43" s="100">
+      <c r="V43" s="112">
         <v>0</v>
       </c>
       <c r="W43" s="38" t="s">
@@ -5748,15 +5748,15 @@
         <f t="shared" si="156"/>
         <v>Costa do Marfim</v>
       </c>
-      <c r="AD43" s="105">
+      <c r="AD43" s="102">
         <f t="shared" si="157"/>
         <v>3</v>
       </c>
-      <c r="AE43" s="105">
+      <c r="AE43" s="102">
         <f t="shared" si="158"/>
         <v>-1</v>
       </c>
-      <c r="AF43" s="105">
+      <c r="AF43" s="102">
         <f t="shared" si="159"/>
         <v>4</v>
       </c>
@@ -5764,37 +5764,37 @@
         <f t="shared" si="160"/>
         <v>E</v>
       </c>
-      <c r="AJ43" s="100"/>
-      <c r="AK43" s="100"/>
-      <c r="AL43" s="100"/>
-      <c r="AM43" s="100"/>
-      <c r="AP43" s="100"/>
-      <c r="AQ43" s="100"/>
-      <c r="AR43" s="100"/>
-      <c r="AS43" s="100"/>
-      <c r="AV43" s="100"/>
-      <c r="AW43" s="100"/>
-      <c r="AX43" s="100"/>
+      <c r="AJ43" s="112"/>
+      <c r="AK43" s="112"/>
+      <c r="AL43" s="112"/>
+      <c r="AM43" s="112"/>
+      <c r="AP43" s="112"/>
+      <c r="AQ43" s="112"/>
+      <c r="AR43" s="112"/>
+      <c r="AS43" s="112"/>
+      <c r="AV43" s="112"/>
+      <c r="AW43" s="112"/>
+      <c r="AX43" s="112"/>
     </row>
     <row r="44" spans="1:50">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="121" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
-      <c r="D44" s="133"/>
-      <c r="E44" s="133"/>
+      <c r="B44" s="121"/>
+      <c r="C44" s="121"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="121"/>
       <c r="F44" s="10">
         <v>46190</v>
       </c>
       <c r="G44" s="3"/>
-      <c r="J44" s="133" t="s">
+      <c r="J44" s="121" t="s">
         <v>146</v>
       </c>
-      <c r="K44" s="133"/>
-      <c r="L44" s="133"/>
-      <c r="M44" s="133"/>
-      <c r="N44" s="133"/>
+      <c r="K44" s="121"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
       <c r="O44" s="10">
         <v>46196</v>
       </c>
@@ -5816,15 +5816,15 @@
         <f t="shared" si="156"/>
         <v>Gana</v>
       </c>
-      <c r="AD44" s="105">
+      <c r="AD44" s="102">
         <f t="shared" si="157"/>
         <v>3</v>
       </c>
-      <c r="AE44" s="105">
+      <c r="AE44" s="102">
         <f t="shared" si="158"/>
         <v>-8</v>
       </c>
-      <c r="AF44" s="105">
+      <c r="AF44" s="102">
         <f t="shared" si="159"/>
         <v>3</v>
       </c>
@@ -5832,29 +5832,29 @@
         <f t="shared" si="160"/>
         <v>L</v>
       </c>
-      <c r="AJ44" s="100"/>
-      <c r="AK44" s="100"/>
-      <c r="AL44" s="100"/>
-      <c r="AM44" s="100"/>
-      <c r="AP44" s="100"/>
-      <c r="AQ44" s="100"/>
-      <c r="AR44" s="100"/>
-      <c r="AS44" s="100"/>
-      <c r="AV44" s="100"/>
-      <c r="AW44" s="100"/>
-      <c r="AX44" s="100"/>
+      <c r="AJ44" s="112"/>
+      <c r="AK44" s="112"/>
+      <c r="AL44" s="112"/>
+      <c r="AM44" s="112"/>
+      <c r="AP44" s="112"/>
+      <c r="AQ44" s="112"/>
+      <c r="AR44" s="112"/>
+      <c r="AS44" s="112"/>
+      <c r="AV44" s="112"/>
+      <c r="AW44" s="112"/>
+      <c r="AX44" s="112"/>
     </row>
     <row r="45" spans="1:50">
       <c r="A45" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="100">
+      <c r="B45" s="112">
         <v>0</v>
       </c>
-      <c r="C45" s="104" t="s">
+      <c r="C45" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="D45" s="100">
+      <c r="D45" s="112">
         <v>0</v>
       </c>
       <c r="E45" s="34" t="s">
@@ -5874,13 +5874,13 @@
       <c r="J45" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="K45" s="100">
+      <c r="K45" s="112">
         <v>5</v>
       </c>
-      <c r="L45" s="104" t="s">
+      <c r="L45" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="M45" s="100">
+      <c r="M45" s="112">
         <v>0</v>
       </c>
       <c r="N45" s="34" t="s">
@@ -5900,13 +5900,13 @@
       <c r="S45" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="T45" s="100">
+      <c r="T45" s="112">
         <v>2</v>
       </c>
-      <c r="U45" s="112" t="s">
+      <c r="U45" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="V45" s="100">
+      <c r="V45" s="112">
         <v>2</v>
       </c>
       <c r="W45" s="38" t="s">
@@ -5930,15 +5930,15 @@
         <f t="shared" si="156"/>
         <v>Austrália</v>
       </c>
-      <c r="AD45" s="105">
+      <c r="AD45" s="102">
         <f t="shared" si="157"/>
         <v>2</v>
       </c>
-      <c r="AE45" s="105">
+      <c r="AE45" s="102">
         <f t="shared" si="158"/>
         <v>-3</v>
       </c>
-      <c r="AF45" s="105">
+      <c r="AF45" s="102">
         <f t="shared" si="159"/>
         <v>5</v>
       </c>
@@ -5946,48 +5946,48 @@
         <f t="shared" si="160"/>
         <v>D</v>
       </c>
-      <c r="AJ45" s="100"/>
-      <c r="AK45" s="100"/>
-      <c r="AL45" s="100"/>
-      <c r="AM45" s="100"/>
-      <c r="AP45" s="100"/>
-      <c r="AQ45" s="100"/>
-      <c r="AR45" s="100"/>
-      <c r="AS45" s="100"/>
-      <c r="AV45" s="100"/>
-      <c r="AW45" s="100"/>
-      <c r="AX45" s="100"/>
+      <c r="AJ45" s="112"/>
+      <c r="AK45" s="112"/>
+      <c r="AL45" s="112"/>
+      <c r="AM45" s="112"/>
+      <c r="AP45" s="112"/>
+      <c r="AQ45" s="112"/>
+      <c r="AR45" s="112"/>
+      <c r="AS45" s="112"/>
+      <c r="AV45" s="112"/>
+      <c r="AW45" s="112"/>
+      <c r="AX45" s="112"/>
     </row>
     <row r="46" spans="1:50">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="121" t="s">
         <v>148</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
-      <c r="D46" s="133"/>
-      <c r="E46" s="133"/>
+      <c r="B46" s="121"/>
+      <c r="C46" s="121"/>
+      <c r="D46" s="121"/>
+      <c r="E46" s="121"/>
       <c r="F46" s="10">
         <v>46190</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="J46" s="133" t="s">
+      <c r="J46" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="K46" s="133"/>
-      <c r="L46" s="133"/>
-      <c r="M46" s="133"/>
-      <c r="N46" s="133"/>
+      <c r="K46" s="121"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
       <c r="O46" s="10">
         <v>46196</v>
       </c>
       <c r="P46" s="3"/>
-      <c r="S46" s="130" t="s">
+      <c r="S46" s="128" t="s">
         <v>150</v>
       </c>
-      <c r="T46" s="130"/>
-      <c r="U46" s="130"/>
-      <c r="V46" s="130"/>
-      <c r="W46" s="130"/>
+      <c r="T46" s="128"/>
+      <c r="U46" s="128"/>
+      <c r="V46" s="128"/>
+      <c r="W46" s="128"/>
       <c r="X46" s="10">
         <v>46200</v>
       </c>
@@ -5998,15 +5998,15 @@
         <f t="shared" si="156"/>
         <v>Coreia do Sul</v>
       </c>
-      <c r="AD46" s="102">
+      <c r="AD46" s="115">
         <f t="shared" si="157"/>
         <v>2</v>
       </c>
-      <c r="AE46" s="102">
+      <c r="AE46" s="115">
         <f t="shared" si="158"/>
         <v>-4</v>
       </c>
-      <c r="AF46" s="102">
+      <c r="AF46" s="115">
         <f t="shared" si="159"/>
         <v>1</v>
       </c>
@@ -6014,29 +6014,29 @@
         <f t="shared" si="160"/>
         <v>A</v>
       </c>
-      <c r="AJ46" s="100"/>
-      <c r="AK46" s="100"/>
-      <c r="AL46" s="100"/>
-      <c r="AM46" s="100"/>
-      <c r="AP46" s="100"/>
-      <c r="AQ46" s="100"/>
-      <c r="AR46" s="100"/>
-      <c r="AS46" s="100"/>
-      <c r="AV46" s="100"/>
-      <c r="AW46" s="100"/>
-      <c r="AX46" s="100"/>
+      <c r="AJ46" s="112"/>
+      <c r="AK46" s="112"/>
+      <c r="AL46" s="112"/>
+      <c r="AM46" s="112"/>
+      <c r="AP46" s="112"/>
+      <c r="AQ46" s="112"/>
+      <c r="AR46" s="112"/>
+      <c r="AS46" s="112"/>
+      <c r="AV46" s="112"/>
+      <c r="AW46" s="112"/>
+      <c r="AX46" s="112"/>
     </row>
     <row r="47" spans="1:50">
       <c r="A47" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="100">
+      <c r="B47" s="112">
         <v>3</v>
       </c>
-      <c r="C47" s="104" t="s">
+      <c r="C47" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="100">
+      <c r="D47" s="112">
         <v>2</v>
       </c>
       <c r="E47" s="34" t="s">
@@ -6056,13 +6056,13 @@
       <c r="J47" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="K47" s="100">
+      <c r="K47" s="112">
         <v>0</v>
       </c>
-      <c r="L47" s="104" t="s">
+      <c r="L47" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="M47" s="100">
+      <c r="M47" s="112">
         <v>4</v>
       </c>
       <c r="N47" s="34" t="s">
@@ -6082,13 +6082,13 @@
       <c r="S47" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="T47" s="100">
+      <c r="T47" s="112">
         <v>2</v>
       </c>
-      <c r="U47" s="111" t="s">
+      <c r="U47" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="V47" s="100">
+      <c r="V47" s="112">
         <v>0</v>
       </c>
       <c r="W47" s="36" t="s">
@@ -6112,15 +6112,15 @@
         <f t="shared" si="156"/>
         <v>Irã</v>
       </c>
-      <c r="AD47" s="102">
+      <c r="AD47" s="115">
         <f t="shared" si="157"/>
         <v>1</v>
       </c>
-      <c r="AE47" s="102">
+      <c r="AE47" s="115">
         <f t="shared" si="158"/>
         <v>-3</v>
       </c>
-      <c r="AF47" s="102">
+      <c r="AF47" s="115">
         <f t="shared" si="159"/>
         <v>1</v>
       </c>
@@ -6128,17 +6128,17 @@
         <f t="shared" si="160"/>
         <v>G</v>
       </c>
-      <c r="AJ47" s="100"/>
-      <c r="AK47" s="100"/>
-      <c r="AL47" s="100"/>
-      <c r="AM47" s="100"/>
-      <c r="AP47" s="100"/>
-      <c r="AQ47" s="100"/>
-      <c r="AR47" s="100"/>
-      <c r="AS47" s="100"/>
-      <c r="AV47" s="100"/>
-      <c r="AW47" s="100"/>
-      <c r="AX47" s="100"/>
+      <c r="AJ47" s="112"/>
+      <c r="AK47" s="112"/>
+      <c r="AL47" s="112"/>
+      <c r="AM47" s="112"/>
+      <c r="AP47" s="112"/>
+      <c r="AQ47" s="112"/>
+      <c r="AR47" s="112"/>
+      <c r="AS47" s="112"/>
+      <c r="AV47" s="112"/>
+      <c r="AW47" s="112"/>
+      <c r="AX47" s="112"/>
     </row>
     <row r="48" spans="1:50">
       <c r="A48" s="129" t="s">
@@ -6163,13 +6163,13 @@
         <v>46196</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="S48" s="130" t="s">
+      <c r="S48" s="128" t="s">
         <v>153</v>
       </c>
-      <c r="T48" s="130"/>
-      <c r="U48" s="130"/>
-      <c r="V48" s="130"/>
-      <c r="W48" s="130"/>
+      <c r="T48" s="128"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="128"/>
+      <c r="W48" s="128"/>
       <c r="X48" s="10">
         <v>46200</v>
       </c>
@@ -6180,15 +6180,15 @@
         <f t="shared" si="156"/>
         <v>Áustria</v>
       </c>
-      <c r="AD48" s="102">
+      <c r="AD48" s="115">
         <f t="shared" si="157"/>
         <v>1</v>
       </c>
-      <c r="AE48" s="102">
+      <c r="AE48" s="115">
         <f t="shared" si="158"/>
         <v>-4</v>
       </c>
-      <c r="AF48" s="102">
+      <c r="AF48" s="115">
         <f t="shared" si="159"/>
         <v>3</v>
       </c>
@@ -6196,29 +6196,29 @@
         <f t="shared" si="160"/>
         <v>J</v>
       </c>
-      <c r="AJ48" s="100"/>
-      <c r="AK48" s="100"/>
-      <c r="AL48" s="100"/>
-      <c r="AM48" s="100"/>
-      <c r="AP48" s="100"/>
-      <c r="AQ48" s="100"/>
-      <c r="AR48" s="100"/>
-      <c r="AS48" s="100"/>
-      <c r="AV48" s="100"/>
-      <c r="AW48" s="100"/>
-      <c r="AX48" s="100"/>
+      <c r="AJ48" s="112"/>
+      <c r="AK48" s="112"/>
+      <c r="AL48" s="112"/>
+      <c r="AM48" s="112"/>
+      <c r="AP48" s="112"/>
+      <c r="AQ48" s="112"/>
+      <c r="AR48" s="112"/>
+      <c r="AS48" s="112"/>
+      <c r="AV48" s="112"/>
+      <c r="AW48" s="112"/>
+      <c r="AX48" s="112"/>
     </row>
     <row r="49" spans="1:50">
       <c r="A49" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="100">
+      <c r="B49" s="112">
         <v>0</v>
       </c>
-      <c r="C49" s="112" t="s">
+      <c r="C49" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="D49" s="100">
+      <c r="D49" s="112">
         <v>5</v>
       </c>
       <c r="E49" s="38" t="s">
@@ -6238,13 +6238,13 @@
       <c r="J49" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="K49" s="100">
+      <c r="K49" s="112">
         <v>5</v>
       </c>
-      <c r="L49" s="112" t="s">
+      <c r="L49" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="M49" s="100">
+      <c r="M49" s="112">
         <v>0</v>
       </c>
       <c r="N49" s="38" t="s">
@@ -6264,13 +6264,13 @@
       <c r="S49" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="T49" s="100">
+      <c r="T49" s="112">
         <v>0</v>
       </c>
-      <c r="U49" s="111" t="s">
+      <c r="U49" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="V49" s="100">
+      <c r="V49" s="112">
         <v>4</v>
       </c>
       <c r="W49" s="36" t="s">
@@ -6294,15 +6294,15 @@
         <f t="shared" si="156"/>
         <v>Uzbequistão</v>
       </c>
-      <c r="AD49" s="102">
+      <c r="AD49" s="115">
         <f t="shared" si="157"/>
         <v>1</v>
       </c>
-      <c r="AE49" s="102">
+      <c r="AE49" s="115">
         <f t="shared" si="158"/>
         <v>-8</v>
       </c>
-      <c r="AF49" s="102">
+      <c r="AF49" s="115">
         <f t="shared" si="159"/>
         <v>2</v>
       </c>
@@ -6310,104 +6310,104 @@
         <f t="shared" si="160"/>
         <v>K</v>
       </c>
-      <c r="AJ49" s="100"/>
-      <c r="AK49" s="100"/>
-      <c r="AL49" s="100"/>
-      <c r="AM49" s="100"/>
-      <c r="AP49" s="100"/>
-      <c r="AQ49" s="100"/>
-      <c r="AR49" s="100"/>
-      <c r="AS49" s="100"/>
-      <c r="AV49" s="100"/>
-      <c r="AW49" s="100"/>
-      <c r="AX49" s="100"/>
+      <c r="AJ49" s="112"/>
+      <c r="AK49" s="112"/>
+      <c r="AL49" s="112"/>
+      <c r="AM49" s="112"/>
+      <c r="AP49" s="112"/>
+      <c r="AQ49" s="112"/>
+      <c r="AR49" s="112"/>
+      <c r="AS49" s="112"/>
+      <c r="AV49" s="112"/>
+      <c r="AW49" s="112"/>
+      <c r="AX49" s="112"/>
     </row>
     <row r="50" spans="1:50">
       <c r="F50" s="7"/>
-      <c r="AD50" s="100"/>
-      <c r="AE50" s="100"/>
-      <c r="AF50" s="100"/>
-      <c r="AJ50" s="100"/>
-      <c r="AK50" s="100"/>
-      <c r="AL50" s="100"/>
-      <c r="AM50" s="100"/>
-      <c r="AP50" s="100"/>
-      <c r="AQ50" s="100"/>
-      <c r="AR50" s="100"/>
-      <c r="AS50" s="100"/>
-      <c r="AV50" s="100"/>
-      <c r="AW50" s="100"/>
-      <c r="AX50" s="100"/>
+      <c r="AD50" s="112"/>
+      <c r="AE50" s="112"/>
+      <c r="AF50" s="112"/>
+      <c r="AJ50" s="112"/>
+      <c r="AK50" s="112"/>
+      <c r="AL50" s="112"/>
+      <c r="AM50" s="112"/>
+      <c r="AP50" s="112"/>
+      <c r="AQ50" s="112"/>
+      <c r="AR50" s="112"/>
+      <c r="AS50" s="112"/>
+      <c r="AV50" s="112"/>
+      <c r="AW50" s="112"/>
+      <c r="AX50" s="112"/>
     </row>
     <row r="51" spans="1:50">
-      <c r="S51" s="132"/>
-      <c r="T51" s="132"/>
-      <c r="U51" s="132"/>
-      <c r="V51" s="132"/>
-      <c r="W51" s="132"/>
-      <c r="AD51" s="100"/>
-      <c r="AE51" s="100"/>
-      <c r="AF51" s="100"/>
-      <c r="AJ51" s="100"/>
-      <c r="AK51" s="100"/>
-      <c r="AL51" s="100"/>
-      <c r="AM51" s="100"/>
-      <c r="AP51" s="100"/>
-      <c r="AQ51" s="100"/>
-      <c r="AR51" s="100"/>
-      <c r="AS51" s="100"/>
-      <c r="AV51" s="100"/>
-      <c r="AW51" s="100"/>
-      <c r="AX51" s="100"/>
+      <c r="S51" s="117"/>
+      <c r="T51" s="117"/>
+      <c r="U51" s="117"/>
+      <c r="V51" s="117"/>
+      <c r="W51" s="117"/>
+      <c r="AD51" s="112"/>
+      <c r="AE51" s="112"/>
+      <c r="AF51" s="112"/>
+      <c r="AJ51" s="112"/>
+      <c r="AK51" s="112"/>
+      <c r="AL51" s="112"/>
+      <c r="AM51" s="112"/>
+      <c r="AP51" s="112"/>
+      <c r="AQ51" s="112"/>
+      <c r="AR51" s="112"/>
+      <c r="AS51" s="112"/>
+      <c r="AV51" s="112"/>
+      <c r="AW51" s="112"/>
+      <c r="AX51" s="112"/>
     </row>
     <row r="52" spans="1:50">
-      <c r="A52" s="134" t="s">
+      <c r="A52" s="118" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="134"/>
-      <c r="C52" s="134"/>
-      <c r="D52" s="134"/>
-      <c r="E52" s="134"/>
-      <c r="AD52" s="100"/>
-      <c r="AE52" s="100"/>
-      <c r="AF52" s="100"/>
-      <c r="AJ52" s="100"/>
-      <c r="AK52" s="100"/>
-      <c r="AL52" s="100"/>
-      <c r="AM52" s="100"/>
-      <c r="AP52" s="100"/>
-      <c r="AQ52" s="100"/>
-      <c r="AR52" s="100"/>
-      <c r="AS52" s="100"/>
-      <c r="AV52" s="100"/>
-      <c r="AW52" s="100"/>
-      <c r="AX52" s="100"/>
+      <c r="B52" s="118"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="AD52" s="112"/>
+      <c r="AE52" s="112"/>
+      <c r="AF52" s="112"/>
+      <c r="AJ52" s="112"/>
+      <c r="AK52" s="112"/>
+      <c r="AL52" s="112"/>
+      <c r="AM52" s="112"/>
+      <c r="AP52" s="112"/>
+      <c r="AQ52" s="112"/>
+      <c r="AR52" s="112"/>
+      <c r="AS52" s="112"/>
+      <c r="AV52" s="112"/>
+      <c r="AW52" s="112"/>
+      <c r="AX52" s="112"/>
     </row>
     <row r="53" spans="1:50">
-      <c r="A53" s="121" t="s">
+      <c r="A53" s="116" t="s">
         <v>155</v>
       </c>
-      <c r="B53" s="121"/>
-      <c r="C53" s="121"/>
-      <c r="D53" s="121"/>
-      <c r="E53" s="121"/>
+      <c r="B53" s="116"/>
+      <c r="C53" s="116"/>
+      <c r="D53" s="116"/>
+      <c r="E53" s="116"/>
       <c r="F53" s="10">
         <v>46201</v>
       </c>
-      <c r="AD53" s="100"/>
-      <c r="AE53" s="100"/>
-      <c r="AF53" s="100"/>
-      <c r="AJ53" s="100"/>
-      <c r="AK53" s="100"/>
-      <c r="AL53" s="100"/>
-      <c r="AM53" s="100"/>
-      <c r="AP53" s="100"/>
-      <c r="AQ53" s="100"/>
-      <c r="AR53" s="100"/>
-      <c r="AS53" s="100"/>
-      <c r="AV53" s="100"/>
-      <c r="AW53" s="100"/>
-      <c r="AX53" s="100"/>
+      <c r="AD53" s="112"/>
+      <c r="AE53" s="112"/>
+      <c r="AF53" s="112"/>
+      <c r="AJ53" s="112"/>
+      <c r="AK53" s="112"/>
+      <c r="AL53" s="112"/>
+      <c r="AM53" s="112"/>
+      <c r="AP53" s="112"/>
+      <c r="AQ53" s="112"/>
+      <c r="AR53" s="112"/>
+      <c r="AS53" s="112"/>
+      <c r="AV53" s="112"/>
+      <c r="AW53" s="112"/>
+      <c r="AX53" s="112"/>
     </row>
     <row r="54" spans="1:50">
       <c r="A54" s="80" t="str">
@@ -6417,7 +6417,7 @@
       <c r="B54" s="2">
         <v>1</v>
       </c>
-      <c r="C54" s="99" t="s">
+      <c r="C54" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="4">
@@ -6430,69 +6430,69 @@
       <c r="F54" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD54" s="100"/>
-      <c r="AE54" s="100"/>
-      <c r="AF54" s="100"/>
-      <c r="AJ54" s="100"/>
-      <c r="AK54" s="100"/>
-      <c r="AL54" s="100"/>
-      <c r="AM54" s="100"/>
-      <c r="AP54" s="100"/>
-      <c r="AQ54" s="100"/>
-      <c r="AR54" s="100"/>
-      <c r="AS54" s="100"/>
-      <c r="AV54" s="100"/>
-      <c r="AW54" s="100"/>
-      <c r="AX54" s="100"/>
+      <c r="AD54" s="112"/>
+      <c r="AE54" s="112"/>
+      <c r="AF54" s="112"/>
+      <c r="AJ54" s="112"/>
+      <c r="AK54" s="112"/>
+      <c r="AL54" s="112"/>
+      <c r="AM54" s="112"/>
+      <c r="AP54" s="112"/>
+      <c r="AQ54" s="112"/>
+      <c r="AR54" s="112"/>
+      <c r="AS54" s="112"/>
+      <c r="AV54" s="112"/>
+      <c r="AW54" s="112"/>
+      <c r="AX54" s="112"/>
     </row>
     <row r="55" spans="1:50">
       <c r="A55" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C55" s="99" t="s">
+      <c r="C55" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E55" s="83"/>
-      <c r="AD55" s="100"/>
-      <c r="AE55" s="100"/>
-      <c r="AF55" s="100"/>
-      <c r="AJ55" s="100"/>
-      <c r="AK55" s="100"/>
-      <c r="AL55" s="100"/>
-      <c r="AM55" s="100"/>
-      <c r="AP55" s="100"/>
-      <c r="AQ55" s="100"/>
-      <c r="AR55" s="100"/>
-      <c r="AS55" s="100"/>
-      <c r="AV55" s="100"/>
-      <c r="AW55" s="100"/>
-      <c r="AX55" s="100"/>
+      <c r="AD55" s="112"/>
+      <c r="AE55" s="112"/>
+      <c r="AF55" s="112"/>
+      <c r="AJ55" s="112"/>
+      <c r="AK55" s="112"/>
+      <c r="AL55" s="112"/>
+      <c r="AM55" s="112"/>
+      <c r="AP55" s="112"/>
+      <c r="AQ55" s="112"/>
+      <c r="AR55" s="112"/>
+      <c r="AS55" s="112"/>
+      <c r="AV55" s="112"/>
+      <c r="AW55" s="112"/>
+      <c r="AX55" s="112"/>
     </row>
     <row r="56" spans="1:50">
-      <c r="A56" s="121" t="s">
+      <c r="A56" s="116" t="s">
         <v>158</v>
       </c>
-      <c r="B56" s="121"/>
-      <c r="C56" s="121"/>
-      <c r="D56" s="121"/>
-      <c r="E56" s="121"/>
+      <c r="B56" s="116"/>
+      <c r="C56" s="116"/>
+      <c r="D56" s="116"/>
+      <c r="E56" s="116"/>
       <c r="F56" s="10">
         <v>46202</v>
       </c>
-      <c r="AD56" s="100"/>
-      <c r="AE56" s="100"/>
-      <c r="AF56" s="100"/>
-      <c r="AJ56" s="100"/>
-      <c r="AK56" s="100"/>
-      <c r="AL56" s="100"/>
-      <c r="AM56" s="100"/>
-      <c r="AP56" s="100"/>
-      <c r="AQ56" s="100"/>
-      <c r="AR56" s="100"/>
-      <c r="AS56" s="100"/>
-      <c r="AV56" s="100"/>
-      <c r="AW56" s="100"/>
-      <c r="AX56" s="100"/>
+      <c r="AD56" s="112"/>
+      <c r="AE56" s="112"/>
+      <c r="AF56" s="112"/>
+      <c r="AJ56" s="112"/>
+      <c r="AK56" s="112"/>
+      <c r="AL56" s="112"/>
+      <c r="AM56" s="112"/>
+      <c r="AP56" s="112"/>
+      <c r="AQ56" s="112"/>
+      <c r="AR56" s="112"/>
+      <c r="AS56" s="112"/>
+      <c r="AV56" s="112"/>
+      <c r="AW56" s="112"/>
+      <c r="AX56" s="112"/>
     </row>
     <row r="57" spans="1:50">
       <c r="A57" s="80" t="str">
@@ -6502,7 +6502,7 @@
       <c r="B57" s="2">
         <v>2</v>
       </c>
-      <c r="C57" s="99" t="s">
+      <c r="C57" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D57" s="4">
@@ -6515,69 +6515,69 @@
       <c r="F57" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="AD57" s="100"/>
-      <c r="AE57" s="100"/>
-      <c r="AF57" s="100"/>
-      <c r="AJ57" s="100"/>
-      <c r="AK57" s="100"/>
-      <c r="AL57" s="100"/>
-      <c r="AM57" s="100"/>
-      <c r="AP57" s="100"/>
-      <c r="AQ57" s="100"/>
-      <c r="AR57" s="100"/>
-      <c r="AS57" s="100"/>
-      <c r="AV57" s="100"/>
-      <c r="AW57" s="100"/>
-      <c r="AX57" s="100"/>
+      <c r="AD57" s="112"/>
+      <c r="AE57" s="112"/>
+      <c r="AF57" s="112"/>
+      <c r="AJ57" s="112"/>
+      <c r="AK57" s="112"/>
+      <c r="AL57" s="112"/>
+      <c r="AM57" s="112"/>
+      <c r="AP57" s="112"/>
+      <c r="AQ57" s="112"/>
+      <c r="AR57" s="112"/>
+      <c r="AS57" s="112"/>
+      <c r="AV57" s="112"/>
+      <c r="AW57" s="112"/>
+      <c r="AX57" s="112"/>
     </row>
     <row r="58" spans="1:50">
       <c r="A58" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="99" t="s">
+      <c r="C58" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E58" s="83"/>
-      <c r="AD58" s="100"/>
-      <c r="AE58" s="100"/>
-      <c r="AF58" s="100"/>
-      <c r="AJ58" s="100"/>
-      <c r="AK58" s="100"/>
-      <c r="AL58" s="100"/>
-      <c r="AM58" s="100"/>
-      <c r="AP58" s="100"/>
-      <c r="AQ58" s="100"/>
-      <c r="AR58" s="100"/>
-      <c r="AS58" s="100"/>
-      <c r="AV58" s="100"/>
-      <c r="AW58" s="100"/>
-      <c r="AX58" s="100"/>
+      <c r="AD58" s="112"/>
+      <c r="AE58" s="112"/>
+      <c r="AF58" s="112"/>
+      <c r="AJ58" s="112"/>
+      <c r="AK58" s="112"/>
+      <c r="AL58" s="112"/>
+      <c r="AM58" s="112"/>
+      <c r="AP58" s="112"/>
+      <c r="AQ58" s="112"/>
+      <c r="AR58" s="112"/>
+      <c r="AS58" s="112"/>
+      <c r="AV58" s="112"/>
+      <c r="AW58" s="112"/>
+      <c r="AX58" s="112"/>
     </row>
     <row r="59" spans="1:50">
-      <c r="A59" s="121" t="s">
+      <c r="A59" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="B59" s="121"/>
-      <c r="C59" s="121"/>
-      <c r="D59" s="121"/>
-      <c r="E59" s="121"/>
+      <c r="B59" s="116"/>
+      <c r="C59" s="116"/>
+      <c r="D59" s="116"/>
+      <c r="E59" s="116"/>
       <c r="F59" s="10">
         <v>46202</v>
       </c>
-      <c r="AD59" s="100"/>
-      <c r="AE59" s="100"/>
-      <c r="AF59" s="100"/>
-      <c r="AJ59" s="100"/>
-      <c r="AK59" s="100"/>
-      <c r="AL59" s="100"/>
-      <c r="AM59" s="100"/>
-      <c r="AP59" s="100"/>
-      <c r="AQ59" s="100"/>
-      <c r="AR59" s="100"/>
-      <c r="AS59" s="100"/>
-      <c r="AV59" s="100"/>
-      <c r="AW59" s="100"/>
-      <c r="AX59" s="100"/>
+      <c r="AD59" s="112"/>
+      <c r="AE59" s="112"/>
+      <c r="AF59" s="112"/>
+      <c r="AJ59" s="112"/>
+      <c r="AK59" s="112"/>
+      <c r="AL59" s="112"/>
+      <c r="AM59" s="112"/>
+      <c r="AP59" s="112"/>
+      <c r="AQ59" s="112"/>
+      <c r="AR59" s="112"/>
+      <c r="AS59" s="112"/>
+      <c r="AV59" s="112"/>
+      <c r="AW59" s="112"/>
+      <c r="AX59" s="112"/>
     </row>
     <row r="60" spans="1:50">
       <c r="A60" s="80" t="str">
@@ -6587,7 +6587,7 @@
       <c r="B60" s="2">
         <v>1</v>
       </c>
-      <c r="C60" s="99" t="s">
+      <c r="C60" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D60" s="4">
@@ -6600,20 +6600,20 @@
       <c r="F60" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AD60" s="100"/>
-      <c r="AE60" s="100"/>
-      <c r="AF60" s="100"/>
-      <c r="AJ60" s="100"/>
-      <c r="AK60" s="100"/>
-      <c r="AL60" s="100"/>
-      <c r="AM60" s="100"/>
-      <c r="AP60" s="100"/>
-      <c r="AQ60" s="100"/>
-      <c r="AR60" s="100"/>
-      <c r="AS60" s="100"/>
-      <c r="AV60" s="100"/>
-      <c r="AW60" s="100"/>
-      <c r="AX60" s="100"/>
+      <c r="AD60" s="112"/>
+      <c r="AE60" s="112"/>
+      <c r="AF60" s="112"/>
+      <c r="AJ60" s="112"/>
+      <c r="AK60" s="112"/>
+      <c r="AL60" s="112"/>
+      <c r="AM60" s="112"/>
+      <c r="AP60" s="112"/>
+      <c r="AQ60" s="112"/>
+      <c r="AR60" s="112"/>
+      <c r="AS60" s="112"/>
+      <c r="AV60" s="112"/>
+      <c r="AW60" s="112"/>
+      <c r="AX60" s="112"/>
     </row>
     <row r="61" spans="1:50">
       <c r="A61" s="81" t="s">
@@ -6622,70 +6622,70 @@
       <c r="B61" s="2">
         <v>4</v>
       </c>
-      <c r="C61" s="99" t="s">
+      <c r="C61" s="101" t="s">
         <v>157</v>
       </c>
       <c r="D61" s="4">
         <v>3</v>
       </c>
       <c r="E61" s="83"/>
-      <c r="J61" s="134" t="s">
+      <c r="J61" s="118" t="s">
         <v>161</v>
       </c>
-      <c r="K61" s="134"/>
-      <c r="L61" s="134"/>
-      <c r="M61" s="134"/>
-      <c r="N61" s="134"/>
-      <c r="AD61" s="100"/>
-      <c r="AE61" s="100"/>
-      <c r="AF61" s="100"/>
-      <c r="AJ61" s="100"/>
-      <c r="AK61" s="100"/>
-      <c r="AL61" s="100"/>
-      <c r="AM61" s="100"/>
-      <c r="AP61" s="100"/>
-      <c r="AQ61" s="100"/>
-      <c r="AR61" s="100"/>
-      <c r="AS61" s="100"/>
-      <c r="AV61" s="100"/>
-      <c r="AW61" s="100"/>
-      <c r="AX61" s="100"/>
+      <c r="K61" s="118"/>
+      <c r="L61" s="118"/>
+      <c r="M61" s="118"/>
+      <c r="N61" s="118"/>
+      <c r="AD61" s="112"/>
+      <c r="AE61" s="112"/>
+      <c r="AF61" s="112"/>
+      <c r="AJ61" s="112"/>
+      <c r="AK61" s="112"/>
+      <c r="AL61" s="112"/>
+      <c r="AM61" s="112"/>
+      <c r="AP61" s="112"/>
+      <c r="AQ61" s="112"/>
+      <c r="AR61" s="112"/>
+      <c r="AS61" s="112"/>
+      <c r="AV61" s="112"/>
+      <c r="AW61" s="112"/>
+      <c r="AX61" s="112"/>
     </row>
     <row r="62" spans="1:50">
-      <c r="A62" s="121" t="s">
+      <c r="A62" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="121"/>
-      <c r="C62" s="121"/>
-      <c r="D62" s="121"/>
-      <c r="E62" s="121"/>
+      <c r="B62" s="116"/>
+      <c r="C62" s="116"/>
+      <c r="D62" s="116"/>
+      <c r="E62" s="116"/>
       <c r="F62" s="10">
         <v>46202</v>
       </c>
-      <c r="J62" s="121" t="s">
+      <c r="J62" s="116" t="s">
         <v>163</v>
       </c>
-      <c r="K62" s="121"/>
-      <c r="L62" s="121"/>
-      <c r="M62" s="121"/>
-      <c r="N62" s="121"/>
+      <c r="K62" s="116"/>
+      <c r="L62" s="116"/>
+      <c r="M62" s="116"/>
+      <c r="N62" s="116"/>
       <c r="O62" s="10">
         <v>46207</v>
       </c>
-      <c r="AD62" s="100"/>
-      <c r="AE62" s="100"/>
-      <c r="AF62" s="100"/>
-      <c r="AJ62" s="100"/>
-      <c r="AK62" s="100"/>
-      <c r="AL62" s="100"/>
-      <c r="AM62" s="100"/>
-      <c r="AP62" s="100"/>
-      <c r="AQ62" s="100"/>
-      <c r="AR62" s="100"/>
-      <c r="AS62" s="100"/>
-      <c r="AV62" s="100"/>
-      <c r="AW62" s="100"/>
-      <c r="AX62" s="100"/>
+      <c r="AD62" s="112"/>
+      <c r="AE62" s="112"/>
+      <c r="AF62" s="112"/>
+      <c r="AJ62" s="112"/>
+      <c r="AK62" s="112"/>
+      <c r="AL62" s="112"/>
+      <c r="AM62" s="112"/>
+      <c r="AP62" s="112"/>
+      <c r="AQ62" s="112"/>
+      <c r="AR62" s="112"/>
+      <c r="AS62" s="112"/>
+      <c r="AV62" s="112"/>
+      <c r="AW62" s="112"/>
+      <c r="AX62" s="112"/>
     </row>
     <row r="63" spans="1:50">
       <c r="A63" s="80" t="str">
@@ -6695,7 +6695,7 @@
       <c r="B63" s="2">
         <v>0</v>
       </c>
-      <c r="C63" s="99" t="s">
+      <c r="C63" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D63" s="4">
@@ -6715,7 +6715,7 @@
       <c r="K63" s="1">
         <v>1</v>
       </c>
-      <c r="L63" s="99" t="s">
+      <c r="L63" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M63">
@@ -6728,20 +6728,20 @@
       <c r="O63" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AD63" s="100"/>
-      <c r="AE63" s="100"/>
-      <c r="AF63" s="100"/>
-      <c r="AJ63" s="100"/>
-      <c r="AK63" s="100"/>
-      <c r="AL63" s="100"/>
-      <c r="AM63" s="100"/>
-      <c r="AP63" s="100"/>
-      <c r="AQ63" s="100"/>
-      <c r="AR63" s="100"/>
-      <c r="AS63" s="100"/>
-      <c r="AV63" s="100"/>
-      <c r="AW63" s="100"/>
-      <c r="AX63" s="100"/>
+      <c r="AD63" s="112"/>
+      <c r="AE63" s="112"/>
+      <c r="AF63" s="112"/>
+      <c r="AJ63" s="112"/>
+      <c r="AK63" s="112"/>
+      <c r="AL63" s="112"/>
+      <c r="AM63" s="112"/>
+      <c r="AP63" s="112"/>
+      <c r="AQ63" s="112"/>
+      <c r="AR63" s="112"/>
+      <c r="AS63" s="112"/>
+      <c r="AV63" s="112"/>
+      <c r="AW63" s="112"/>
+      <c r="AX63" s="112"/>
     </row>
     <row r="64" spans="1:50">
       <c r="A64" s="81" t="s">
@@ -6750,7 +6750,7 @@
       <c r="B64" s="2">
         <v>5</v>
       </c>
-      <c r="C64" s="99" t="s">
+      <c r="C64" s="101" t="s">
         <v>157</v>
       </c>
       <c r="D64" s="4">
@@ -6760,60 +6760,60 @@
       <c r="J64" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L64" s="99" t="s">
+      <c r="L64" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N64" s="83"/>
-      <c r="AD64" s="100"/>
-      <c r="AE64" s="100"/>
-      <c r="AF64" s="100"/>
-      <c r="AJ64" s="100"/>
-      <c r="AK64" s="100"/>
-      <c r="AL64" s="100"/>
-      <c r="AM64" s="100"/>
-      <c r="AP64" s="100"/>
-      <c r="AQ64" s="100"/>
-      <c r="AR64" s="100"/>
-      <c r="AS64" s="100"/>
-      <c r="AV64" s="100"/>
-      <c r="AW64" s="100"/>
-      <c r="AX64" s="100"/>
+      <c r="AD64" s="112"/>
+      <c r="AE64" s="112"/>
+      <c r="AF64" s="112"/>
+      <c r="AJ64" s="112"/>
+      <c r="AK64" s="112"/>
+      <c r="AL64" s="112"/>
+      <c r="AM64" s="112"/>
+      <c r="AP64" s="112"/>
+      <c r="AQ64" s="112"/>
+      <c r="AR64" s="112"/>
+      <c r="AS64" s="112"/>
+      <c r="AV64" s="112"/>
+      <c r="AW64" s="112"/>
+      <c r="AX64" s="112"/>
     </row>
     <row r="65" spans="1:60">
-      <c r="A65" s="121" t="s">
+      <c r="A65" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="B65" s="121"/>
-      <c r="C65" s="121"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="121"/>
+      <c r="B65" s="116"/>
+      <c r="C65" s="116"/>
+      <c r="D65" s="116"/>
+      <c r="E65" s="116"/>
       <c r="F65" s="10">
         <v>46203</v>
       </c>
-      <c r="J65" s="121" t="s">
+      <c r="J65" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="K65" s="121"/>
-      <c r="L65" s="121"/>
-      <c r="M65" s="121"/>
-      <c r="N65" s="121"/>
+      <c r="K65" s="116"/>
+      <c r="L65" s="116"/>
+      <c r="M65" s="116"/>
+      <c r="N65" s="116"/>
       <c r="O65" s="10">
         <v>46207</v>
       </c>
-      <c r="AD65" s="100"/>
-      <c r="AE65" s="100"/>
-      <c r="AF65" s="100"/>
-      <c r="AJ65" s="100"/>
-      <c r="AK65" s="100"/>
-      <c r="AL65" s="100"/>
-      <c r="AM65" s="100"/>
-      <c r="AP65" s="100"/>
-      <c r="AQ65" s="100"/>
-      <c r="AR65" s="100"/>
-      <c r="AS65" s="100"/>
-      <c r="AV65" s="100"/>
-      <c r="AW65" s="100"/>
-      <c r="AX65" s="100"/>
+      <c r="AD65" s="112"/>
+      <c r="AE65" s="112"/>
+      <c r="AF65" s="112"/>
+      <c r="AJ65" s="112"/>
+      <c r="AK65" s="112"/>
+      <c r="AL65" s="112"/>
+      <c r="AM65" s="112"/>
+      <c r="AP65" s="112"/>
+      <c r="AQ65" s="112"/>
+      <c r="AR65" s="112"/>
+      <c r="AS65" s="112"/>
+      <c r="AV65" s="112"/>
+      <c r="AW65" s="112"/>
+      <c r="AX65" s="112"/>
     </row>
     <row r="66" spans="1:60">
       <c r="A66" s="80" t="str">
@@ -6823,7 +6823,7 @@
       <c r="B66" s="2">
         <v>3</v>
       </c>
-      <c r="C66" s="99" t="s">
+      <c r="C66" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D66" s="4">
@@ -6843,7 +6843,7 @@
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="99" t="s">
+      <c r="L66" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M66">
@@ -6856,86 +6856,86 @@
       <c r="O66" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AD66" s="100"/>
-      <c r="AE66" s="100"/>
-      <c r="AF66" s="100"/>
-      <c r="AJ66" s="100"/>
-      <c r="AK66" s="100"/>
-      <c r="AL66" s="100"/>
-      <c r="AM66" s="100"/>
-      <c r="AP66" s="100"/>
-      <c r="AQ66" s="100"/>
-      <c r="AR66" s="100"/>
-      <c r="AS66" s="100"/>
-      <c r="AV66" s="100"/>
-      <c r="AW66" s="100"/>
-      <c r="AX66" s="100"/>
+      <c r="AD66" s="112"/>
+      <c r="AE66" s="112"/>
+      <c r="AF66" s="112"/>
+      <c r="AJ66" s="112"/>
+      <c r="AK66" s="112"/>
+      <c r="AL66" s="112"/>
+      <c r="AM66" s="112"/>
+      <c r="AP66" s="112"/>
+      <c r="AQ66" s="112"/>
+      <c r="AR66" s="112"/>
+      <c r="AS66" s="112"/>
+      <c r="AV66" s="112"/>
+      <c r="AW66" s="112"/>
+      <c r="AX66" s="112"/>
     </row>
     <row r="67" spans="1:60">
       <c r="A67" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C67" s="99" t="s">
+      <c r="C67" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E67" s="83"/>
       <c r="J67" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L67" s="99" t="s">
+      <c r="L67" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N67" s="83"/>
-      <c r="AD67" s="100"/>
-      <c r="AE67" s="100"/>
-      <c r="AF67" s="100"/>
-      <c r="AJ67" s="100"/>
-      <c r="AK67" s="100"/>
-      <c r="AL67" s="100"/>
-      <c r="AM67" s="100"/>
-      <c r="AP67" s="100"/>
-      <c r="AQ67" s="100"/>
-      <c r="AR67" s="100"/>
-      <c r="AS67" s="100"/>
-      <c r="AV67" s="100"/>
-      <c r="AW67" s="100"/>
-      <c r="AX67" s="100"/>
+      <c r="AD67" s="112"/>
+      <c r="AE67" s="112"/>
+      <c r="AF67" s="112"/>
+      <c r="AJ67" s="112"/>
+      <c r="AK67" s="112"/>
+      <c r="AL67" s="112"/>
+      <c r="AM67" s="112"/>
+      <c r="AP67" s="112"/>
+      <c r="AQ67" s="112"/>
+      <c r="AR67" s="112"/>
+      <c r="AS67" s="112"/>
+      <c r="AV67" s="112"/>
+      <c r="AW67" s="112"/>
+      <c r="AX67" s="112"/>
     </row>
     <row r="68" spans="1:60">
-      <c r="A68" s="121" t="s">
+      <c r="A68" s="116" t="s">
         <v>166</v>
       </c>
-      <c r="B68" s="121"/>
-      <c r="C68" s="121"/>
-      <c r="D68" s="121"/>
-      <c r="E68" s="121"/>
+      <c r="B68" s="116"/>
+      <c r="C68" s="116"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="116"/>
       <c r="F68" s="10">
         <v>46203</v>
       </c>
-      <c r="J68" s="121" t="s">
+      <c r="J68" s="116" t="s">
         <v>167</v>
       </c>
-      <c r="K68" s="121"/>
-      <c r="L68" s="121"/>
-      <c r="M68" s="121"/>
-      <c r="N68" s="121"/>
+      <c r="K68" s="116"/>
+      <c r="L68" s="116"/>
+      <c r="M68" s="116"/>
+      <c r="N68" s="116"/>
       <c r="O68" s="10">
         <v>46208</v>
       </c>
-      <c r="AD68" s="100"/>
-      <c r="AE68" s="100"/>
-      <c r="AF68" s="100"/>
-      <c r="AJ68" s="100"/>
-      <c r="AK68" s="100"/>
-      <c r="AL68" s="100"/>
-      <c r="AM68" s="100"/>
-      <c r="AP68" s="100"/>
-      <c r="AQ68" s="100"/>
-      <c r="AR68" s="100"/>
-      <c r="AS68" s="100"/>
-      <c r="AV68" s="100"/>
-      <c r="AW68" s="100"/>
-      <c r="AX68" s="100"/>
+      <c r="AD68" s="112"/>
+      <c r="AE68" s="112"/>
+      <c r="AF68" s="112"/>
+      <c r="AJ68" s="112"/>
+      <c r="AK68" s="112"/>
+      <c r="AL68" s="112"/>
+      <c r="AM68" s="112"/>
+      <c r="AP68" s="112"/>
+      <c r="AQ68" s="112"/>
+      <c r="AR68" s="112"/>
+      <c r="AS68" s="112"/>
+      <c r="AV68" s="112"/>
+      <c r="AW68" s="112"/>
+      <c r="AX68" s="112"/>
     </row>
     <row r="69" spans="1:60">
       <c r="A69" s="80" t="str">
@@ -6945,7 +6945,7 @@
       <c r="B69" s="2">
         <v>2</v>
       </c>
-      <c r="C69" s="99" t="s">
+      <c r="C69" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="4">
@@ -6965,7 +6965,7 @@
       <c r="K69" s="1">
         <v>3</v>
       </c>
-      <c r="L69" s="99" t="s">
+      <c r="L69" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M69">
@@ -6978,86 +6978,86 @@
       <c r="O69" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AD69" s="100"/>
-      <c r="AE69" s="100"/>
-      <c r="AF69" s="100"/>
-      <c r="AJ69" s="100"/>
-      <c r="AK69" s="100"/>
-      <c r="AL69" s="100"/>
-      <c r="AM69" s="100"/>
-      <c r="AP69" s="100"/>
-      <c r="AQ69" s="100"/>
-      <c r="AR69" s="100"/>
-      <c r="AS69" s="100"/>
-      <c r="AV69" s="100"/>
-      <c r="AW69" s="100"/>
-      <c r="AX69" s="100"/>
+      <c r="AD69" s="112"/>
+      <c r="AE69" s="112"/>
+      <c r="AF69" s="112"/>
+      <c r="AJ69" s="112"/>
+      <c r="AK69" s="112"/>
+      <c r="AL69" s="112"/>
+      <c r="AM69" s="112"/>
+      <c r="AP69" s="112"/>
+      <c r="AQ69" s="112"/>
+      <c r="AR69" s="112"/>
+      <c r="AS69" s="112"/>
+      <c r="AV69" s="112"/>
+      <c r="AW69" s="112"/>
+      <c r="AX69" s="112"/>
     </row>
     <row r="70" spans="1:60">
       <c r="A70" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C70" s="99" t="s">
+      <c r="C70" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E70" s="83"/>
       <c r="J70" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L70" s="99" t="s">
+      <c r="L70" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N70" s="83"/>
-      <c r="AD70" s="100"/>
-      <c r="AE70" s="100"/>
-      <c r="AF70" s="100"/>
-      <c r="AJ70" s="100"/>
-      <c r="AK70" s="100"/>
-      <c r="AL70" s="100"/>
-      <c r="AM70" s="100"/>
-      <c r="AP70" s="100"/>
-      <c r="AQ70" s="100"/>
-      <c r="AR70" s="100"/>
-      <c r="AS70" s="100"/>
-      <c r="AV70" s="100"/>
-      <c r="AW70" s="100"/>
-      <c r="AX70" s="100"/>
+      <c r="AD70" s="112"/>
+      <c r="AE70" s="112"/>
+      <c r="AF70" s="112"/>
+      <c r="AJ70" s="112"/>
+      <c r="AK70" s="112"/>
+      <c r="AL70" s="112"/>
+      <c r="AM70" s="112"/>
+      <c r="AP70" s="112"/>
+      <c r="AQ70" s="112"/>
+      <c r="AR70" s="112"/>
+      <c r="AS70" s="112"/>
+      <c r="AV70" s="112"/>
+      <c r="AW70" s="112"/>
+      <c r="AX70" s="112"/>
     </row>
     <row r="71" spans="1:60">
-      <c r="A71" s="121" t="s">
+      <c r="A71" s="116" t="s">
         <v>168</v>
       </c>
-      <c r="B71" s="121"/>
-      <c r="C71" s="121"/>
-      <c r="D71" s="121"/>
-      <c r="E71" s="121"/>
+      <c r="B71" s="116"/>
+      <c r="C71" s="116"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
       <c r="F71" s="10">
         <v>46203</v>
       </c>
-      <c r="J71" s="121" t="s">
+      <c r="J71" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="K71" s="121"/>
-      <c r="L71" s="121"/>
-      <c r="M71" s="121"/>
-      <c r="N71" s="121"/>
+      <c r="K71" s="116"/>
+      <c r="L71" s="116"/>
+      <c r="M71" s="116"/>
+      <c r="N71" s="116"/>
       <c r="O71" s="10">
         <v>46208</v>
       </c>
-      <c r="AD71" s="100"/>
-      <c r="AE71" s="100"/>
-      <c r="AF71" s="100"/>
-      <c r="AJ71" s="100"/>
-      <c r="AK71" s="100"/>
-      <c r="AL71" s="100"/>
-      <c r="AM71" s="100"/>
-      <c r="AP71" s="100"/>
-      <c r="AQ71" s="100"/>
-      <c r="AR71" s="100"/>
-      <c r="AS71" s="100"/>
-      <c r="AV71" s="100"/>
-      <c r="AW71" s="100"/>
-      <c r="AX71" s="100"/>
+      <c r="AD71" s="112"/>
+      <c r="AE71" s="112"/>
+      <c r="AF71" s="112"/>
+      <c r="AJ71" s="112"/>
+      <c r="AK71" s="112"/>
+      <c r="AL71" s="112"/>
+      <c r="AM71" s="112"/>
+      <c r="AP71" s="112"/>
+      <c r="AQ71" s="112"/>
+      <c r="AR71" s="112"/>
+      <c r="AS71" s="112"/>
+      <c r="AV71" s="112"/>
+      <c r="AW71" s="112"/>
+      <c r="AX71" s="112"/>
     </row>
     <row r="72" spans="1:60">
       <c r="A72" s="80" t="str">
@@ -7067,7 +7067,7 @@
       <c r="B72" s="2">
         <v>3</v>
       </c>
-      <c r="C72" s="99" t="s">
+      <c r="C72" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="4">
@@ -7087,7 +7087,7 @@
       <c r="K72" s="1">
         <v>2</v>
       </c>
-      <c r="L72" s="99" t="s">
+      <c r="L72" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M72">
@@ -7100,26 +7100,26 @@
       <c r="O72" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="AD72" s="100"/>
-      <c r="AE72" s="100"/>
-      <c r="AF72" s="100"/>
-      <c r="AJ72" s="100"/>
-      <c r="AK72" s="100"/>
-      <c r="AL72" s="100"/>
-      <c r="AM72" s="100"/>
-      <c r="AP72" s="100"/>
-      <c r="AQ72" s="100"/>
-      <c r="AR72" s="100"/>
-      <c r="AS72" s="100"/>
-      <c r="AV72" s="100"/>
-      <c r="AW72" s="100"/>
-      <c r="AX72" s="100"/>
+      <c r="AD72" s="112"/>
+      <c r="AE72" s="112"/>
+      <c r="AF72" s="112"/>
+      <c r="AJ72" s="112"/>
+      <c r="AK72" s="112"/>
+      <c r="AL72" s="112"/>
+      <c r="AM72" s="112"/>
+      <c r="AP72" s="112"/>
+      <c r="AQ72" s="112"/>
+      <c r="AR72" s="112"/>
+      <c r="AS72" s="112"/>
+      <c r="AV72" s="112"/>
+      <c r="AW72" s="112"/>
+      <c r="AX72" s="112"/>
     </row>
     <row r="73" spans="1:60">
       <c r="A73" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C73" s="99" t="s">
+      <c r="C73" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E73" s="83"/>
@@ -7129,63 +7129,63 @@
       <c r="K73" s="1">
         <v>5</v>
       </c>
-      <c r="L73" s="99" t="s">
+      <c r="L73" s="101" t="s">
         <v>157</v>
       </c>
       <c r="M73">
         <v>4</v>
       </c>
       <c r="N73" s="83"/>
-      <c r="AD73" s="100"/>
-      <c r="AE73" s="100"/>
-      <c r="AF73" s="100"/>
-      <c r="AJ73" s="100"/>
-      <c r="AK73" s="100"/>
-      <c r="AL73" s="100"/>
-      <c r="AM73" s="100"/>
-      <c r="AP73" s="100"/>
-      <c r="AQ73" s="100"/>
-      <c r="AR73" s="100"/>
-      <c r="AS73" s="100"/>
-      <c r="AV73" s="100"/>
-      <c r="AW73" s="100"/>
-      <c r="AX73" s="100"/>
+      <c r="AD73" s="112"/>
+      <c r="AE73" s="112"/>
+      <c r="AF73" s="112"/>
+      <c r="AJ73" s="112"/>
+      <c r="AK73" s="112"/>
+      <c r="AL73" s="112"/>
+      <c r="AM73" s="112"/>
+      <c r="AP73" s="112"/>
+      <c r="AQ73" s="112"/>
+      <c r="AR73" s="112"/>
+      <c r="AS73" s="112"/>
+      <c r="AV73" s="112"/>
+      <c r="AW73" s="112"/>
+      <c r="AX73" s="112"/>
     </row>
     <row r="74" spans="1:60">
-      <c r="A74" s="121" t="s">
+      <c r="A74" s="116" t="s">
         <v>170</v>
       </c>
-      <c r="B74" s="121"/>
-      <c r="C74" s="121"/>
-      <c r="D74" s="121"/>
-      <c r="E74" s="121"/>
+      <c r="B74" s="116"/>
+      <c r="C74" s="116"/>
+      <c r="D74" s="116"/>
+      <c r="E74" s="116"/>
       <c r="F74" s="10">
         <v>46204</v>
       </c>
-      <c r="J74" s="121" t="s">
+      <c r="J74" s="116" t="s">
         <v>171</v>
       </c>
-      <c r="K74" s="121"/>
-      <c r="L74" s="121"/>
-      <c r="M74" s="121"/>
-      <c r="N74" s="121"/>
+      <c r="K74" s="116"/>
+      <c r="L74" s="116"/>
+      <c r="M74" s="116"/>
+      <c r="N74" s="116"/>
       <c r="O74" s="10">
         <v>46209</v>
       </c>
-      <c r="AD74" s="100"/>
-      <c r="AE74" s="100"/>
-      <c r="AF74" s="100"/>
-      <c r="AJ74" s="100"/>
-      <c r="AK74" s="100"/>
-      <c r="AL74" s="100"/>
-      <c r="AM74" s="100"/>
-      <c r="AP74" s="100"/>
-      <c r="AQ74" s="100"/>
-      <c r="AR74" s="100"/>
-      <c r="AS74" s="100"/>
-      <c r="AV74" s="100"/>
-      <c r="AW74" s="100"/>
-      <c r="AX74" s="100"/>
+      <c r="AD74" s="112"/>
+      <c r="AE74" s="112"/>
+      <c r="AF74" s="112"/>
+      <c r="AJ74" s="112"/>
+      <c r="AK74" s="112"/>
+      <c r="AL74" s="112"/>
+      <c r="AM74" s="112"/>
+      <c r="AP74" s="112"/>
+      <c r="AQ74" s="112"/>
+      <c r="AR74" s="112"/>
+      <c r="AS74" s="112"/>
+      <c r="AV74" s="112"/>
+      <c r="AW74" s="112"/>
+      <c r="AX74" s="112"/>
     </row>
     <row r="75" spans="1:60">
       <c r="A75" s="80" t="str">
@@ -7195,7 +7195,7 @@
       <c r="B75" s="2">
         <v>3</v>
       </c>
-      <c r="C75" s="99" t="s">
+      <c r="C75" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="4">
@@ -7215,7 +7215,7 @@
       <c r="K75" s="1">
         <v>1</v>
       </c>
-      <c r="L75" s="99" t="s">
+      <c r="L75" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M75">
@@ -7228,26 +7228,26 @@
       <c r="O75" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD75" s="100"/>
-      <c r="AE75" s="100"/>
-      <c r="AF75" s="100"/>
-      <c r="AJ75" s="100"/>
-      <c r="AK75" s="100"/>
-      <c r="AL75" s="100"/>
-      <c r="AM75" s="100"/>
-      <c r="AP75" s="100"/>
-      <c r="AQ75" s="100"/>
-      <c r="AR75" s="100"/>
-      <c r="AS75" s="100"/>
-      <c r="AV75" s="100"/>
-      <c r="AW75" s="100"/>
-      <c r="AX75" s="100"/>
+      <c r="AD75" s="112"/>
+      <c r="AE75" s="112"/>
+      <c r="AF75" s="112"/>
+      <c r="AJ75" s="112"/>
+      <c r="AK75" s="112"/>
+      <c r="AL75" s="112"/>
+      <c r="AM75" s="112"/>
+      <c r="AP75" s="112"/>
+      <c r="AQ75" s="112"/>
+      <c r="AR75" s="112"/>
+      <c r="AS75" s="112"/>
+      <c r="AV75" s="112"/>
+      <c r="AW75" s="112"/>
+      <c r="AX75" s="112"/>
     </row>
     <row r="76" spans="1:60">
       <c r="A76" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="99" t="s">
+      <c r="C76" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E76" s="83"/>
@@ -7257,63 +7257,63 @@
       <c r="K76" s="1">
         <v>7</v>
       </c>
-      <c r="L76" s="99" t="s">
+      <c r="L76" s="101" t="s">
         <v>157</v>
       </c>
       <c r="M76">
         <v>6</v>
       </c>
       <c r="N76" s="83"/>
-      <c r="AD76" s="100"/>
-      <c r="AE76" s="100"/>
-      <c r="AF76" s="100"/>
-      <c r="AJ76" s="100"/>
-      <c r="AK76" s="100"/>
-      <c r="AL76" s="100"/>
-      <c r="AM76" s="100"/>
-      <c r="AP76" s="100"/>
-      <c r="AQ76" s="100"/>
-      <c r="AR76" s="100"/>
-      <c r="AS76" s="100"/>
-      <c r="AV76" s="100"/>
-      <c r="AW76" s="100"/>
-      <c r="AX76" s="100"/>
+      <c r="AD76" s="112"/>
+      <c r="AE76" s="112"/>
+      <c r="AF76" s="112"/>
+      <c r="AJ76" s="112"/>
+      <c r="AK76" s="112"/>
+      <c r="AL76" s="112"/>
+      <c r="AM76" s="112"/>
+      <c r="AP76" s="112"/>
+      <c r="AQ76" s="112"/>
+      <c r="AR76" s="112"/>
+      <c r="AS76" s="112"/>
+      <c r="AV76" s="112"/>
+      <c r="AW76" s="112"/>
+      <c r="AX76" s="112"/>
     </row>
     <row r="77" spans="1:60">
-      <c r="A77" s="121" t="s">
+      <c r="A77" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="121"/>
-      <c r="C77" s="121"/>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
+      <c r="B77" s="116"/>
+      <c r="C77" s="116"/>
+      <c r="D77" s="116"/>
+      <c r="E77" s="116"/>
       <c r="F77" s="10">
         <v>46204</v>
       </c>
-      <c r="J77" s="121" t="s">
+      <c r="J77" s="116" t="s">
         <v>173</v>
       </c>
-      <c r="K77" s="121"/>
-      <c r="L77" s="121"/>
-      <c r="M77" s="121"/>
-      <c r="N77" s="121"/>
+      <c r="K77" s="116"/>
+      <c r="L77" s="116"/>
+      <c r="M77" s="116"/>
+      <c r="N77" s="116"/>
       <c r="O77" s="10">
         <v>46209</v>
       </c>
-      <c r="AD77" s="100"/>
-      <c r="AE77" s="100"/>
-      <c r="AF77" s="100"/>
-      <c r="AJ77" s="100"/>
-      <c r="AK77" s="100"/>
-      <c r="AL77" s="100"/>
-      <c r="AM77" s="100"/>
-      <c r="AP77" s="100"/>
-      <c r="AQ77" s="100"/>
-      <c r="AR77" s="100"/>
-      <c r="AS77" s="100"/>
-      <c r="AV77" s="100"/>
-      <c r="AW77" s="100"/>
-      <c r="AX77" s="100"/>
+      <c r="AD77" s="112"/>
+      <c r="AE77" s="112"/>
+      <c r="AF77" s="112"/>
+      <c r="AJ77" s="112"/>
+      <c r="AK77" s="112"/>
+      <c r="AL77" s="112"/>
+      <c r="AM77" s="112"/>
+      <c r="AP77" s="112"/>
+      <c r="AQ77" s="112"/>
+      <c r="AR77" s="112"/>
+      <c r="AS77" s="112"/>
+      <c r="AV77" s="112"/>
+      <c r="AW77" s="112"/>
+      <c r="AX77" s="112"/>
     </row>
     <row r="78" spans="1:60">
       <c r="A78" s="80" t="str">
@@ -7323,7 +7323,7 @@
       <c r="B78" s="2">
         <v>4</v>
       </c>
-      <c r="C78" s="99" t="s">
+      <c r="C78" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="4">
@@ -7343,7 +7343,7 @@
       <c r="K78" s="1">
         <v>0</v>
       </c>
-      <c r="L78" s="99" t="s">
+      <c r="L78" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M78">
@@ -7356,90 +7356,90 @@
       <c r="O78" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="AD78" s="100"/>
-      <c r="AE78" s="100"/>
-      <c r="AF78" s="100"/>
-      <c r="AJ78" s="100"/>
-      <c r="AK78" s="100"/>
-      <c r="AL78" s="100"/>
-      <c r="AM78" s="100"/>
-      <c r="AP78" s="100"/>
-      <c r="AQ78" s="100"/>
-      <c r="AR78" s="100"/>
-      <c r="AS78" s="100"/>
-      <c r="AV78" s="100"/>
-      <c r="AW78" s="100"/>
-      <c r="AX78" s="100"/>
+      <c r="AD78" s="112"/>
+      <c r="AE78" s="112"/>
+      <c r="AF78" s="112"/>
+      <c r="AJ78" s="112"/>
+      <c r="AK78" s="112"/>
+      <c r="AL78" s="112"/>
+      <c r="AM78" s="112"/>
+      <c r="AP78" s="112"/>
+      <c r="AQ78" s="112"/>
+      <c r="AR78" s="112"/>
+      <c r="AS78" s="112"/>
+      <c r="AV78" s="112"/>
+      <c r="AW78" s="112"/>
+      <c r="AX78" s="112"/>
     </row>
     <row r="79" spans="1:60">
       <c r="A79" s="81" t="s">
         <v>156</v>
       </c>
       <c r="B79" s="85"/>
-      <c r="C79" s="99" t="s">
+      <c r="C79" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E79" s="83"/>
       <c r="J79" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L79" s="99" t="s">
+      <c r="L79" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N79" s="83"/>
       <c r="AB79" s="12"/>
-      <c r="AC79" s="114" t="s">
+      <c r="AC79" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="AD79" s="114" t="s">
+      <c r="AD79" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AE79" s="114" t="s">
+      <c r="AE79" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AF79" s="114" t="s">
+      <c r="AF79" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AG79" s="13"/>
       <c r="AH79" s="12"/>
-      <c r="AI79" s="114" t="s">
+      <c r="AI79" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="AJ79" s="114" t="s">
+      <c r="AJ79" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AK79" s="114" t="s">
+      <c r="AK79" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AL79" s="114" t="s">
+      <c r="AL79" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AM79" s="114"/>
+      <c r="AM79" s="111"/>
       <c r="AN79" s="12"/>
-      <c r="AO79" s="114" t="s">
+      <c r="AO79" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="AP79" s="114" t="s">
+      <c r="AP79" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AQ79" s="114" t="s">
+      <c r="AQ79" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AR79" s="114" t="s">
+      <c r="AR79" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AS79" s="114"/>
+      <c r="AS79" s="111"/>
       <c r="AT79" s="12"/>
-      <c r="AU79" s="114" t="s">
+      <c r="AU79" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="AV79" s="114" t="s">
+      <c r="AV79" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AW79" s="114" t="s">
+      <c r="AW79" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AX79" s="114" t="s">
+      <c r="AX79" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AY79" s="11"/>
@@ -7456,23 +7456,23 @@
       <c r="BH79" s="11"/>
     </row>
     <row r="80" spans="1:60">
-      <c r="A80" s="121" t="s">
+      <c r="A80" s="116" t="s">
         <v>174</v>
       </c>
-      <c r="B80" s="121"/>
-      <c r="C80" s="121"/>
-      <c r="D80" s="121"/>
-      <c r="E80" s="121"/>
+      <c r="B80" s="116"/>
+      <c r="C80" s="116"/>
+      <c r="D80" s="116"/>
+      <c r="E80" s="116"/>
       <c r="F80" s="10">
         <v>46204</v>
       </c>
-      <c r="J80" s="121" t="s">
+      <c r="J80" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="K80" s="121"/>
-      <c r="L80" s="121"/>
-      <c r="M80" s="121"/>
-      <c r="N80" s="121"/>
+      <c r="K80" s="116"/>
+      <c r="L80" s="116"/>
+      <c r="M80" s="116"/>
+      <c r="N80" s="116"/>
       <c r="O80" s="10">
         <v>46210</v>
       </c>
@@ -7482,15 +7482,15 @@
       <c r="AC80" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="AD80" s="114">
+      <c r="AD80" s="111">
         <f>$G$3+$P$9+$Z$13</f>
         <v>9</v>
       </c>
-      <c r="AE80" s="114">
+      <c r="AE80" s="111">
         <f>$B$3+$K$9+$V$13-$D$3-$M$9-$T$13</f>
         <v>8</v>
       </c>
-      <c r="AF80" s="114">
+      <c r="AF80" s="111">
         <f>$B$3+$K$9+$V$13</f>
         <v>9</v>
       </c>
@@ -7504,19 +7504,19 @@
       <c r="AI80" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="AJ80" s="114">
+      <c r="AJ80" s="111">
         <f>Y$3+P$5+H$11</f>
         <v>7</v>
       </c>
-      <c r="AK80" s="114">
+      <c r="AK80" s="111">
         <f>AL80-V$3-M$5-B$11</f>
         <v>5</v>
       </c>
-      <c r="AL80" s="114">
+      <c r="AL80" s="111">
         <f>T$3+K$5+D$11</f>
         <v>7</v>
       </c>
-      <c r="AM80" s="114">
+      <c r="AM80" s="111">
         <f>AJ80+(AK80/100)+(AL80/10000)+0.00001</f>
         <v>7.0507099999999996</v>
       </c>
@@ -7526,19 +7526,19 @@
       <c r="AO80" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AP80" s="114">
+      <c r="AP80" s="111">
         <f>Z$9+P$15+G$13</f>
         <v>9</v>
       </c>
-      <c r="AQ80" s="114">
+      <c r="AQ80" s="111">
         <f>AR80-T$9-M$15-D$13</f>
         <v>8</v>
       </c>
-      <c r="AR80" s="114">
+      <c r="AR80" s="111">
         <f>V$9+K$15+B$13</f>
         <v>10</v>
       </c>
-      <c r="AS80" s="114">
+      <c r="AS80" s="111">
         <f>AP80+(AQ80/100)+(AR80/10000)+0.00004</f>
         <v>9.0810399999999998</v>
       </c>
@@ -7548,15 +7548,15 @@
       <c r="AU80" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AV80" s="114">
+      <c r="AV80" s="111">
         <f>Y$23+P$17+H$17</f>
         <v>1</v>
       </c>
-      <c r="AW80" s="114">
+      <c r="AW80" s="111">
         <f>AX80-V$23-M$17-B$17</f>
         <v>-3</v>
       </c>
-      <c r="AX80" s="114">
+      <c r="AX80" s="111">
         <f>T$23+K$17+D$17</f>
         <v>4</v>
       </c>
@@ -7601,7 +7601,7 @@
       <c r="B81" s="2">
         <v>2</v>
       </c>
-      <c r="C81" s="99" t="s">
+      <c r="C81" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="4">
@@ -7621,7 +7621,7 @@
       <c r="K81" s="1">
         <v>4</v>
       </c>
-      <c r="L81" s="99" t="s">
+      <c r="L81" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M81">
@@ -7640,15 +7640,15 @@
       <c r="AC81" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AD81" s="114">
+      <c r="AD81" s="111">
         <f>$P$3+$H$5+$Y$13</f>
         <v>1</v>
       </c>
-      <c r="AE81" s="114">
+      <c r="AE81" s="111">
         <f>$D$5-$B$5+$K$3-$M$3+$T$13-$V$13</f>
         <v>-4</v>
       </c>
-      <c r="AF81" s="114">
+      <c r="AF81" s="111">
         <f>$D$5+$T$13+$K$3</f>
         <v>1</v>
       </c>
@@ -7662,19 +7662,19 @@
       <c r="AI81" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AJ81" s="114">
+      <c r="AJ81" s="111">
         <f>Y$5+Q$5+H$7</f>
         <v>1</v>
       </c>
-      <c r="AK81" s="114">
+      <c r="AK81" s="111">
         <f>AL81-V$5-K$5-B$7</f>
         <v>-3</v>
       </c>
-      <c r="AL81" s="114">
+      <c r="AL81" s="111">
         <f>T$5+M$5+D$7</f>
         <v>3</v>
       </c>
-      <c r="AM81" s="114">
+      <c r="AM81" s="111">
         <f>AJ81+(AK81/100)+(AL81/10000)+0.00003</f>
         <v>0.97032999999999991</v>
       </c>
@@ -7684,19 +7684,19 @@
       <c r="AO81" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AP81" s="114">
+      <c r="AP81" s="111">
         <f>Y$7+Q$13+H$13</f>
         <v>6</v>
       </c>
-      <c r="AQ81" s="114">
+      <c r="AQ81" s="111">
         <f>AR81-V$7-K$13-B$13</f>
         <v>0</v>
       </c>
-      <c r="AR81" s="114">
+      <c r="AR81" s="111">
         <f>T$7+M$13+D$13</f>
         <v>4</v>
       </c>
-      <c r="AS81" s="114">
+      <c r="AS81" s="111">
         <f>AP81+(AQ81/100)+(AR81/10000)+0.00003</f>
         <v>6.0004299999999997</v>
       </c>
@@ -7706,15 +7706,15 @@
       <c r="AU81" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AV81" s="114">
+      <c r="AV81" s="111">
         <f>Z$23+P$11+G$9</f>
         <v>5</v>
       </c>
-      <c r="AW81" s="114">
+      <c r="AW81" s="111">
         <f>AX81-T$23-M$11-D$9</f>
         <v>1</v>
       </c>
-      <c r="AX81" s="114">
+      <c r="AX81" s="111">
         <f>V$23+K$11+B$9</f>
         <v>5</v>
       </c>
@@ -7755,14 +7755,14 @@
       <c r="A82" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C82" s="99" t="s">
+      <c r="C82" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E82" s="83"/>
       <c r="J82" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L82" s="99" t="s">
+      <c r="L82" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N82" s="83"/>
@@ -7772,15 +7772,15 @@
       <c r="AC82" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AD82" s="114">
+      <c r="AD82" s="111">
         <f>$G$5+$Q$9+$Z$11</f>
         <v>2</v>
       </c>
-      <c r="AE82" s="114">
+      <c r="AE82" s="111">
         <f>$B$5+$M$9+$V$11-$T$11-$K$9-$D$5</f>
         <v>-4</v>
       </c>
-      <c r="AF82" s="114">
+      <c r="AF82" s="111">
         <f>$B$5+$M$9+$V$11</f>
         <v>1</v>
       </c>
@@ -7794,19 +7794,19 @@
       <c r="AI82" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AJ82" s="114">
+      <c r="AJ82" s="111">
         <f>Z$3+P$7+G$7</f>
         <v>4</v>
       </c>
-      <c r="AK82" s="114">
+      <c r="AK82" s="111">
         <f>AL82-T$3-M$7-D$7</f>
         <v>-1</v>
       </c>
-      <c r="AL82" s="114">
+      <c r="AL82" s="111">
         <f>V$3+K$7+B$7</f>
         <v>3</v>
       </c>
-      <c r="AM82" s="114">
+      <c r="AM82" s="111">
         <f>AJ82+(AK82/100)+(AL82/10000)+0.00004</f>
         <v>3.9903400000000002</v>
       </c>
@@ -7816,21 +7816,21 @@
       <c r="AO82" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AP82" s="114">
+      <c r="AP82" s="111">
         <f>Y$9+P$13+H$15</f>
         <v>3</v>
       </c>
-      <c r="AQ82" s="114">
+      <c r="AQ82" s="111">
         <f>AR82-V$9-M$13-B$15</f>
-        <v>0</v>
-      </c>
-      <c r="AR82" s="114">
-        <f>T$9+P$13+H$15</f>
-        <v>5</v>
-      </c>
-      <c r="AS82" s="114">
+        <v>2</v>
+      </c>
+      <c r="AR82" s="111">
+        <f>T$9+K$13+D$15</f>
+        <v>7</v>
+      </c>
+      <c r="AS82" s="111">
         <f>AP82+(AQ82/100)+(AR82/10000)+0.00001</f>
-        <v>3.0005100000000002</v>
+        <v>3.0207100000000002</v>
       </c>
       <c r="AT82" s="12" t="s">
         <v>180</v>
@@ -7838,15 +7838,15 @@
       <c r="AU82" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AV82" s="114">
+      <c r="AV82" s="111">
         <f>Y$25+Q$17+H$9</f>
         <v>7</v>
       </c>
-      <c r="AW82" s="114">
+      <c r="AW82" s="111">
         <f>AX82-V$25-K$17-B$9</f>
         <v>5</v>
       </c>
-      <c r="AX82" s="114">
+      <c r="AX82" s="111">
         <f>T$25+M$17+D$9</f>
         <v>8</v>
       </c>
@@ -7884,48 +7884,48 @@
       </c>
     </row>
     <row r="83" spans="1:60">
-      <c r="A83" s="121" t="s">
+      <c r="A83" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="121"/>
-      <c r="C83" s="121"/>
-      <c r="D83" s="121"/>
-      <c r="E83" s="121"/>
+      <c r="B83" s="116"/>
+      <c r="C83" s="116"/>
+      <c r="D83" s="116"/>
+      <c r="E83" s="116"/>
       <c r="F83" s="10">
         <v>46205</v>
       </c>
-      <c r="J83" s="121" t="s">
+      <c r="J83" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="K83" s="121"/>
-      <c r="L83" s="121"/>
-      <c r="M83" s="121"/>
-      <c r="N83" s="121"/>
+      <c r="K83" s="116"/>
+      <c r="L83" s="116"/>
+      <c r="M83" s="116"/>
+      <c r="N83" s="116"/>
       <c r="O83" s="10">
         <v>46210</v>
       </c>
-      <c r="S83" s="117" t="s">
+      <c r="S83" s="133" t="s">
         <v>184</v>
       </c>
-      <c r="T83" s="117"/>
-      <c r="U83" s="117"/>
-      <c r="V83" s="117"/>
-      <c r="W83" s="117"/>
+      <c r="T83" s="133"/>
+      <c r="U83" s="133"/>
+      <c r="V83" s="133"/>
+      <c r="W83" s="133"/>
       <c r="AB83" s="12" t="s">
         <v>185</v>
       </c>
       <c r="AC83" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AD83" s="114">
+      <c r="AD83" s="111">
         <f>$H$3+$Q$3+$Y$11</f>
         <v>4</v>
       </c>
-      <c r="AE83" s="114">
+      <c r="AE83" s="111">
         <f>$M$3+$D$3+$T$11-$V$11-$K$3-$B$3</f>
         <v>0</v>
       </c>
-      <c r="AF83" s="114">
+      <c r="AF83" s="111">
         <f>$M$3+$D$3+$T$11</f>
         <v>4</v>
       </c>
@@ -7939,19 +7939,19 @@
       <c r="AI83" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AJ83" s="114">
+      <c r="AJ83" s="111">
         <f>Z$5+Q$7+G$11</f>
         <v>4</v>
       </c>
-      <c r="AK83" s="114">
+      <c r="AK83" s="111">
         <f>AL83-T$5-K$7-D$11</f>
         <v>-1</v>
       </c>
-      <c r="AL83" s="114">
+      <c r="AL83" s="111">
         <f>V$5+M$7+B$11</f>
         <v>5</v>
       </c>
-      <c r="AM83" s="114">
+      <c r="AM83" s="111">
         <f>AJ83+(AK83/100)+(AL83/10000)+0.00002</f>
         <v>3.9905200000000005</v>
       </c>
@@ -7961,19 +7961,19 @@
       <c r="AO83" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AP83" s="114">
+      <c r="AP83" s="111">
         <f>Z$7+Q$15+G$15</f>
         <v>0</v>
       </c>
-      <c r="AQ83" s="114">
+      <c r="AQ83" s="111">
         <f>AR83-T$7-K$15-D$15</f>
         <v>-10</v>
       </c>
-      <c r="AR83" s="114">
+      <c r="AR83" s="111">
         <f>V$7+M$15+B$15</f>
         <v>1</v>
       </c>
-      <c r="AS83" s="114">
+      <c r="AS83" s="111">
         <f>AP83+(AQ83/100)+(AR83/10000)+0.00002</f>
         <v>-9.9879999999999997E-2</v>
       </c>
@@ -7983,15 +7983,15 @@
       <c r="AU83" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AV83" s="114">
+      <c r="AV83" s="111">
         <f>Z$25+Q$11+G$17</f>
         <v>2</v>
       </c>
-      <c r="AW83" s="114">
+      <c r="AW83" s="111">
         <f>AX83-T$25-K$11-D$17</f>
         <v>-3</v>
       </c>
-      <c r="AX83" s="114">
+      <c r="AX83" s="111">
         <f>V$25+M$11+B$17</f>
         <v>5</v>
       </c>
@@ -8036,7 +8036,7 @@
       <c r="B84" s="2">
         <v>2</v>
       </c>
-      <c r="C84" s="99" t="s">
+      <c r="C84" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="4">
@@ -8056,7 +8056,7 @@
       <c r="K84" s="1">
         <v>1</v>
       </c>
-      <c r="L84" s="99" t="s">
+      <c r="L84" s="101" t="s">
         <v>12</v>
       </c>
       <c r="M84">
@@ -8069,39 +8069,39 @@
       <c r="O84" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="S84" s="118" t="s">
+      <c r="S84" s="134" t="s">
         <v>187</v>
       </c>
-      <c r="T84" s="118"/>
-      <c r="U84" s="118"/>
-      <c r="V84" s="118"/>
-      <c r="W84" s="118"/>
+      <c r="T84" s="134"/>
+      <c r="U84" s="134"/>
+      <c r="V84" s="134"/>
+      <c r="W84" s="134"/>
       <c r="X84" s="3">
         <v>46217</v>
       </c>
       <c r="AB84" s="12"/>
       <c r="AC84" s="12"/>
-      <c r="AD84" s="114"/>
-      <c r="AE84" s="114"/>
-      <c r="AF84" s="114"/>
+      <c r="AD84" s="111"/>
+      <c r="AE84" s="111"/>
+      <c r="AF84" s="111"/>
       <c r="AG84" s="13"/>
       <c r="AH84" s="12"/>
       <c r="AI84" s="11"/>
-      <c r="AJ84" s="114"/>
-      <c r="AK84" s="114"/>
-      <c r="AL84" s="114"/>
-      <c r="AM84" s="114"/>
+      <c r="AJ84" s="111"/>
+      <c r="AK84" s="111"/>
+      <c r="AL84" s="111"/>
+      <c r="AM84" s="111"/>
       <c r="AN84" s="12"/>
       <c r="AO84" s="14"/>
-      <c r="AP84" s="114"/>
-      <c r="AQ84" s="114"/>
-      <c r="AR84" s="114"/>
-      <c r="AS84" s="114"/>
+      <c r="AP84" s="111"/>
+      <c r="AQ84" s="111"/>
+      <c r="AR84" s="111"/>
+      <c r="AS84" s="111"/>
       <c r="AT84" s="12"/>
       <c r="AU84" s="11"/>
-      <c r="AV84" s="114"/>
-      <c r="AW84" s="114"/>
-      <c r="AX84" s="114"/>
+      <c r="AV84" s="111"/>
+      <c r="AW84" s="111"/>
+      <c r="AX84" s="111"/>
       <c r="AY84" s="11"/>
       <c r="AZ84" s="11"/>
       <c r="BA84" s="11"/>
@@ -8139,7 +8139,7 @@
       <c r="B85" s="2">
         <v>4</v>
       </c>
-      <c r="C85" s="99" t="s">
+      <c r="C85" s="101" t="s">
         <v>157</v>
       </c>
       <c r="D85" s="4">
@@ -8149,7 +8149,7 @@
       <c r="J85" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="L85" s="99" t="s">
+      <c r="L85" s="101" t="s">
         <v>157</v>
       </c>
       <c r="N85" s="83"/>
@@ -8160,7 +8160,7 @@
       <c r="T85" s="1">
         <v>3</v>
       </c>
-      <c r="U85" s="115" t="s">
+      <c r="U85" s="99" t="s">
         <v>12</v>
       </c>
       <c r="V85" s="4">
@@ -8174,58 +8174,58 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="AB85" s="12"/>
-      <c r="AC85" s="114" t="s">
+      <c r="AC85" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="AD85" s="114" t="s">
+      <c r="AD85" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AE85" s="114" t="s">
+      <c r="AE85" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AF85" s="114" t="s">
+      <c r="AF85" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AG85" s="13"/>
       <c r="AH85" s="12"/>
-      <c r="AI85" s="114" t="s">
+      <c r="AI85" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="AJ85" s="114" t="s">
+      <c r="AJ85" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AK85" s="114" t="s">
+      <c r="AK85" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AL85" s="114" t="s">
+      <c r="AL85" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AM85" s="114"/>
+      <c r="AM85" s="111"/>
       <c r="AN85" s="12"/>
-      <c r="AO85" s="114" t="s">
+      <c r="AO85" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="AP85" s="114" t="s">
+      <c r="AP85" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AQ85" s="114" t="s">
+      <c r="AQ85" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AR85" s="114" t="s">
+      <c r="AR85" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AS85" s="114"/>
+      <c r="AS85" s="111"/>
       <c r="AT85" s="12"/>
-      <c r="AU85" s="114" t="s">
+      <c r="AU85" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="AV85" s="114" t="s">
+      <c r="AV85" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AW85" s="114" t="s">
+      <c r="AW85" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AX85" s="114" t="s">
+      <c r="AX85" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AY85" s="11"/>
@@ -8259,13 +8259,13 @@
       </c>
     </row>
     <row r="86" spans="1:60">
-      <c r="A86" s="121" t="s">
+      <c r="A86" s="116" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="121"/>
-      <c r="C86" s="121"/>
-      <c r="D86" s="121"/>
-      <c r="E86" s="121"/>
+      <c r="B86" s="116"/>
+      <c r="C86" s="116"/>
+      <c r="D86" s="116"/>
+      <c r="E86" s="116"/>
       <c r="F86" s="10">
         <v>46205</v>
       </c>
@@ -8276,7 +8276,7 @@
       <c r="N86" s="83"/>
       <c r="O86" s="10"/>
       <c r="S86" s="86"/>
-      <c r="U86" s="115" t="s">
+      <c r="U86" s="99" t="s">
         <v>157</v>
       </c>
       <c r="W86" s="88"/>
@@ -8286,15 +8286,15 @@
       <c r="AC86" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AD86" s="114">
+      <c r="AD86" s="111">
         <f>G$19+P$21+Z$17</f>
         <v>7</v>
       </c>
-      <c r="AE86" s="114">
+      <c r="AE86" s="111">
         <f>AF86-T$17-M$21-D$19</f>
         <v>8</v>
       </c>
-      <c r="AF86" s="114">
+      <c r="AF86" s="111">
         <f>V$17+K$21+B$19</f>
         <v>11</v>
       </c>
@@ -8308,15 +8308,15 @@
       <c r="AI86" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AJ86" s="114">
+      <c r="AJ86" s="111">
         <f>Z$19+P$19+G$21</f>
         <v>5</v>
       </c>
-      <c r="AK86" s="114">
+      <c r="AK86" s="111">
         <f>AL86-M$19-D$21-T$19</f>
         <v>1</v>
       </c>
-      <c r="AL86" s="114">
+      <c r="AL86" s="111">
         <f>V$19+K$19+B$21</f>
         <v>4</v>
       </c>
@@ -8330,19 +8330,19 @@
       <c r="AO86" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AP86" s="114">
+      <c r="AP86" s="111">
         <f>Z$35+P$29+G$29</f>
         <v>9</v>
       </c>
-      <c r="AQ86" s="114">
+      <c r="AQ86" s="111">
         <f>AR86-T$35-M$29-D$29</f>
         <v>7</v>
       </c>
-      <c r="AR86" s="114">
+      <c r="AR86" s="111">
         <f>V$35+K$29+B$29</f>
         <v>8</v>
       </c>
-      <c r="AS86" s="114">
+      <c r="AS86" s="111">
         <f>AP86+(AQ86/100)+(AR86/10000)+0.00004</f>
         <v>9.0708400000000005</v>
       </c>
@@ -8352,15 +8352,15 @@
       <c r="AU86" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="AV86" s="114">
+      <c r="AV86" s="111">
         <f>Z$33+P$27+G$27</f>
         <v>7</v>
       </c>
-      <c r="AW86" s="114">
+      <c r="AW86" s="111">
         <f>AX86-T$33-M$27-D$27</f>
         <v>4</v>
       </c>
-      <c r="AX86" s="114">
+      <c r="AX86" s="111">
         <f>V$33+K$27+B$27</f>
         <v>6</v>
       </c>
@@ -8383,15 +8383,15 @@
       </c>
       <c r="BE86" s="11">
         <f>AE$10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF86" s="11">
         <f>AF$10</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG86" s="12">
         <f>BD86+(BE86/100)+(BF86/10000)+0.00001</f>
-        <v>3.0005100000000002</v>
+        <v>3.0207100000000002</v>
       </c>
       <c r="BH86" s="11" t="s">
         <v>194</v>
@@ -8405,7 +8405,7 @@
       <c r="B87" s="2">
         <v>4</v>
       </c>
-      <c r="C87" s="99" t="s">
+      <c r="C87" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="4">
@@ -8419,13 +8419,13 @@
         <v>14</v>
       </c>
       <c r="O87" s="8"/>
-      <c r="S87" s="118" t="s">
+      <c r="S87" s="134" t="s">
         <v>195</v>
       </c>
-      <c r="T87" s="118"/>
-      <c r="U87" s="118"/>
-      <c r="V87" s="118"/>
-      <c r="W87" s="118"/>
+      <c r="T87" s="134"/>
+      <c r="U87" s="134"/>
+      <c r="V87" s="134"/>
+      <c r="W87" s="134"/>
       <c r="X87" s="3">
         <v>46218</v>
       </c>
@@ -8435,15 +8435,15 @@
       <c r="AC87" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="AD87" s="114">
+      <c r="AD87" s="111">
         <f>Z$15+Q$21+G$23</f>
         <v>3</v>
       </c>
-      <c r="AE87" s="114">
+      <c r="AE87" s="111">
         <f>AF87-T$15-K$21-D$23</f>
         <v>-1</v>
       </c>
-      <c r="AF87" s="114">
+      <c r="AF87" s="111">
         <f>V$15+M$21+B$23</f>
         <v>4</v>
       </c>
@@ -8457,19 +8457,19 @@
       <c r="AI87" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ87" s="114">
+      <c r="AJ87" s="111">
         <f>Y$21+Q$25+H$21</f>
         <v>7</v>
       </c>
-      <c r="AK87" s="114">
+      <c r="AK87" s="111">
         <f>AL87-V$21-K$25-B$21</f>
         <v>3</v>
       </c>
-      <c r="AL87" s="114">
+      <c r="AL87" s="111">
         <f>M$25+T$21+D$21</f>
         <v>6</v>
       </c>
-      <c r="AM87" s="114">
+      <c r="AM87" s="111">
         <f>AJ87+(AK87/100)+(AL87/10000)+0.00003</f>
         <v>7.0306300000000004</v>
       </c>
@@ -8479,19 +8479,19 @@
       <c r="AO87" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="AP87" s="114">
+      <c r="AP87" s="111">
         <f>Z$37+Q$29+G$33</f>
         <v>1</v>
       </c>
-      <c r="AQ87" s="114">
+      <c r="AQ87" s="111">
         <f>AR87-T$37-K$29-D$33</f>
         <v>-3</v>
       </c>
-      <c r="AR87" s="114">
+      <c r="AR87" s="111">
         <f>V$37+M$29+B$33</f>
         <v>1</v>
       </c>
-      <c r="AS87" s="114">
+      <c r="AS87" s="111">
         <f>AP87+(AQ87/100)+(AR87/10000)+0.00002</f>
         <v>0.97011999999999998</v>
       </c>
@@ -8501,15 +8501,15 @@
       <c r="AU87" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="AV87" s="114">
+      <c r="AV87" s="111">
         <f>Y$33+P$31+H$31</f>
         <v>5</v>
       </c>
-      <c r="AW87" s="114">
+      <c r="AW87" s="111">
         <f>AX87-V$33-M$31-B$31</f>
         <v>3</v>
       </c>
-      <c r="AX87" s="114">
+      <c r="AX87" s="111">
         <f>T$33+K$31+D$31</f>
         <v>5</v>
       </c>
@@ -8550,17 +8550,17 @@
       <c r="A88" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C88" s="99" t="s">
+      <c r="C88" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E88" s="83"/>
-      <c r="J88" s="117" t="s">
+      <c r="J88" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="K88" s="117"/>
-      <c r="L88" s="117"/>
-      <c r="M88" s="117"/>
-      <c r="N88" s="117"/>
+      <c r="K88" s="133"/>
+      <c r="L88" s="133"/>
+      <c r="M88" s="133"/>
+      <c r="N88" s="133"/>
       <c r="S88" s="86" t="str">
         <f>IF(K96 = "", "", IF(K96 &gt; M96, J96, IF(M96 &gt; K96, N96, IF(M97 &gt; K97, N96, J96))))</f>
         <v>Brasil</v>
@@ -8568,7 +8568,7 @@
       <c r="T88" s="1">
         <v>2</v>
       </c>
-      <c r="U88" s="115" t="s">
+      <c r="U88" s="99" t="s">
         <v>12</v>
       </c>
       <c r="V88" s="4">
@@ -8587,15 +8587,15 @@
       <c r="AC88" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AD88" s="114">
+      <c r="AD88" s="111">
         <f>Y$17+P$23+H$23</f>
         <v>7</v>
       </c>
-      <c r="AE88" s="114">
+      <c r="AE88" s="111">
         <f>AF88-V$17-M$23-B$23</f>
         <v>6</v>
       </c>
-      <c r="AF88" s="114">
+      <c r="AF88" s="111">
         <f>T$17+K$23+D$23</f>
         <v>8</v>
       </c>
@@ -8609,19 +8609,19 @@
       <c r="AI88" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AJ88" s="114">
+      <c r="AJ88" s="111">
         <f>G$25+Z$21+Q$19</f>
         <v>4</v>
       </c>
-      <c r="AK88" s="114">
+      <c r="AK88" s="111">
         <f>AL88-T$21-K$19-D$25</f>
         <v>-1</v>
       </c>
-      <c r="AL88" s="114">
+      <c r="AL88" s="111">
         <f>V$21+M$19+B$25</f>
         <v>4</v>
       </c>
-      <c r="AM88" s="114">
+      <c r="AM88" s="111">
         <f>AJ88+(AK88/100)+(AL88/10000)+0.00002</f>
         <v>3.9904200000000003</v>
       </c>
@@ -8631,19 +8631,19 @@
       <c r="AO88" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AP88" s="114">
+      <c r="AP88" s="111">
         <f>Y$37+Q$33+H$29</f>
         <v>6</v>
       </c>
-      <c r="AQ88" s="114">
+      <c r="AQ88" s="111">
         <f>AR88-V$37-K$33-B$29</f>
         <v>0</v>
       </c>
-      <c r="AR88" s="114">
+      <c r="AR88" s="111">
         <f>T$37+M$33+D$29</f>
         <v>2</v>
       </c>
-      <c r="AS88" s="114">
+      <c r="AS88" s="111">
         <f>AP88+(AQ88/100)+(AR88/10000)+0.00003</f>
         <v>6.0002300000000002</v>
       </c>
@@ -8653,15 +8653,15 @@
       <c r="AU88" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AV88" s="114">
+      <c r="AV88" s="111">
         <f>Z$31+Q$27+G$31</f>
         <v>4</v>
       </c>
-      <c r="AW88" s="114">
+      <c r="AW88" s="111">
         <f>AX88-T$31-K$27-D$31</f>
         <v>2</v>
       </c>
-      <c r="AX88" s="114">
+      <c r="AX88" s="111">
         <f>V$31+M$27+B$31</f>
         <v>5</v>
       </c>
@@ -8699,23 +8699,23 @@
       </c>
     </row>
     <row r="89" spans="1:60">
-      <c r="A89" s="121" t="s">
+      <c r="A89" s="116" t="s">
         <v>201</v>
       </c>
-      <c r="B89" s="121"/>
-      <c r="C89" s="121"/>
-      <c r="D89" s="121"/>
-      <c r="E89" s="121"/>
+      <c r="B89" s="116"/>
+      <c r="C89" s="116"/>
+      <c r="D89" s="116"/>
+      <c r="E89" s="116"/>
       <c r="F89" s="10">
         <v>46206</v>
       </c>
-      <c r="J89" s="118" t="s">
+      <c r="J89" s="134" t="s">
         <v>202</v>
       </c>
-      <c r="K89" s="118"/>
-      <c r="L89" s="118"/>
-      <c r="M89" s="118"/>
-      <c r="N89" s="118"/>
+      <c r="K89" s="134"/>
+      <c r="L89" s="134"/>
+      <c r="M89" s="134"/>
+      <c r="N89" s="134"/>
       <c r="O89" s="10">
         <v>46212</v>
       </c>
@@ -8723,7 +8723,7 @@
       <c r="T89" s="1">
         <v>2</v>
       </c>
-      <c r="U89" s="115" t="s">
+      <c r="U89" s="99" t="s">
         <v>157</v>
       </c>
       <c r="V89" s="4">
@@ -8736,15 +8736,15 @@
       <c r="AC89" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AD89" s="114">
+      <c r="AD89" s="111">
         <f>H$19+Q$23+Y$15</f>
         <v>0</v>
       </c>
-      <c r="AE89" s="114">
+      <c r="AE89" s="111">
         <f>AF89-V$15-K$23-B$19</f>
         <v>-13</v>
       </c>
-      <c r="AF89" s="114">
+      <c r="AF89" s="111">
         <f>T$15+M$23+D$19</f>
         <v>0</v>
       </c>
@@ -8758,19 +8758,19 @@
       <c r="AI89" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AJ89" s="114">
+      <c r="AJ89" s="111">
         <f>Y$19+P$25+H$25</f>
         <v>0</v>
       </c>
-      <c r="AK89" s="114">
+      <c r="AK89" s="111">
         <f>AL89-V$19-M$25-B$25</f>
         <v>-3</v>
       </c>
-      <c r="AL89" s="114">
+      <c r="AL89" s="111">
         <f>T$19+K$25+D$25</f>
         <v>1</v>
       </c>
-      <c r="AM89" s="114">
+      <c r="AM89" s="111">
         <f>AJ89+(AK89/100)+(AL89/10000)+0.00001</f>
         <v>-2.989E-2</v>
       </c>
@@ -8780,19 +8780,19 @@
       <c r="AO89" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="AP89" s="114">
+      <c r="AP89" s="111">
         <f>Y$35+P$33+H$33</f>
         <v>1</v>
       </c>
-      <c r="AQ89" s="114">
+      <c r="AQ89" s="111">
         <f>AR89-V$35-M$33-B$33</f>
         <v>-4</v>
       </c>
-      <c r="AR89" s="114">
+      <c r="AR89" s="111">
         <f>T$35+K$33+D$33</f>
         <v>0</v>
       </c>
-      <c r="AS89" s="114">
+      <c r="AS89" s="111">
         <f>AP89+(AQ89/100)+(AR89/10000)+0.00001</f>
         <v>0.96000999999999992</v>
       </c>
@@ -8802,15 +8802,15 @@
       <c r="AU89" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="AV89" s="114">
+      <c r="AV89" s="111">
         <f>Y$31+Q$31+H$27</f>
         <v>0</v>
       </c>
-      <c r="AW89" s="114">
+      <c r="AW89" s="111">
         <f>AX89-V$31-K$31-B$27</f>
         <v>-9</v>
       </c>
-      <c r="AX89" s="114">
+      <c r="AX89" s="111">
         <f>T$31+M$31+D$27</f>
         <v>0</v>
       </c>
@@ -8855,7 +8855,7 @@
       <c r="B90" s="2">
         <v>1</v>
       </c>
-      <c r="C90" s="99" t="s">
+      <c r="C90" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="4">
@@ -8875,7 +8875,7 @@
       <c r="K90" s="1">
         <v>2</v>
       </c>
-      <c r="L90" s="115" t="s">
+      <c r="L90" s="99" t="s">
         <v>12</v>
       </c>
       <c r="M90">
@@ -8895,27 +8895,27 @@
       <c r="W90" s="88"/>
       <c r="AB90" s="12"/>
       <c r="AC90" s="12"/>
-      <c r="AD90" s="114"/>
-      <c r="AE90" s="114"/>
-      <c r="AF90" s="114"/>
+      <c r="AD90" s="111"/>
+      <c r="AE90" s="111"/>
+      <c r="AF90" s="111"/>
       <c r="AG90" s="13"/>
       <c r="AH90" s="12"/>
       <c r="AI90" s="11"/>
-      <c r="AJ90" s="114"/>
-      <c r="AK90" s="114"/>
-      <c r="AL90" s="114"/>
-      <c r="AM90" s="114"/>
+      <c r="AJ90" s="111"/>
+      <c r="AK90" s="111"/>
+      <c r="AL90" s="111"/>
+      <c r="AM90" s="111"/>
       <c r="AN90" s="12"/>
       <c r="AO90" s="14"/>
-      <c r="AP90" s="114"/>
-      <c r="AQ90" s="114"/>
-      <c r="AR90" s="114"/>
-      <c r="AS90" s="114"/>
+      <c r="AP90" s="111"/>
+      <c r="AQ90" s="111"/>
+      <c r="AR90" s="111"/>
+      <c r="AS90" s="111"/>
       <c r="AT90" s="12"/>
       <c r="AU90" s="11"/>
-      <c r="AV90" s="114"/>
-      <c r="AW90" s="114"/>
-      <c r="AX90" s="114"/>
+      <c r="AV90" s="111"/>
+      <c r="AW90" s="111"/>
+      <c r="AX90" s="111"/>
       <c r="AY90" s="11"/>
       <c r="AZ90" s="11"/>
       <c r="BA90" s="11"/>
@@ -8950,70 +8950,70 @@
       <c r="A91" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C91" s="99" t="s">
+      <c r="C91" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E91" s="83"/>
       <c r="J91" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="L91" s="115" t="s">
+      <c r="L91" s="99" t="s">
         <v>157</v>
       </c>
       <c r="N91" s="88"/>
       <c r="AB91" s="12"/>
-      <c r="AC91" s="114" t="s">
+      <c r="AC91" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="AD91" s="114" t="s">
+      <c r="AD91" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="114" t="s">
+      <c r="AE91" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AF91" s="114" t="s">
+      <c r="AF91" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AG91" s="13"/>
       <c r="AH91" s="12"/>
-      <c r="AI91" s="114" t="s">
+      <c r="AI91" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="AJ91" s="114" t="s">
+      <c r="AJ91" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AK91" s="114" t="s">
+      <c r="AK91" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AL91" s="114" t="s">
+      <c r="AL91" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AM91" s="114"/>
+      <c r="AM91" s="111"/>
       <c r="AN91" s="12"/>
-      <c r="AO91" s="114" t="s">
+      <c r="AO91" s="111" t="s">
         <v>109</v>
       </c>
-      <c r="AP91" s="114" t="s">
+      <c r="AP91" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AQ91" s="114" t="s">
+      <c r="AQ91" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AR91" s="114" t="s">
+      <c r="AR91" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AS91" s="114"/>
+      <c r="AS91" s="111"/>
       <c r="AT91" s="12"/>
-      <c r="AU91" s="114" t="s">
+      <c r="AU91" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="AV91" s="114" t="s">
+      <c r="AV91" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="AW91" s="114" t="s">
+      <c r="AW91" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="AX91" s="114" t="s">
+      <c r="AX91" s="111" t="s">
         <v>6</v>
       </c>
       <c r="AY91" s="11"/>
@@ -9047,33 +9047,33 @@
       </c>
     </row>
     <row r="92" spans="1:60">
-      <c r="A92" s="121" t="s">
+      <c r="A92" s="116" t="s">
         <v>209</v>
       </c>
-      <c r="B92" s="121"/>
-      <c r="C92" s="121"/>
-      <c r="D92" s="121"/>
-      <c r="E92" s="121"/>
+      <c r="B92" s="116"/>
+      <c r="C92" s="116"/>
+      <c r="D92" s="116"/>
+      <c r="E92" s="116"/>
       <c r="F92" s="10">
         <v>46206</v>
       </c>
-      <c r="J92" s="118" t="s">
+      <c r="J92" s="134" t="s">
         <v>210</v>
       </c>
-      <c r="K92" s="118"/>
-      <c r="L92" s="118"/>
-      <c r="M92" s="118"/>
-      <c r="N92" s="118"/>
+      <c r="K92" s="134"/>
+      <c r="L92" s="134"/>
+      <c r="M92" s="134"/>
+      <c r="N92" s="134"/>
       <c r="O92" s="10">
         <v>46213</v>
       </c>
-      <c r="S92" s="119" t="s">
+      <c r="S92" s="135" t="s">
         <v>211</v>
       </c>
-      <c r="T92" s="119"/>
-      <c r="U92" s="119"/>
-      <c r="V92" s="119"/>
-      <c r="W92" s="119"/>
+      <c r="T92" s="135"/>
+      <c r="U92" s="135"/>
+      <c r="V92" s="135"/>
+      <c r="W92" s="135"/>
       <c r="X92" s="10">
         <v>46221</v>
       </c>
@@ -9083,15 +9083,15 @@
       <c r="AC92" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AD92" s="114">
+      <c r="AD92" s="111">
         <f>Z$27+P$37+G$35</f>
         <v>9</v>
       </c>
-      <c r="AE92" s="114">
+      <c r="AE92" s="111">
         <f>AF92-T$27-D$35-M$37</f>
         <v>8</v>
       </c>
-      <c r="AF92" s="114">
+      <c r="AF92" s="111">
         <f>V$27+K$37+B$35</f>
         <v>10</v>
       </c>
@@ -9105,19 +9105,19 @@
       <c r="AI92" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="AJ92" s="114">
+      <c r="AJ92" s="111">
         <f>Z$49+P$35+G$39</f>
         <v>9</v>
       </c>
-      <c r="AK92" s="114">
+      <c r="AK92" s="111">
         <f>AL92-T$49-M$35-D$39</f>
         <v>8</v>
       </c>
-      <c r="AL92" s="114">
+      <c r="AL92" s="111">
         <f>V$49+K$35+B$39</f>
         <v>9</v>
       </c>
-      <c r="AM92" s="114">
+      <c r="AM92" s="111">
         <f>AJ92+(AK92/100)+(AL92/10000)+0.00004</f>
         <v>9.08094</v>
       </c>
@@ -9127,19 +9127,19 @@
       <c r="AO92" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="AP92" s="114">
+      <c r="AP92" s="111">
         <f>G$43+P$43+Z$43</f>
         <v>7</v>
       </c>
-      <c r="AQ92" s="114">
+      <c r="AQ92" s="111">
         <f>AR92-T$43-M$43-D$43</f>
         <v>7</v>
       </c>
-      <c r="AR92" s="114">
+      <c r="AR92" s="111">
         <f>V$43+K$43+B$43</f>
         <v>7</v>
       </c>
-      <c r="AS92" s="114">
+      <c r="AS92" s="111">
         <f>AP92+(AQ92/100)+(AR92/10000)+0.00004</f>
         <v>7.0707400000000007</v>
       </c>
@@ -9149,15 +9149,15 @@
       <c r="AU92" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AV92" s="114">
+      <c r="AV92" s="111">
         <f>Z$39+P$45+G$45</f>
         <v>7</v>
       </c>
-      <c r="AW92" s="114">
+      <c r="AW92" s="111">
         <f>AX92-T$39-M$45-D$45</f>
         <v>9</v>
       </c>
-      <c r="AX92" s="114">
+      <c r="AX92" s="111">
         <f>V$39+K$45+B$45</f>
         <v>9</v>
       </c>
@@ -9183,7 +9183,7 @@
       <c r="B93" s="2">
         <v>0</v>
       </c>
-      <c r="C93" s="99" t="s">
+      <c r="C93" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="4">
@@ -9203,7 +9203,7 @@
       <c r="K93" s="1">
         <v>1</v>
       </c>
-      <c r="L93" s="115" t="s">
+      <c r="L93" s="99" t="s">
         <v>12</v>
       </c>
       <c r="M93">
@@ -9242,15 +9242,15 @@
       <c r="AC93" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AD93" s="114">
+      <c r="AD93" s="111">
         <f>Y$27+P$39+H$37</f>
         <v>4</v>
       </c>
-      <c r="AE93" s="114">
+      <c r="AE93" s="111">
         <f>AF93-V$27-B$37-M$39</f>
         <v>1</v>
       </c>
-      <c r="AF93" s="114">
+      <c r="AF93" s="111">
         <f>T$27+K$39+D$37</f>
         <v>6</v>
       </c>
@@ -9264,19 +9264,19 @@
       <c r="AI93" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="AJ93" s="114">
+      <c r="AJ93" s="111">
         <f>Z$47+Q$35+G$41</f>
         <v>1</v>
       </c>
-      <c r="AK93" s="114">
+      <c r="AK93" s="111">
         <f>AL93-T$47-K$35-D$41</f>
         <v>-4</v>
       </c>
-      <c r="AL93" s="114">
+      <c r="AL93" s="111">
         <f>V$47+M$35+B$41</f>
         <v>3</v>
       </c>
-      <c r="AM93" s="114">
+      <c r="AM93" s="111">
         <f>AJ93+(AK93/100)+(AL93/10000)+0.00002</f>
         <v>0.96031999999999995</v>
       </c>
@@ -9286,19 +9286,19 @@
       <c r="AO93" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="AP93" s="114">
+      <c r="AP93" s="111">
         <f>Y$43+P$49+H$49</f>
         <v>7</v>
       </c>
-      <c r="AQ93" s="114">
+      <c r="AQ93" s="111">
         <f>AR93-V$43-M$49-B$49</f>
         <v>10</v>
       </c>
-      <c r="AR93" s="114">
+      <c r="AR93" s="111">
         <f>T$43+K$49+D$49</f>
         <v>10</v>
       </c>
-      <c r="AS93" s="114">
+      <c r="AS93" s="111">
         <f>AP93+(AQ93/100)+(AR93/10000)+0.00001</f>
         <v>7.1010099999999996</v>
       </c>
@@ -9308,15 +9308,15 @@
       <c r="AU93" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="AV93" s="114">
+      <c r="AV93" s="111">
         <f>Y$41+Q$47+H$45</f>
         <v>7</v>
       </c>
-      <c r="AW93" s="114">
+      <c r="AW93" s="111">
         <f>AX93-V$41-K$47-B$45</f>
         <v>8</v>
       </c>
-      <c r="AX93" s="114">
+      <c r="AX93" s="111">
         <f>T$41+M$47+D$45</f>
         <v>8</v>
       </c>
@@ -9341,7 +9341,7 @@
       <c r="B94" s="2">
         <v>5</v>
       </c>
-      <c r="C94" s="99" t="s">
+      <c r="C94" s="101" t="s">
         <v>157</v>
       </c>
       <c r="D94" s="4">
@@ -9351,7 +9351,7 @@
       <c r="J94" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="L94" s="115" t="s">
+      <c r="L94" s="99" t="s">
         <v>157</v>
       </c>
       <c r="N94" s="88"/>
@@ -9368,15 +9368,15 @@
       <c r="AC94" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="AD94" s="114">
+      <c r="AD94" s="111">
         <f>Y$29+Q$39+H$35</f>
         <v>4</v>
       </c>
-      <c r="AE94" s="114">
+      <c r="AE94" s="111">
         <f>AF94-K$39-B$35-V$29</f>
         <v>-1</v>
       </c>
-      <c r="AF94" s="114">
+      <c r="AF94" s="111">
         <f>D$35+M$39+T$29</f>
         <v>4</v>
       </c>
@@ -9390,19 +9390,19 @@
       <c r="AI94" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AJ94" s="114">
+      <c r="AJ94" s="111">
         <f>Y$47+Q$41+H$39</f>
         <v>6</v>
       </c>
-      <c r="AK94" s="114">
+      <c r="AK94" s="111">
         <f>AL94-V$47-K$41-B$39</f>
         <v>1</v>
       </c>
-      <c r="AL94" s="114">
+      <c r="AL94" s="111">
         <f>T$47+M$41+D$39</f>
         <v>4</v>
       </c>
-      <c r="AM94" s="114">
+      <c r="AM94" s="111">
         <f>AJ94+(AK94/100)+(AL94/10000)+0.00003</f>
         <v>6.0104299999999995</v>
       </c>
@@ -9412,19 +9412,19 @@
       <c r="AO94" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="AP94" s="114">
+      <c r="AP94" s="111">
         <f>Y$45+Q$49+H$43</f>
         <v>1</v>
       </c>
-      <c r="AQ94" s="114">
+      <c r="AQ94" s="111">
         <f>AR94-V$45-K$49-B$43</f>
         <v>-9</v>
       </c>
-      <c r="AR94" s="114">
+      <c r="AR94" s="111">
         <f>T$45+M$49+D$43</f>
         <v>2</v>
       </c>
-      <c r="AS94" s="114">
+      <c r="AS94" s="111">
         <f>AP94+(AQ94/100)+(AR94/10000)+0.00003</f>
         <v>0.91022999999999998</v>
       </c>
@@ -9434,15 +9434,15 @@
       <c r="AU94" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="AV94" s="114">
+      <c r="AV94" s="111">
         <f>Z$41+Q$45+G$47</f>
         <v>3</v>
       </c>
-      <c r="AW94" s="114">
+      <c r="AW94" s="111">
         <f>AX94-T$41-K$45-D$47</f>
         <v>-8</v>
       </c>
-      <c r="AX94" s="114">
+      <c r="AX94" s="111">
         <f>V$41+M$45+B$47</f>
         <v>3</v>
       </c>
@@ -9461,23 +9461,23 @@
       <c r="BH94" s="11"/>
     </row>
     <row r="95" spans="1:60">
-      <c r="A95" s="121" t="s">
+      <c r="A95" s="116" t="s">
         <v>212</v>
       </c>
-      <c r="B95" s="121"/>
-      <c r="C95" s="121"/>
-      <c r="D95" s="121"/>
-      <c r="E95" s="121"/>
+      <c r="B95" s="116"/>
+      <c r="C95" s="116"/>
+      <c r="D95" s="116"/>
+      <c r="E95" s="116"/>
       <c r="F95" s="10">
         <v>46206</v>
       </c>
-      <c r="J95" s="118" t="s">
+      <c r="J95" s="134" t="s">
         <v>213</v>
       </c>
-      <c r="K95" s="118"/>
-      <c r="L95" s="118"/>
-      <c r="M95" s="118"/>
-      <c r="N95" s="118"/>
+      <c r="K95" s="134"/>
+      <c r="L95" s="134"/>
+      <c r="M95" s="134"/>
+      <c r="N95" s="134"/>
       <c r="O95" s="10">
         <v>46214</v>
       </c>
@@ -9488,15 +9488,15 @@
       <c r="AC95" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="AD95" s="114">
+      <c r="AD95" s="111">
         <f>Z$29+Q$37+G$37</f>
         <v>0</v>
       </c>
-      <c r="AE95" s="114">
+      <c r="AE95" s="111">
         <f>AF95-T$29-K$37-D$37</f>
         <v>-8</v>
       </c>
-      <c r="AF95" s="114">
+      <c r="AF95" s="111">
         <f>V$29+M$37+B$37</f>
         <v>0</v>
       </c>
@@ -9510,19 +9510,19 @@
       <c r="AI95" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="AJ95" s="114">
+      <c r="AJ95" s="111">
         <f>Y$49+P$41+H$41</f>
         <v>1</v>
       </c>
-      <c r="AK95" s="114">
+      <c r="AK95" s="111">
         <f>AL95-V$49-M$41-B$41</f>
         <v>-5</v>
       </c>
-      <c r="AL95" s="114">
+      <c r="AL95" s="111">
         <f>T$49+D$41+K$41</f>
         <v>3</v>
       </c>
-      <c r="AM95" s="114">
+      <c r="AM95" s="111">
         <f>AJ95+(AK95/100)+(AL95/10000)+0.00001</f>
         <v>0.95030999999999988</v>
       </c>
@@ -9532,19 +9532,19 @@
       <c r="AO95" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="AP95" s="114">
+      <c r="AP95" s="111">
         <f>Z$45+Q$43+G$49</f>
         <v>1</v>
       </c>
-      <c r="AQ95" s="114">
+      <c r="AQ95" s="111">
         <f>AR95-T$45-K$43-D$49</f>
         <v>-8</v>
       </c>
-      <c r="AR95" s="114">
+      <c r="AR95" s="111">
         <f>V$45+M$43+B$49</f>
         <v>2</v>
       </c>
-      <c r="AS95" s="114">
+      <c r="AS95" s="111">
         <f>AP95+(AQ95/100)+(AR95/10000)+0.00002</f>
         <v>0.92022000000000004</v>
       </c>
@@ -9554,19 +9554,19 @@
       <c r="AU95" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="AV95" s="114">
+      <c r="AV95" s="111">
         <f>Y$39+P$47+H$47</f>
         <v>0</v>
       </c>
-      <c r="AW95" s="114">
+      <c r="AW95" s="111">
         <f>AX95-V$39-M$47-B$47</f>
         <v>-9</v>
       </c>
-      <c r="AX95" s="114">
+      <c r="AX95" s="111">
         <f>T$39+K$47+D$47</f>
         <v>2</v>
       </c>
-      <c r="AY95" s="114">
+      <c r="AY95" s="111">
         <f>AV95+(AW95/100)+(AX95/10000)+0.00001</f>
         <v>-8.9789999999999995E-2</v>
       </c>
@@ -9588,7 +9588,7 @@
       <c r="B96" s="2">
         <v>2</v>
       </c>
-      <c r="C96" s="99" t="s">
+      <c r="C96" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="4">
@@ -9608,7 +9608,7 @@
       <c r="K96" s="1">
         <v>2</v>
       </c>
-      <c r="L96" s="115" t="s">
+      <c r="L96" s="99" t="s">
         <v>12</v>
       </c>
       <c r="M96">
@@ -9621,81 +9621,81 @@
       <c r="O96" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AD96" s="100"/>
-      <c r="AE96" s="100"/>
-      <c r="AF96" s="100"/>
-      <c r="AJ96" s="100"/>
-      <c r="AK96" s="100"/>
-      <c r="AL96" s="100"/>
-      <c r="AM96" s="100"/>
-      <c r="AP96" s="100"/>
-      <c r="AQ96" s="100"/>
-      <c r="AR96" s="100"/>
-      <c r="AS96" s="100"/>
-      <c r="AV96" s="100"/>
-      <c r="AW96" s="100"/>
-      <c r="AX96" s="100"/>
+      <c r="AD96" s="112"/>
+      <c r="AE96" s="112"/>
+      <c r="AF96" s="112"/>
+      <c r="AJ96" s="112"/>
+      <c r="AK96" s="112"/>
+      <c r="AL96" s="112"/>
+      <c r="AM96" s="112"/>
+      <c r="AP96" s="112"/>
+      <c r="AQ96" s="112"/>
+      <c r="AR96" s="112"/>
+      <c r="AS96" s="112"/>
+      <c r="AV96" s="112"/>
+      <c r="AW96" s="112"/>
+      <c r="AX96" s="112"/>
     </row>
     <row r="97" spans="1:32">
       <c r="A97" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="99" t="s">
+      <c r="C97" s="101" t="s">
         <v>157</v>
       </c>
       <c r="E97" s="83"/>
       <c r="J97" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="L97" s="115" t="s">
+      <c r="L97" s="99" t="s">
         <v>157</v>
       </c>
       <c r="N97" s="88"/>
-      <c r="AD97" s="100"/>
-      <c r="AE97" s="100"/>
-      <c r="AF97" s="100"/>
+      <c r="AD97" s="112"/>
+      <c r="AE97" s="112"/>
+      <c r="AF97" s="112"/>
     </row>
     <row r="98" spans="1:32">
-      <c r="A98" s="121" t="s">
+      <c r="A98" s="116" t="s">
         <v>215</v>
       </c>
-      <c r="B98" s="121"/>
-      <c r="C98" s="121"/>
-      <c r="D98" s="121"/>
-      <c r="E98" s="121"/>
+      <c r="B98" s="116"/>
+      <c r="C98" s="116"/>
+      <c r="D98" s="116"/>
+      <c r="E98" s="116"/>
       <c r="F98" s="10">
         <v>46206</v>
       </c>
-      <c r="J98" s="118" t="s">
+      <c r="J98" s="134" t="s">
         <v>216</v>
       </c>
-      <c r="K98" s="118"/>
-      <c r="L98" s="118"/>
-      <c r="M98" s="118"/>
-      <c r="N98" s="118"/>
+      <c r="K98" s="134"/>
+      <c r="L98" s="134"/>
+      <c r="M98" s="134"/>
+      <c r="N98" s="134"/>
       <c r="O98" s="10">
         <v>46214</v>
       </c>
-      <c r="S98" s="116" t="s">
+      <c r="S98" s="132" t="s">
         <v>217</v>
       </c>
-      <c r="T98" s="116"/>
-      <c r="U98" s="116"/>
-      <c r="V98" s="116"/>
-      <c r="W98" s="116"/>
+      <c r="T98" s="132"/>
+      <c r="U98" s="132"/>
+      <c r="V98" s="132"/>
+      <c r="W98" s="132"/>
       <c r="X98" s="15">
         <v>46222</v>
       </c>
-      <c r="Y98" s="100"/>
-      <c r="Z98" s="100"/>
-      <c r="AA98" s="100"/>
-      <c r="AB98" s="116" t="s">
+      <c r="Y98" s="112"/>
+      <c r="Z98" s="112"/>
+      <c r="AA98" s="112"/>
+      <c r="AB98" s="132" t="s">
         <v>218</v>
       </c>
-      <c r="AC98" s="116"/>
-      <c r="AD98" s="116"/>
-      <c r="AE98" s="116"/>
-      <c r="AF98" s="116"/>
+      <c r="AC98" s="132"/>
+      <c r="AD98" s="132"/>
+      <c r="AE98" s="132"/>
+      <c r="AF98" s="132"/>
     </row>
     <row r="99" spans="1:32">
       <c r="A99" s="80" t="str">
@@ -9705,7 +9705,7 @@
       <c r="B99" s="2">
         <v>1</v>
       </c>
-      <c r="C99" s="99" t="s">
+      <c r="C99" s="101" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="4">
@@ -9725,7 +9725,7 @@
       <c r="K99" s="1">
         <v>2</v>
       </c>
-      <c r="L99" s="115" t="s">
+      <c r="L99" s="99" t="s">
         <v>12</v>
       </c>
       <c r="M99">
@@ -9758,17 +9758,17 @@
       <c r="X99" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Y99" s="100"/>
-      <c r="Z99" s="100"/>
-      <c r="AA99" s="100"/>
-      <c r="AB99" s="116" t="str">
+      <c r="Y99" s="112"/>
+      <c r="Z99" s="112"/>
+      <c r="AA99" s="112"/>
+      <c r="AB99" s="132" t="str">
         <f>IF(T99 = "", "", IF(T99 &gt; V99, S99, IF(V99 &gt; T99, W99, IF(V100 &gt; T100, W99, S99))))</f>
         <v>França</v>
       </c>
-      <c r="AC99" s="116"/>
-      <c r="AD99" s="116"/>
-      <c r="AE99" s="116"/>
-      <c r="AF99" s="116"/>
+      <c r="AC99" s="132"/>
+      <c r="AD99" s="132"/>
+      <c r="AE99" s="132"/>
+      <c r="AF99" s="132"/>
     </row>
     <row r="100" spans="1:32">
       <c r="A100" s="81" t="s">
@@ -9777,7 +9777,7 @@
       <c r="B100" s="2">
         <v>3</v>
       </c>
-      <c r="C100" s="99" t="s">
+      <c r="C100" s="101" t="s">
         <v>157</v>
       </c>
       <c r="D100" s="4">
@@ -9787,7 +9787,7 @@
       <c r="J100" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="L100" s="115" t="s">
+      <c r="L100" s="99" t="s">
         <v>157</v>
       </c>
       <c r="N100" s="88"/>
@@ -9798,9 +9798,9 @@
         <v>157</v>
       </c>
       <c r="W100" s="92"/>
-      <c r="AD100" s="100"/>
-      <c r="AE100" s="100"/>
-      <c r="AF100" s="100"/>
+      <c r="AD100" s="112"/>
+      <c r="AE100" s="112"/>
+      <c r="AF100" s="112"/>
     </row>
     <row r="101" spans="1:32">
       <c r="A101" s="80"/>
@@ -9818,75 +9818,75 @@
       <c r="U101" s="85"/>
       <c r="V101" s="94"/>
       <c r="W101" s="95"/>
-      <c r="AD101" s="100"/>
-      <c r="AE101" s="100"/>
-      <c r="AF101" s="100"/>
+      <c r="AD101" s="112"/>
+      <c r="AE101" s="112"/>
+      <c r="AF101" s="112"/>
     </row>
     <row r="102" spans="1:32">
-      <c r="AD102" s="100"/>
-      <c r="AE102" s="100"/>
-      <c r="AF102" s="100"/>
+      <c r="AD102" s="112"/>
+      <c r="AE102" s="112"/>
+      <c r="AF102" s="112"/>
     </row>
     <row r="103" spans="1:32">
-      <c r="AD103" s="100"/>
-      <c r="AE103" s="100"/>
-      <c r="AF103" s="100"/>
+      <c r="AD103" s="112"/>
+      <c r="AE103" s="112"/>
+      <c r="AF103" s="112"/>
     </row>
     <row r="104" spans="1:32">
       <c r="B104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="AD104" s="100"/>
-      <c r="AE104" s="100"/>
-      <c r="AF104" s="100"/>
+      <c r="AD104" s="112"/>
+      <c r="AE104" s="112"/>
+      <c r="AF104" s="112"/>
     </row>
     <row r="105" spans="1:32">
-      <c r="AD105" s="100"/>
-      <c r="AE105" s="100"/>
-      <c r="AF105" s="100"/>
+      <c r="AD105" s="112"/>
+      <c r="AE105" s="112"/>
+      <c r="AF105" s="112"/>
     </row>
     <row r="106" spans="1:32">
-      <c r="AD106" s="100"/>
-      <c r="AE106" s="100"/>
-      <c r="AF106" s="100"/>
+      <c r="AD106" s="112"/>
+      <c r="AE106" s="112"/>
+      <c r="AF106" s="112"/>
     </row>
     <row r="107" spans="1:32">
       <c r="B107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
-      <c r="AD107" s="100"/>
-      <c r="AE107" s="100"/>
-      <c r="AF107" s="100"/>
+      <c r="AD107" s="112"/>
+      <c r="AE107" s="112"/>
+      <c r="AF107" s="112"/>
     </row>
     <row r="108" spans="1:32">
-      <c r="AD108" s="100"/>
-      <c r="AE108" s="100"/>
-      <c r="AF108" s="100"/>
+      <c r="AD108" s="112"/>
+      <c r="AE108" s="112"/>
+      <c r="AF108" s="112"/>
     </row>
     <row r="109" spans="1:32">
-      <c r="AD109" s="100"/>
-      <c r="AE109" s="100"/>
-      <c r="AF109" s="100"/>
+      <c r="AD109" s="112"/>
+      <c r="AE109" s="112"/>
+      <c r="AF109" s="112"/>
     </row>
     <row r="110" spans="1:32">
-      <c r="A110" s="132"/>
-      <c r="B110" s="132"/>
-      <c r="C110" s="132"/>
-      <c r="D110" s="132"/>
-      <c r="E110" s="132"/>
-      <c r="AD110" s="100"/>
-      <c r="AE110" s="100"/>
-      <c r="AF110" s="100"/>
+      <c r="A110" s="117"/>
+      <c r="B110" s="117"/>
+      <c r="C110" s="117"/>
+      <c r="D110" s="117"/>
+      <c r="E110" s="117"/>
+      <c r="AD110" s="112"/>
+      <c r="AE110" s="112"/>
+      <c r="AF110" s="112"/>
     </row>
     <row r="111" spans="1:32">
-      <c r="AD111" s="100"/>
-      <c r="AE111" s="100"/>
-      <c r="AF111" s="100"/>
+      <c r="AD111" s="112"/>
+      <c r="AE111" s="112"/>
+      <c r="AF111" s="112"/>
     </row>
     <row r="112" spans="1:32">
-      <c r="AD112" s="100"/>
-      <c r="AE112" s="100"/>
-      <c r="AF112" s="100"/>
+      <c r="AD112" s="112"/>
+      <c r="AE112" s="112"/>
+      <c r="AF112" s="112"/>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1"/>
@@ -9915,17 +9915,87 @@
     <sortCondition descending="1" ref="AX92:AX95"/>
   </sortState>
   <mergeCells count="116">
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A92:E92"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="AB98:AF98"/>
+    <mergeCell ref="AB99:AF99"/>
+    <mergeCell ref="S83:W83"/>
+    <mergeCell ref="S84:W84"/>
+    <mergeCell ref="S87:W87"/>
+    <mergeCell ref="S92:W92"/>
+    <mergeCell ref="S98:W98"/>
+    <mergeCell ref="J36:N36"/>
+    <mergeCell ref="J71:N71"/>
+    <mergeCell ref="J74:N74"/>
+    <mergeCell ref="J80:N80"/>
+    <mergeCell ref="J83:N83"/>
+    <mergeCell ref="J89:N89"/>
+    <mergeCell ref="J77:N77"/>
+    <mergeCell ref="J88:N88"/>
+    <mergeCell ref="J92:N92"/>
+    <mergeCell ref="J95:N95"/>
+    <mergeCell ref="J98:N98"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="S22:W22"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="J38:N38"/>
+    <mergeCell ref="BC79:BF79"/>
+    <mergeCell ref="S26:W26"/>
+    <mergeCell ref="S28:W28"/>
+    <mergeCell ref="S51:W51"/>
+    <mergeCell ref="S40:W40"/>
+    <mergeCell ref="S42:W42"/>
+    <mergeCell ref="S44:W44"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="S48:W48"/>
+    <mergeCell ref="J34:N34"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="J48:N48"/>
+    <mergeCell ref="J46:N46"/>
+    <mergeCell ref="J44:N44"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="J62:N62"/>
+    <mergeCell ref="J65:N65"/>
+    <mergeCell ref="J68:N68"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="J14:N14"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="J30:N30"/>
+    <mergeCell ref="J28:N28"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A53:E53"/>
@@ -9950,87 +10020,17 @@
     <mergeCell ref="J24:N24"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="J62:N62"/>
-    <mergeCell ref="J65:N65"/>
-    <mergeCell ref="J68:N68"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="J61:N61"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="J22:N22"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="J18:N18"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="J14:N14"/>
-    <mergeCell ref="J32:N32"/>
-    <mergeCell ref="J30:N30"/>
-    <mergeCell ref="J28:N28"/>
-    <mergeCell ref="J26:N26"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="J42:N42"/>
-    <mergeCell ref="J40:N40"/>
-    <mergeCell ref="J38:N38"/>
-    <mergeCell ref="BC79:BF79"/>
-    <mergeCell ref="S26:W26"/>
-    <mergeCell ref="S28:W28"/>
-    <mergeCell ref="S51:W51"/>
-    <mergeCell ref="S40:W40"/>
-    <mergeCell ref="S42:W42"/>
-    <mergeCell ref="S44:W44"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="J34:N34"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="J48:N48"/>
-    <mergeCell ref="J46:N46"/>
-    <mergeCell ref="J44:N44"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="S22:W22"/>
-    <mergeCell ref="S24:W24"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="AB98:AF98"/>
-    <mergeCell ref="AB99:AF99"/>
-    <mergeCell ref="S83:W83"/>
-    <mergeCell ref="S84:W84"/>
-    <mergeCell ref="S87:W87"/>
-    <mergeCell ref="S92:W92"/>
-    <mergeCell ref="S98:W98"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="J71:N71"/>
-    <mergeCell ref="J74:N74"/>
-    <mergeCell ref="J80:N80"/>
-    <mergeCell ref="J83:N83"/>
-    <mergeCell ref="J89:N89"/>
-    <mergeCell ref="J77:N77"/>
-    <mergeCell ref="J88:N88"/>
-    <mergeCell ref="J92:N92"/>
-    <mergeCell ref="J95:N95"/>
-    <mergeCell ref="J98:N98"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A98:E98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
